--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -4265,7 +4265,7 @@
     <x:col min="2" max="8" width="10.832031" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" spans="1:8" customFormat="1" ht="30.75" customHeight="1">
+    <x:row r="2" spans="1:8" ht="30.75" customHeight="1">
       <x:c r="B2" s="49" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -4288,7 +4288,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:8" customFormat="1" ht="20.1" customHeight="1">
+    <x:row r="3" spans="1:8" ht="20.1" customHeight="1">
       <x:c r="B3" s="48" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -9033,12 +9033,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:6"/>
-    <x:row r="4" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="5" spans="1:6" customFormat="1" ht="25.5" customHeight="1"/>
+    <x:row r="4" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="5" spans="1:6" ht="25.5" customHeight="1"/>
     <x:row r="6" spans="1:6"/>
     <x:row r="7" spans="1:6"/>
-    <x:row r="8" spans="1:6" customFormat="1" ht="12" customHeight="1"/>
-    <x:row r="9" spans="1:6" customFormat="1" ht="12.75" customHeight="1"/>
+    <x:row r="8" spans="1:6" ht="12" customHeight="1"/>
+    <x:row r="9" spans="1:6" ht="12.75" customHeight="1"/>
   </x:sheetData>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -9068,7 +9068,7 @@
     <x:row r="4" spans="1:5"/>
     <x:row r="5" spans="1:5"/>
     <x:row r="6" spans="1:5"/>
-    <x:row r="7" spans="1:5" customFormat="1" ht="11.25" customHeight="1"/>
+    <x:row r="7" spans="1:5" ht="11.25" customHeight="1"/>
     <x:row r="8" spans="1:5"/>
     <x:row r="9" spans="1:5"/>
   </x:sheetData>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -4301,13 +4301,13 @@
       <x:c r="E3" s="52">
         <x:v>32266</x:v>
       </x:c>
-      <x:c r="F3" s="53" t="n">
+      <x:c r="F3" s="53">
         <x:v>1250</x:v>
       </x:c>
-      <x:c r="G3" s="54" t="n">
+      <x:c r="G3" s="54">
         <x:v>4.5</x:v>
       </x:c>
-      <x:c r="H3" s="53" t="n">
+      <x:c r="H3" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4324,13 +4324,13 @@
       <x:c r="E4" s="52">
         <x:v>32251</x:v>
       </x:c>
-      <x:c r="F4" s="53" t="n">
+      <x:c r="F4" s="53">
         <x:v>7885</x:v>
       </x:c>
-      <x:c r="G4" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="53" t="n">
+      <x:c r="G4" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="53">
         <x:v>7885</x:v>
       </x:c>
     </x:row>
@@ -4347,13 +4347,13 @@
       <x:c r="E5" s="52">
         <x:v>32163</x:v>
       </x:c>
-      <x:c r="F5" s="53" t="n">
+      <x:c r="F5" s="53">
         <x:v>4807</x:v>
       </x:c>
-      <x:c r="G5" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="53" t="n">
+      <x:c r="G5" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="53">
         <x:v>4807</x:v>
       </x:c>
     </x:row>
@@ -4370,13 +4370,13 @@
       <x:c r="E6" s="52">
         <x:v>32454</x:v>
       </x:c>
-      <x:c r="F6" s="53" t="n">
+      <x:c r="F6" s="53">
         <x:v>31987</x:v>
       </x:c>
-      <x:c r="G6" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="53" t="n">
+      <x:c r="G6" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4393,13 +4393,13 @@
       <x:c r="E7" s="52">
         <x:v>32265</x:v>
       </x:c>
-      <x:c r="F7" s="53" t="n">
+      <x:c r="F7" s="53">
         <x:v>6500</x:v>
       </x:c>
-      <x:c r="G7" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="53" t="n">
+      <x:c r="G7" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="53">
         <x:v>6500</x:v>
       </x:c>
     </x:row>
@@ -4416,13 +4416,13 @@
       <x:c r="E8" s="52">
         <x:v>32267</x:v>
       </x:c>
-      <x:c r="F8" s="53" t="n">
+      <x:c r="F8" s="53">
         <x:v>1449.5</x:v>
       </x:c>
-      <x:c r="G8" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="53" t="n">
+      <x:c r="G8" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4439,13 +4439,13 @@
       <x:c r="E9" s="52">
         <x:v>32275</x:v>
       </x:c>
-      <x:c r="F9" s="53" t="n">
+      <x:c r="F9" s="53">
         <x:v>5587</x:v>
       </x:c>
-      <x:c r="G9" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="53" t="n">
+      <x:c r="G9" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4462,13 +4462,13 @@
       <x:c r="E10" s="52">
         <x:v>32275</x:v>
       </x:c>
-      <x:c r="F10" s="53" t="n">
+      <x:c r="F10" s="53">
         <x:v>4996</x:v>
       </x:c>
-      <x:c r="G10" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="53" t="n">
+      <x:c r="G10" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="53">
         <x:v>4996</x:v>
       </x:c>
     </x:row>
@@ -4485,13 +4485,13 @@
       <x:c r="E11" s="52">
         <x:v>32282</x:v>
       </x:c>
-      <x:c r="F11" s="53" t="n">
+      <x:c r="F11" s="53">
         <x:v>2679.85</x:v>
       </x:c>
-      <x:c r="G11" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="53" t="n">
+      <x:c r="G11" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="53">
         <x:v>2679.85</x:v>
       </x:c>
     </x:row>
@@ -4508,13 +4508,13 @@
       <x:c r="E12" s="52">
         <x:v>32283</x:v>
       </x:c>
-      <x:c r="F12" s="53" t="n">
+      <x:c r="F12" s="53">
         <x:v>5201</x:v>
       </x:c>
-      <x:c r="G12" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="53" t="n">
+      <x:c r="G12" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="53">
         <x:v>5201</x:v>
       </x:c>
     </x:row>
@@ -4531,13 +4531,13 @@
       <x:c r="E13" s="52">
         <x:v>32289</x:v>
       </x:c>
-      <x:c r="F13" s="53" t="n">
+      <x:c r="F13" s="53">
         <x:v>3115</x:v>
       </x:c>
-      <x:c r="G13" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="53" t="n">
+      <x:c r="G13" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="53">
         <x:v>3115</x:v>
       </x:c>
     </x:row>
@@ -4554,13 +4554,13 @@
       <x:c r="E14" s="52">
         <x:v>32289</x:v>
       </x:c>
-      <x:c r="F14" s="53" t="n">
+      <x:c r="F14" s="53">
         <x:v>134.85</x:v>
       </x:c>
-      <x:c r="G14" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="53" t="n">
+      <x:c r="G14" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="53">
         <x:v>134.85</x:v>
       </x:c>
     </x:row>
@@ -4577,13 +4577,13 @@
       <x:c r="E15" s="52">
         <x:v>32289</x:v>
       </x:c>
-      <x:c r="F15" s="53" t="n">
+      <x:c r="F15" s="53">
         <x:v>20321.75</x:v>
       </x:c>
-      <x:c r="G15" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="53" t="n">
+      <x:c r="G15" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="53">
         <x:v>20321.75</x:v>
       </x:c>
     </x:row>
@@ -4600,13 +4600,13 @@
       <x:c r="E16" s="52">
         <x:v>32297</x:v>
       </x:c>
-      <x:c r="F16" s="53" t="n">
+      <x:c r="F16" s="53">
         <x:v>2605</x:v>
       </x:c>
-      <x:c r="G16" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="53" t="n">
+      <x:c r="G16" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4623,13 +4623,13 @@
       <x:c r="E17" s="52">
         <x:v>32307</x:v>
       </x:c>
-      <x:c r="F17" s="53" t="n">
+      <x:c r="F17" s="53">
         <x:v>10195</x:v>
       </x:c>
-      <x:c r="G17" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="53" t="n">
+      <x:c r="G17" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4646,13 +4646,13 @@
       <x:c r="E18" s="52">
         <x:v>32313</x:v>
       </x:c>
-      <x:c r="F18" s="53" t="n">
+      <x:c r="F18" s="53">
         <x:v>5256</x:v>
       </x:c>
-      <x:c r="G18" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H18" s="53" t="n">
+      <x:c r="G18" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4669,13 +4669,13 @@
       <x:c r="E19" s="52">
         <x:v>32319</x:v>
       </x:c>
-      <x:c r="F19" s="53" t="n">
+      <x:c r="F19" s="53">
         <x:v>20602</x:v>
       </x:c>
-      <x:c r="G19" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="53" t="n">
+      <x:c r="G19" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4692,13 +4692,13 @@
       <x:c r="E20" s="52">
         <x:v>32319</x:v>
       </x:c>
-      <x:c r="F20" s="53" t="n">
+      <x:c r="F20" s="53">
         <x:v>9955</x:v>
       </x:c>
-      <x:c r="G20" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="53" t="n">
+      <x:c r="G20" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="53">
         <x:v>9955</x:v>
       </x:c>
     </x:row>
@@ -4715,13 +4715,13 @@
       <x:c r="E21" s="52">
         <x:v>32319</x:v>
       </x:c>
-      <x:c r="F21" s="53" t="n">
+      <x:c r="F21" s="53">
         <x:v>3719</x:v>
       </x:c>
-      <x:c r="G21" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="53" t="n">
+      <x:c r="G21" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="53">
         <x:v>3719</x:v>
       </x:c>
     </x:row>
@@ -4738,13 +4738,13 @@
       <x:c r="E22" s="52">
         <x:v>32325</x:v>
       </x:c>
-      <x:c r="F22" s="53" t="n">
+      <x:c r="F22" s="53">
         <x:v>10064.65</x:v>
       </x:c>
-      <x:c r="G22" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H22" s="53" t="n">
+      <x:c r="G22" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="53">
         <x:v>10064.65</x:v>
       </x:c>
     </x:row>
@@ -4761,13 +4761,13 @@
       <x:c r="E23" s="52">
         <x:v>32326</x:v>
       </x:c>
-      <x:c r="F23" s="53" t="n">
+      <x:c r="F23" s="53">
         <x:v>4674</x:v>
       </x:c>
-      <x:c r="G23" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="53" t="n">
+      <x:c r="G23" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="53">
         <x:v>4674</x:v>
       </x:c>
     </x:row>
@@ -4784,13 +4784,13 @@
       <x:c r="E24" s="52">
         <x:v>32327</x:v>
       </x:c>
-      <x:c r="F24" s="53" t="n">
+      <x:c r="F24" s="53">
         <x:v>6897</x:v>
       </x:c>
-      <x:c r="G24" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H24" s="53" t="n">
+      <x:c r="G24" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H24" s="53">
         <x:v>6897</x:v>
       </x:c>
     </x:row>
@@ -4807,13 +4807,13 @@
       <x:c r="E25" s="52">
         <x:v>32328</x:v>
       </x:c>
-      <x:c r="F25" s="53" t="n">
+      <x:c r="F25" s="53">
         <x:v>930</x:v>
       </x:c>
-      <x:c r="G25" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H25" s="53" t="n">
+      <x:c r="G25" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="53">
         <x:v>930</x:v>
       </x:c>
     </x:row>
@@ -4830,13 +4830,13 @@
       <x:c r="E26" s="52">
         <x:v>32332</x:v>
       </x:c>
-      <x:c r="F26" s="53" t="n">
+      <x:c r="F26" s="53">
         <x:v>2920</x:v>
       </x:c>
-      <x:c r="G26" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="53" t="n">
+      <x:c r="G26" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="53">
         <x:v>2920</x:v>
       </x:c>
     </x:row>
@@ -4853,13 +4853,13 @@
       <x:c r="E27" s="52">
         <x:v>32332</x:v>
       </x:c>
-      <x:c r="F27" s="53" t="n">
+      <x:c r="F27" s="53">
         <x:v>25210</x:v>
       </x:c>
-      <x:c r="G27" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="53" t="n">
+      <x:c r="G27" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="53">
         <x:v>25210</x:v>
       </x:c>
     </x:row>
@@ -4876,13 +4876,13 @@
       <x:c r="E28" s="52">
         <x:v>32332</x:v>
       </x:c>
-      <x:c r="F28" s="53" t="n">
+      <x:c r="F28" s="53">
         <x:v>343.8</x:v>
       </x:c>
-      <x:c r="G28" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H28" s="53" t="n">
+      <x:c r="G28" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="53">
         <x:v>343.8</x:v>
       </x:c>
     </x:row>
@@ -4899,13 +4899,13 @@
       <x:c r="E29" s="52">
         <x:v>32343</x:v>
       </x:c>
-      <x:c r="F29" s="53" t="n">
+      <x:c r="F29" s="53">
         <x:v>20108</x:v>
       </x:c>
-      <x:c r="G29" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="53" t="n">
+      <x:c r="G29" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="53">
         <x:v>20108</x:v>
       </x:c>
     </x:row>
@@ -4922,13 +4922,13 @@
       <x:c r="E30" s="52">
         <x:v>32350</x:v>
       </x:c>
-      <x:c r="F30" s="53" t="n">
+      <x:c r="F30" s="53">
         <x:v>559.6</x:v>
       </x:c>
-      <x:c r="G30" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="53" t="n">
+      <x:c r="G30" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="53">
         <x:v>559.6</x:v>
       </x:c>
     </x:row>
@@ -4945,13 +4945,13 @@
       <x:c r="E31" s="52">
         <x:v>32356</x:v>
       </x:c>
-      <x:c r="F31" s="53" t="n">
+      <x:c r="F31" s="53">
         <x:v>12685</x:v>
       </x:c>
-      <x:c r="G31" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H31" s="53" t="n">
+      <x:c r="G31" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H31" s="53">
         <x:v>12685</x:v>
       </x:c>
     </x:row>
@@ -4968,13 +4968,13 @@
       <x:c r="E32" s="52">
         <x:v>32356</x:v>
       </x:c>
-      <x:c r="F32" s="53" t="n">
+      <x:c r="F32" s="53">
         <x:v>775</x:v>
       </x:c>
-      <x:c r="G32" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="53" t="n">
+      <x:c r="G32" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="53">
         <x:v>775</x:v>
       </x:c>
     </x:row>
@@ -4991,13 +4991,13 @@
       <x:c r="E33" s="52">
         <x:v>32357</x:v>
       </x:c>
-      <x:c r="F33" s="53" t="n">
+      <x:c r="F33" s="53">
         <x:v>1238</x:v>
       </x:c>
-      <x:c r="G33" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H33" s="53" t="n">
+      <x:c r="G33" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H33" s="53">
         <x:v>1238</x:v>
       </x:c>
     </x:row>
@@ -5014,13 +5014,13 @@
       <x:c r="E34" s="52">
         <x:v>32369</x:v>
       </x:c>
-      <x:c r="F34" s="53" t="n">
+      <x:c r="F34" s="53">
         <x:v>18532</x:v>
       </x:c>
-      <x:c r="G34" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="53" t="n">
+      <x:c r="G34" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="53">
         <x:v>18532</x:v>
       </x:c>
     </x:row>
@@ -5037,13 +5037,13 @@
       <x:c r="E35" s="52">
         <x:v>32372</x:v>
       </x:c>
-      <x:c r="F35" s="53" t="n">
+      <x:c r="F35" s="53">
         <x:v>560</x:v>
       </x:c>
-      <x:c r="G35" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="53" t="n">
+      <x:c r="G35" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="53">
         <x:v>560</x:v>
       </x:c>
     </x:row>
@@ -5060,13 +5060,13 @@
       <x:c r="E36" s="52">
         <x:v>32381</x:v>
       </x:c>
-      <x:c r="F36" s="53" t="n">
+      <x:c r="F36" s="53">
         <x:v>4110</x:v>
       </x:c>
-      <x:c r="G36" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="53" t="n">
+      <x:c r="G36" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="53">
         <x:v>4110</x:v>
       </x:c>
     </x:row>
@@ -5083,13 +5083,13 @@
       <x:c r="E37" s="52">
         <x:v>32382</x:v>
       </x:c>
-      <x:c r="F37" s="53" t="n">
+      <x:c r="F37" s="53">
         <x:v>3117</x:v>
       </x:c>
-      <x:c r="G37" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="53" t="n">
+      <x:c r="G37" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="53">
         <x:v>3117</x:v>
       </x:c>
     </x:row>
@@ -5106,13 +5106,13 @@
       <x:c r="E38" s="52">
         <x:v>32382</x:v>
       </x:c>
-      <x:c r="F38" s="53" t="n">
+      <x:c r="F38" s="53">
         <x:v>10152</x:v>
       </x:c>
-      <x:c r="G38" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="53" t="n">
+      <x:c r="G38" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="53">
         <x:v>10152</x:v>
       </x:c>
     </x:row>
@@ -5129,13 +5129,13 @@
       <x:c r="E39" s="52">
         <x:v>32387</x:v>
       </x:c>
-      <x:c r="F39" s="53" t="n">
+      <x:c r="F39" s="53">
         <x:v>536.8</x:v>
       </x:c>
-      <x:c r="G39" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H39" s="53" t="n">
+      <x:c r="G39" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H39" s="53">
         <x:v>536.8</x:v>
       </x:c>
     </x:row>
@@ -5152,13 +5152,13 @@
       <x:c r="E40" s="52">
         <x:v>32391</x:v>
       </x:c>
-      <x:c r="F40" s="53" t="n">
+      <x:c r="F40" s="53">
         <x:v>3632</x:v>
       </x:c>
-      <x:c r="G40" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="53" t="n">
+      <x:c r="G40" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="53">
         <x:v>3632</x:v>
       </x:c>
     </x:row>
@@ -5175,13 +5175,13 @@
       <x:c r="E41" s="52">
         <x:v>32403</x:v>
       </x:c>
-      <x:c r="F41" s="53" t="n">
+      <x:c r="F41" s="53">
         <x:v>7807</x:v>
       </x:c>
-      <x:c r="G41" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H41" s="53" t="n">
+      <x:c r="G41" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H41" s="53">
         <x:v>7807</x:v>
       </x:c>
     </x:row>
@@ -5198,13 +5198,13 @@
       <x:c r="E42" s="52">
         <x:v>32411</x:v>
       </x:c>
-      <x:c r="F42" s="53" t="n">
+      <x:c r="F42" s="53">
         <x:v>971.7</x:v>
       </x:c>
-      <x:c r="G42" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" s="53" t="n">
+      <x:c r="G42" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="53">
         <x:v>971.7</x:v>
       </x:c>
     </x:row>
@@ -5221,13 +5221,13 @@
       <x:c r="E43" s="52">
         <x:v>32417</x:v>
       </x:c>
-      <x:c r="F43" s="53" t="n">
+      <x:c r="F43" s="53">
         <x:v>12455</x:v>
       </x:c>
-      <x:c r="G43" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" s="53" t="n">
+      <x:c r="G43" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="53">
         <x:v>12455</x:v>
       </x:c>
     </x:row>
@@ -5244,13 +5244,13 @@
       <x:c r="E44" s="52">
         <x:v>32425</x:v>
       </x:c>
-      <x:c r="F44" s="53" t="n">
+      <x:c r="F44" s="53">
         <x:v>64050</x:v>
       </x:c>
-      <x:c r="G44" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H44" s="53" t="n">
+      <x:c r="G44" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="53">
         <x:v>64050</x:v>
       </x:c>
     </x:row>
@@ -5267,13 +5267,13 @@
       <x:c r="E45" s="52">
         <x:v>32433</x:v>
       </x:c>
-      <x:c r="F45" s="53" t="n">
+      <x:c r="F45" s="53">
         <x:v>787.8</x:v>
       </x:c>
-      <x:c r="G45" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H45" s="53" t="n">
+      <x:c r="G45" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="53">
         <x:v>787.8</x:v>
       </x:c>
     </x:row>
@@ -5290,13 +5290,13 @@
       <x:c r="E46" s="52">
         <x:v>32460</x:v>
       </x:c>
-      <x:c r="F46" s="53" t="n">
+      <x:c r="F46" s="53">
         <x:v>766.8</x:v>
       </x:c>
-      <x:c r="G46" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H46" s="53" t="n">
+      <x:c r="G46" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" s="53">
         <x:v>766.8</x:v>
       </x:c>
     </x:row>
@@ -5313,13 +5313,13 @@
       <x:c r="E47" s="52">
         <x:v>32475</x:v>
       </x:c>
-      <x:c r="F47" s="53" t="n">
+      <x:c r="F47" s="53">
         <x:v>15365</x:v>
       </x:c>
-      <x:c r="G47" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H47" s="53" t="n">
+      <x:c r="G47" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" s="53">
         <x:v>15365</x:v>
       </x:c>
     </x:row>
@@ -5336,13 +5336,13 @@
       <x:c r="E48" s="52">
         <x:v>32480</x:v>
       </x:c>
-      <x:c r="F48" s="53" t="n">
+      <x:c r="F48" s="53">
         <x:v>7346</x:v>
       </x:c>
-      <x:c r="G48" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H48" s="53" t="n">
+      <x:c r="G48" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H48" s="53">
         <x:v>7346</x:v>
       </x:c>
     </x:row>
@@ -5359,13 +5359,13 @@
       <x:c r="E49" s="52">
         <x:v>32491</x:v>
       </x:c>
-      <x:c r="F49" s="53" t="n">
+      <x:c r="F49" s="53">
         <x:v>1809.85</x:v>
       </x:c>
-      <x:c r="G49" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H49" s="53" t="n">
+      <x:c r="G49" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" s="53">
         <x:v>1809.85</x:v>
       </x:c>
     </x:row>
@@ -5382,13 +5382,13 @@
       <x:c r="E50" s="52">
         <x:v>32502</x:v>
       </x:c>
-      <x:c r="F50" s="53" t="n">
+      <x:c r="F50" s="53">
         <x:v>6287.85</x:v>
       </x:c>
-      <x:c r="G50" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H50" s="53" t="n">
+      <x:c r="G50" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H50" s="53">
         <x:v>6287.85</x:v>
       </x:c>
     </x:row>
@@ -5405,13 +5405,13 @@
       <x:c r="E51" s="52">
         <x:v>32513</x:v>
       </x:c>
-      <x:c r="F51" s="53" t="n">
+      <x:c r="F51" s="53">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="G51" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H51" s="53" t="n">
+      <x:c r="G51" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H51" s="53">
         <x:v>325</x:v>
       </x:c>
     </x:row>
@@ -5428,13 +5428,13 @@
       <x:c r="E52" s="52">
         <x:v>32515</x:v>
       </x:c>
-      <x:c r="F52" s="53" t="n">
+      <x:c r="F52" s="53">
         <x:v>16788</x:v>
       </x:c>
-      <x:c r="G52" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H52" s="53" t="n">
+      <x:c r="G52" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H52" s="53">
         <x:v>16788</x:v>
       </x:c>
     </x:row>
@@ -5451,13 +5451,13 @@
       <x:c r="E53" s="52">
         <x:v>32524</x:v>
       </x:c>
-      <x:c r="F53" s="53" t="n">
+      <x:c r="F53" s="53">
         <x:v>24650</x:v>
       </x:c>
-      <x:c r="G53" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H53" s="53" t="n">
+      <x:c r="G53" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H53" s="53">
         <x:v>24650</x:v>
       </x:c>
     </x:row>
@@ -5474,13 +5474,13 @@
       <x:c r="E54" s="52">
         <x:v>32540</x:v>
       </x:c>
-      <x:c r="F54" s="53" t="n">
+      <x:c r="F54" s="53">
         <x:v>14188</x:v>
       </x:c>
-      <x:c r="G54" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H54" s="53" t="n">
+      <x:c r="G54" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H54" s="53">
         <x:v>14188</x:v>
       </x:c>
     </x:row>
@@ -5497,13 +5497,13 @@
       <x:c r="E55" s="52">
         <x:v>32544</x:v>
       </x:c>
-      <x:c r="F55" s="53" t="n">
+      <x:c r="F55" s="53">
         <x:v>23406</x:v>
       </x:c>
-      <x:c r="G55" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H55" s="53" t="n">
+      <x:c r="G55" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" s="53">
         <x:v>23406</x:v>
       </x:c>
     </x:row>
@@ -5520,13 +5520,13 @@
       <x:c r="E56" s="52">
         <x:v>32548</x:v>
       </x:c>
-      <x:c r="F56" s="53" t="n">
+      <x:c r="F56" s="53">
         <x:v>19293.7</x:v>
       </x:c>
-      <x:c r="G56" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H56" s="53" t="n">
+      <x:c r="G56" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" s="53">
         <x:v>19293.7</x:v>
       </x:c>
     </x:row>
@@ -5543,13 +5543,13 @@
       <x:c r="E57" s="52">
         <x:v>32558</x:v>
       </x:c>
-      <x:c r="F57" s="53" t="n">
+      <x:c r="F57" s="53">
         <x:v>1975</x:v>
       </x:c>
-      <x:c r="G57" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H57" s="53" t="n">
+      <x:c r="G57" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H57" s="53">
         <x:v>1975</x:v>
       </x:c>
     </x:row>
@@ -5566,13 +5566,13 @@
       <x:c r="E58" s="52">
         <x:v>32561</x:v>
       </x:c>
-      <x:c r="F58" s="53" t="n">
+      <x:c r="F58" s="53">
         <x:v>12736</x:v>
       </x:c>
-      <x:c r="G58" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H58" s="53" t="n">
+      <x:c r="G58" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58" s="53">
         <x:v>12736</x:v>
       </x:c>
     </x:row>
@@ -5589,13 +5589,13 @@
       <x:c r="E59" s="52">
         <x:v>32564</x:v>
       </x:c>
-      <x:c r="F59" s="53" t="n">
+      <x:c r="F59" s="53">
         <x:v>2150</x:v>
       </x:c>
-      <x:c r="G59" s="54" t="n">
+      <x:c r="G59" s="54">
         <x:v>8.5</x:v>
       </x:c>
-      <x:c r="H59" s="53" t="n">
+      <x:c r="H59" s="53">
         <x:v>2150</x:v>
       </x:c>
     </x:row>
@@ -5612,13 +5612,13 @@
       <x:c r="E60" s="52">
         <x:v>32568</x:v>
       </x:c>
-      <x:c r="F60" s="53" t="n">
+      <x:c r="F60" s="53">
         <x:v>15355</x:v>
       </x:c>
-      <x:c r="G60" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H60" s="53" t="n">
+      <x:c r="G60" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H60" s="53">
         <x:v>15355</x:v>
       </x:c>
     </x:row>
@@ -5635,13 +5635,13 @@
       <x:c r="E61" s="52">
         <x:v>32571</x:v>
       </x:c>
-      <x:c r="F61" s="53" t="n">
+      <x:c r="F61" s="53">
         <x:v>24277.3</x:v>
       </x:c>
-      <x:c r="G61" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H61" s="53" t="n">
+      <x:c r="G61" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="53">
         <x:v>24277.3</x:v>
       </x:c>
     </x:row>
@@ -5658,13 +5658,13 @@
       <x:c r="E62" s="52">
         <x:v>32576</x:v>
       </x:c>
-      <x:c r="F62" s="53" t="n">
+      <x:c r="F62" s="53">
         <x:v>18320</x:v>
       </x:c>
-      <x:c r="G62" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H62" s="53" t="n">
+      <x:c r="G62" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62" s="53">
         <x:v>18320</x:v>
       </x:c>
     </x:row>
@@ -5681,13 +5681,13 @@
       <x:c r="E63" s="52">
         <x:v>32581</x:v>
       </x:c>
-      <x:c r="F63" s="53" t="n">
+      <x:c r="F63" s="53">
         <x:v>61869.3</x:v>
       </x:c>
-      <x:c r="G63" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H63" s="53" t="n">
+      <x:c r="G63" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H63" s="53">
         <x:v>61869.3</x:v>
       </x:c>
     </x:row>
@@ -5704,13 +5704,13 @@
       <x:c r="E64" s="52">
         <x:v>32592</x:v>
       </x:c>
-      <x:c r="F64" s="53" t="n">
+      <x:c r="F64" s="53">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="G64" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H64" s="53" t="n">
+      <x:c r="G64" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H64" s="53">
         <x:v>395</x:v>
       </x:c>
     </x:row>
@@ -5727,13 +5727,13 @@
       <x:c r="E65" s="52">
         <x:v>32593</x:v>
       </x:c>
-      <x:c r="F65" s="53" t="n">
+      <x:c r="F65" s="53">
         <x:v>17814</x:v>
       </x:c>
-      <x:c r="G65" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H65" s="53" t="n">
+      <x:c r="G65" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65" s="53">
         <x:v>17814</x:v>
       </x:c>
     </x:row>
@@ -5750,13 +5750,13 @@
       <x:c r="E66" s="52">
         <x:v>32594</x:v>
       </x:c>
-      <x:c r="F66" s="53" t="n">
+      <x:c r="F66" s="53">
         <x:v>19812</x:v>
       </x:c>
-      <x:c r="G66" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H66" s="53" t="n">
+      <x:c r="G66" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H66" s="53">
         <x:v>19812</x:v>
       </x:c>
     </x:row>
@@ -5773,13 +5773,13 @@
       <x:c r="E67" s="52">
         <x:v>32600</x:v>
       </x:c>
-      <x:c r="F67" s="53" t="n">
+      <x:c r="F67" s="53">
         <x:v>4495</x:v>
       </x:c>
-      <x:c r="G67" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H67" s="53" t="n">
+      <x:c r="G67" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H67" s="53">
         <x:v>4495</x:v>
       </x:c>
     </x:row>
@@ -5796,13 +5796,13 @@
       <x:c r="E68" s="52">
         <x:v>32602</x:v>
       </x:c>
-      <x:c r="F68" s="53" t="n">
+      <x:c r="F68" s="53">
         <x:v>31847</x:v>
       </x:c>
-      <x:c r="G68" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H68" s="53" t="n">
+      <x:c r="G68" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H68" s="53">
         <x:v>31847</x:v>
       </x:c>
     </x:row>
@@ -5819,13 +5819,13 @@
       <x:c r="E69" s="52">
         <x:v>32604</x:v>
       </x:c>
-      <x:c r="F69" s="53" t="n">
+      <x:c r="F69" s="53">
         <x:v>33829.45</x:v>
       </x:c>
-      <x:c r="G69" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H69" s="53" t="n">
+      <x:c r="G69" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H69" s="53">
         <x:v>33829.45</x:v>
       </x:c>
     </x:row>
@@ -5842,13 +5842,13 @@
       <x:c r="E70" s="52">
         <x:v>32606</x:v>
       </x:c>
-      <x:c r="F70" s="53" t="n">
+      <x:c r="F70" s="53">
         <x:v>22354</x:v>
       </x:c>
-      <x:c r="G70" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H70" s="53" t="n">
+      <x:c r="G70" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H70" s="53">
         <x:v>22354</x:v>
       </x:c>
     </x:row>
@@ -5865,13 +5865,13 @@
       <x:c r="E71" s="52">
         <x:v>32608</x:v>
       </x:c>
-      <x:c r="F71" s="53" t="n">
+      <x:c r="F71" s="53">
         <x:v>103041</x:v>
       </x:c>
-      <x:c r="G71" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H71" s="53" t="n">
+      <x:c r="G71" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H71" s="53">
         <x:v>103041</x:v>
       </x:c>
     </x:row>
@@ -5888,13 +5888,13 @@
       <x:c r="E72" s="52">
         <x:v>32610</x:v>
       </x:c>
-      <x:c r="F72" s="53" t="n">
+      <x:c r="F72" s="53">
         <x:v>3596</x:v>
       </x:c>
-      <x:c r="G72" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H72" s="53" t="n">
+      <x:c r="G72" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H72" s="53">
         <x:v>3596</x:v>
       </x:c>
     </x:row>
@@ -5911,13 +5911,13 @@
       <x:c r="E73" s="52">
         <x:v>32614</x:v>
       </x:c>
-      <x:c r="F73" s="53" t="n">
+      <x:c r="F73" s="53">
         <x:v>19414</x:v>
       </x:c>
-      <x:c r="G73" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H73" s="53" t="n">
+      <x:c r="G73" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H73" s="53">
         <x:v>19414</x:v>
       </x:c>
     </x:row>
@@ -5934,13 +5934,13 @@
       <x:c r="E74" s="52">
         <x:v>32618</x:v>
       </x:c>
-      <x:c r="F74" s="53" t="n">
+      <x:c r="F74" s="53">
         <x:v>2195</x:v>
       </x:c>
-      <x:c r="G74" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H74" s="53" t="n">
+      <x:c r="G74" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H74" s="53">
         <x:v>2195</x:v>
       </x:c>
     </x:row>
@@ -5957,13 +5957,13 @@
       <x:c r="E75" s="52">
         <x:v>32620</x:v>
       </x:c>
-      <x:c r="F75" s="53" t="n">
+      <x:c r="F75" s="53">
         <x:v>8560</x:v>
       </x:c>
-      <x:c r="G75" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H75" s="53" t="n">
+      <x:c r="G75" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H75" s="53">
         <x:v>8560</x:v>
       </x:c>
     </x:row>
@@ -5980,13 +5980,13 @@
       <x:c r="E76" s="52">
         <x:v>32624</x:v>
       </x:c>
-      <x:c r="F76" s="53" t="n">
+      <x:c r="F76" s="53">
         <x:v>17781</x:v>
       </x:c>
-      <x:c r="G76" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H76" s="53" t="n">
+      <x:c r="G76" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H76" s="53">
         <x:v>17781</x:v>
       </x:c>
     </x:row>
@@ -6003,13 +6003,13 @@
       <x:c r="E77" s="52">
         <x:v>32629</x:v>
       </x:c>
-      <x:c r="F77" s="53" t="n">
+      <x:c r="F77" s="53">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G77" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H77" s="53" t="n">
+      <x:c r="G77" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H77" s="53">
         <x:v>156</x:v>
       </x:c>
     </x:row>
@@ -6026,13 +6026,13 @@
       <x:c r="E78" s="52">
         <x:v>32630</x:v>
       </x:c>
-      <x:c r="F78" s="53" t="n">
+      <x:c r="F78" s="53">
         <x:v>79116</x:v>
       </x:c>
-      <x:c r="G78" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H78" s="53" t="n">
+      <x:c r="G78" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H78" s="53">
         <x:v>79116</x:v>
       </x:c>
     </x:row>
@@ -6049,13 +6049,13 @@
       <x:c r="E79" s="52">
         <x:v>32632</x:v>
       </x:c>
-      <x:c r="F79" s="53" t="n">
+      <x:c r="F79" s="53">
         <x:v>4445</x:v>
       </x:c>
-      <x:c r="G79" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H79" s="53" t="n">
+      <x:c r="G79" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H79" s="53">
         <x:v>4445</x:v>
       </x:c>
     </x:row>
@@ -6072,13 +6072,13 @@
       <x:c r="E80" s="52">
         <x:v>32634</x:v>
       </x:c>
-      <x:c r="F80" s="53" t="n">
+      <x:c r="F80" s="53">
         <x:v>9634</x:v>
       </x:c>
-      <x:c r="G80" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H80" s="53" t="n">
+      <x:c r="G80" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H80" s="53">
         <x:v>9634</x:v>
       </x:c>
     </x:row>
@@ -6095,13 +6095,13 @@
       <x:c r="E81" s="52">
         <x:v>32636</x:v>
       </x:c>
-      <x:c r="F81" s="53" t="n">
+      <x:c r="F81" s="53">
         <x:v>30566</x:v>
       </x:c>
-      <x:c r="G81" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H81" s="53" t="n">
+      <x:c r="G81" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H81" s="53">
         <x:v>30566</x:v>
       </x:c>
     </x:row>
@@ -6118,13 +6118,13 @@
       <x:c r="E82" s="52">
         <x:v>32638</x:v>
       </x:c>
-      <x:c r="F82" s="53" t="n">
+      <x:c r="F82" s="53">
         <x:v>1416.45</x:v>
       </x:c>
-      <x:c r="G82" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H82" s="53" t="n">
+      <x:c r="G82" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82" s="53">
         <x:v>1416.45</x:v>
       </x:c>
     </x:row>
@@ -6141,13 +6141,13 @@
       <x:c r="E83" s="52">
         <x:v>32638</x:v>
       </x:c>
-      <x:c r="F83" s="53" t="n">
+      <x:c r="F83" s="53">
         <x:v>11164.8</x:v>
       </x:c>
-      <x:c r="G83" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H83" s="53" t="n">
+      <x:c r="G83" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="53">
         <x:v>11164.8</x:v>
       </x:c>
     </x:row>
@@ -6164,13 +6164,13 @@
       <x:c r="E84" s="52">
         <x:v>32640</x:v>
       </x:c>
-      <x:c r="F84" s="53" t="n">
+      <x:c r="F84" s="53">
         <x:v>1185</x:v>
       </x:c>
-      <x:c r="G84" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H84" s="53" t="n">
+      <x:c r="G84" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84" s="53">
         <x:v>1185</x:v>
       </x:c>
     </x:row>
@@ -6187,13 +6187,13 @@
       <x:c r="E85" s="52">
         <x:v>32647</x:v>
       </x:c>
-      <x:c r="F85" s="53" t="n">
+      <x:c r="F85" s="53">
         <x:v>14049.95</x:v>
       </x:c>
-      <x:c r="G85" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H85" s="53" t="n">
+      <x:c r="G85" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H85" s="53">
         <x:v>14049.95</x:v>
       </x:c>
     </x:row>
@@ -6210,13 +6210,13 @@
       <x:c r="E86" s="52">
         <x:v>32649</x:v>
       </x:c>
-      <x:c r="F86" s="53" t="n">
+      <x:c r="F86" s="53">
         <x:v>14045</x:v>
       </x:c>
-      <x:c r="G86" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H86" s="53" t="n">
+      <x:c r="G86" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H86" s="53">
         <x:v>14045</x:v>
       </x:c>
     </x:row>
@@ -6233,13 +6233,13 @@
       <x:c r="E87" s="52">
         <x:v>32651</x:v>
       </x:c>
-      <x:c r="F87" s="53" t="n">
+      <x:c r="F87" s="53">
         <x:v>2706</x:v>
       </x:c>
-      <x:c r="G87" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H87" s="53" t="n">
+      <x:c r="G87" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H87" s="53">
         <x:v>2706</x:v>
       </x:c>
     </x:row>
@@ -6256,13 +6256,13 @@
       <x:c r="E88" s="52">
         <x:v>32654</x:v>
       </x:c>
-      <x:c r="F88" s="53" t="n">
+      <x:c r="F88" s="53">
         <x:v>8507</x:v>
       </x:c>
-      <x:c r="G88" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H88" s="53" t="n">
+      <x:c r="G88" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88" s="53">
         <x:v>8507</x:v>
       </x:c>
     </x:row>
@@ -6279,13 +6279,13 @@
       <x:c r="E89" s="52">
         <x:v>32660</x:v>
       </x:c>
-      <x:c r="F89" s="53" t="n">
+      <x:c r="F89" s="53">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="G89" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H89" s="53" t="n">
+      <x:c r="G89" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H89" s="53">
         <x:v>1950</x:v>
       </x:c>
     </x:row>
@@ -6302,13 +6302,13 @@
       <x:c r="E90" s="52">
         <x:v>32660</x:v>
       </x:c>
-      <x:c r="F90" s="53" t="n">
+      <x:c r="F90" s="53">
         <x:v>76698.75</x:v>
       </x:c>
-      <x:c r="G90" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H90" s="53" t="n">
+      <x:c r="G90" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H90" s="53">
         <x:v>76698.75</x:v>
       </x:c>
     </x:row>
@@ -6325,13 +6325,13 @@
       <x:c r="E91" s="52">
         <x:v>32661</x:v>
       </x:c>
-      <x:c r="F91" s="53" t="n">
+      <x:c r="F91" s="53">
         <x:v>479.8</x:v>
       </x:c>
-      <x:c r="G91" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H91" s="53" t="n">
+      <x:c r="G91" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H91" s="53">
         <x:v>479.8</x:v>
       </x:c>
     </x:row>
@@ -6348,13 +6348,13 @@
       <x:c r="E92" s="52">
         <x:v>32663</x:v>
       </x:c>
-      <x:c r="F92" s="53" t="n">
+      <x:c r="F92" s="53">
         <x:v>4113.75</x:v>
       </x:c>
-      <x:c r="G92" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H92" s="53" t="n">
+      <x:c r="G92" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H92" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6371,13 +6371,13 @@
       <x:c r="E93" s="52">
         <x:v>32665</x:v>
       </x:c>
-      <x:c r="F93" s="53" t="n">
+      <x:c r="F93" s="53">
         <x:v>7531.75</x:v>
       </x:c>
-      <x:c r="G93" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H93" s="53" t="n">
+      <x:c r="G93" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H93" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6394,13 +6394,13 @@
       <x:c r="E94" s="52">
         <x:v>32668</x:v>
       </x:c>
-      <x:c r="F94" s="53" t="n">
+      <x:c r="F94" s="53">
         <x:v>123740</x:v>
       </x:c>
-      <x:c r="G94" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H94" s="53" t="n">
+      <x:c r="G94" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H94" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6417,13 +6417,13 @@
       <x:c r="E95" s="52">
         <x:v>32671</x:v>
       </x:c>
-      <x:c r="F95" s="53" t="n">
+      <x:c r="F95" s="53">
         <x:v>12953.6</x:v>
       </x:c>
-      <x:c r="G95" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H95" s="53" t="n">
+      <x:c r="G95" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H95" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6440,13 +6440,13 @@
       <x:c r="E96" s="52">
         <x:v>32673</x:v>
       </x:c>
-      <x:c r="F96" s="53" t="n">
+      <x:c r="F96" s="53">
         <x:v>472.9</x:v>
       </x:c>
-      <x:c r="G96" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H96" s="53" t="n">
+      <x:c r="G96" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H96" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6463,13 +6463,13 @@
       <x:c r="E97" s="52">
         <x:v>32675</x:v>
       </x:c>
-      <x:c r="F97" s="53" t="n">
+      <x:c r="F97" s="53">
         <x:v>859.95</x:v>
       </x:c>
-      <x:c r="G97" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H97" s="53" t="n">
+      <x:c r="G97" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H97" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6486,13 +6486,13 @@
       <x:c r="E98" s="52">
         <x:v>32679</x:v>
       </x:c>
-      <x:c r="F98" s="53" t="n">
+      <x:c r="F98" s="53">
         <x:v>6094.8</x:v>
       </x:c>
-      <x:c r="G98" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H98" s="53" t="n">
+      <x:c r="G98" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H98" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6509,13 +6509,13 @@
       <x:c r="E99" s="52">
         <x:v>32693</x:v>
       </x:c>
-      <x:c r="F99" s="53" t="n">
+      <x:c r="F99" s="53">
         <x:v>11629.85</x:v>
       </x:c>
-      <x:c r="G99" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H99" s="53" t="n">
+      <x:c r="G99" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H99" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6532,13 +6532,13 @@
       <x:c r="E100" s="52">
         <x:v>33761</x:v>
       </x:c>
-      <x:c r="F100" s="53" t="n">
+      <x:c r="F100" s="53">
         <x:v>2844</x:v>
       </x:c>
-      <x:c r="G100" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H100" s="53" t="n">
+      <x:c r="G100" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H100" s="53">
         <x:v>2844</x:v>
       </x:c>
     </x:row>
@@ -6555,13 +6555,13 @@
       <x:c r="E101" s="52">
         <x:v>33798</x:v>
       </x:c>
-      <x:c r="F101" s="53" t="n">
+      <x:c r="F101" s="53">
         <x:v>39797.7</x:v>
       </x:c>
-      <x:c r="G101" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H101" s="53" t="n">
+      <x:c r="G101" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H101" s="53">
         <x:v>39797.7</x:v>
       </x:c>
     </x:row>
@@ -6578,13 +6578,13 @@
       <x:c r="E102" s="52">
         <x:v>33803</x:v>
       </x:c>
-      <x:c r="F102" s="53" t="n">
+      <x:c r="F102" s="53">
         <x:v>51673.15</x:v>
       </x:c>
-      <x:c r="G102" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H102" s="53" t="n">
+      <x:c r="G102" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H102" s="53">
         <x:v>51673.15</x:v>
       </x:c>
     </x:row>
@@ -6601,13 +6601,13 @@
       <x:c r="E103" s="52">
         <x:v>33806</x:v>
       </x:c>
-      <x:c r="F103" s="53" t="n">
+      <x:c r="F103" s="53">
         <x:v>31219.95</x:v>
       </x:c>
-      <x:c r="G103" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H103" s="53" t="n">
+      <x:c r="G103" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H103" s="53">
         <x:v>31219.95</x:v>
       </x:c>
     </x:row>
@@ -6624,13 +6624,13 @@
       <x:c r="E104" s="52">
         <x:v>33870</x:v>
       </x:c>
-      <x:c r="F104" s="53" t="n">
+      <x:c r="F104" s="53">
         <x:v>3531.8</x:v>
       </x:c>
-      <x:c r="G104" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H104" s="53" t="n">
+      <x:c r="G104" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H104" s="53">
         <x:v>3531.8</x:v>
       </x:c>
     </x:row>
@@ -6647,13 +6647,13 @@
       <x:c r="E105" s="52">
         <x:v>33901</x:v>
       </x:c>
-      <x:c r="F105" s="53" t="n">
+      <x:c r="F105" s="53">
         <x:v>28389</x:v>
       </x:c>
-      <x:c r="G105" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H105" s="53" t="n">
+      <x:c r="G105" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H105" s="53">
         <x:v>28389</x:v>
       </x:c>
     </x:row>
@@ -6670,13 +6670,13 @@
       <x:c r="E106" s="52">
         <x:v>33921</x:v>
       </x:c>
-      <x:c r="F106" s="53" t="n">
+      <x:c r="F106" s="53">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G106" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H106" s="53" t="n">
+      <x:c r="G106" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H106" s="53">
         <x:v>203</x:v>
       </x:c>
     </x:row>
@@ -6693,13 +6693,13 @@
       <x:c r="E107" s="52">
         <x:v>33952</x:v>
       </x:c>
-      <x:c r="F107" s="53" t="n">
+      <x:c r="F107" s="53">
         <x:v>4720.8</x:v>
       </x:c>
-      <x:c r="G107" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H107" s="53" t="n">
+      <x:c r="G107" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H107" s="53">
         <x:v>4720.8</x:v>
       </x:c>
     </x:row>
@@ -6716,13 +6716,13 @@
       <x:c r="E108" s="52">
         <x:v>33971</x:v>
       </x:c>
-      <x:c r="F108" s="53" t="n">
+      <x:c r="F108" s="53">
         <x:v>5565</x:v>
       </x:c>
-      <x:c r="G108" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H108" s="53" t="n">
+      <x:c r="G108" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H108" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6739,13 +6739,13 @@
       <x:c r="E109" s="52">
         <x:v>34012</x:v>
       </x:c>
-      <x:c r="F109" s="53" t="n">
+      <x:c r="F109" s="53">
         <x:v>2514.65</x:v>
       </x:c>
-      <x:c r="G109" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H109" s="53" t="n">
+      <x:c r="G109" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H109" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6762,13 +6762,13 @@
       <x:c r="E110" s="52">
         <x:v>34041</x:v>
       </x:c>
-      <x:c r="F110" s="53" t="n">
+      <x:c r="F110" s="53">
         <x:v>4894.95</x:v>
       </x:c>
-      <x:c r="G110" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H110" s="53" t="n">
+      <x:c r="G110" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H110" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6785,13 +6785,13 @@
       <x:c r="E111" s="52">
         <x:v>34049</x:v>
       </x:c>
-      <x:c r="F111" s="53" t="n">
+      <x:c r="F111" s="53">
         <x:v>23104</x:v>
       </x:c>
-      <x:c r="G111" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H111" s="53" t="n">
+      <x:c r="G111" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H111" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6808,13 +6808,13 @@
       <x:c r="E112" s="52">
         <x:v>34072</x:v>
       </x:c>
-      <x:c r="F112" s="53" t="n">
+      <x:c r="F112" s="53">
         <x:v>6734.85</x:v>
       </x:c>
-      <x:c r="G112" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H112" s="53" t="n">
+      <x:c r="G112" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H112" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -6831,13 +6831,13 @@
       <x:c r="E113" s="52">
         <x:v>34082</x:v>
       </x:c>
-      <x:c r="F113" s="53" t="n">
+      <x:c r="F113" s="53">
         <x:v>21614</x:v>
       </x:c>
-      <x:c r="G113" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H113" s="53" t="n">
+      <x:c r="G113" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H113" s="53">
         <x:v>21614</x:v>
       </x:c>
     </x:row>
@@ -6854,13 +6854,13 @@
       <x:c r="E114" s="52">
         <x:v>34104</x:v>
       </x:c>
-      <x:c r="F114" s="53" t="n">
+      <x:c r="F114" s="53">
         <x:v>14557.95</x:v>
       </x:c>
-      <x:c r="G114" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H114" s="53" t="n">
+      <x:c r="G114" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H114" s="53">
         <x:v>14557.95</x:v>
       </x:c>
     </x:row>
@@ -6877,13 +6877,13 @@
       <x:c r="E115" s="52">
         <x:v>34114</x:v>
       </x:c>
-      <x:c r="F115" s="53" t="n">
+      <x:c r="F115" s="53">
         <x:v>784.9</x:v>
       </x:c>
-      <x:c r="G115" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H115" s="53" t="n">
+      <x:c r="G115" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H115" s="53">
         <x:v>784.9</x:v>
       </x:c>
     </x:row>
@@ -6900,13 +6900,13 @@
       <x:c r="E116" s="52">
         <x:v>34122</x:v>
       </x:c>
-      <x:c r="F116" s="53" t="n">
+      <x:c r="F116" s="53">
         <x:v>820</x:v>
       </x:c>
-      <x:c r="G116" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H116" s="53" t="n">
+      <x:c r="G116" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H116" s="53">
         <x:v>820</x:v>
       </x:c>
     </x:row>
@@ -6923,13 +6923,13 @@
       <x:c r="E117" s="52">
         <x:v>34173</x:v>
       </x:c>
-      <x:c r="F117" s="53" t="n">
+      <x:c r="F117" s="53">
         <x:v>44854</x:v>
       </x:c>
-      <x:c r="G117" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H117" s="53" t="n">
+      <x:c r="G117" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H117" s="53">
         <x:v>44854</x:v>
       </x:c>
     </x:row>
@@ -6946,13 +6946,13 @@
       <x:c r="E118" s="52">
         <x:v>34205</x:v>
       </x:c>
-      <x:c r="F118" s="53" t="n">
+      <x:c r="F118" s="53">
         <x:v>13945</x:v>
       </x:c>
-      <x:c r="G118" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H118" s="53" t="n">
+      <x:c r="G118" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H118" s="53">
         <x:v>13945</x:v>
       </x:c>
     </x:row>
@@ -6969,13 +6969,13 @@
       <x:c r="E119" s="52">
         <x:v>34213</x:v>
       </x:c>
-      <x:c r="F119" s="53" t="n">
+      <x:c r="F119" s="53">
         <x:v>33071</x:v>
       </x:c>
-      <x:c r="G119" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H119" s="53" t="n">
+      <x:c r="G119" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H119" s="53">
         <x:v>33071</x:v>
       </x:c>
     </x:row>
@@ -6992,13 +6992,13 @@
       <x:c r="E120" s="52">
         <x:v>34216</x:v>
       </x:c>
-      <x:c r="F120" s="53" t="n">
+      <x:c r="F120" s="53">
         <x:v>6583.8</x:v>
       </x:c>
-      <x:c r="G120" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H120" s="53" t="n">
+      <x:c r="G120" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H120" s="53">
         <x:v>6583.8</x:v>
       </x:c>
     </x:row>
@@ -7015,13 +7015,13 @@
       <x:c r="E121" s="52">
         <x:v>34243</x:v>
       </x:c>
-      <x:c r="F121" s="53" t="n">
+      <x:c r="F121" s="53">
         <x:v>10107</x:v>
       </x:c>
-      <x:c r="G121" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H121" s="53" t="n">
+      <x:c r="G121" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H121" s="53">
         <x:v>10107</x:v>
       </x:c>
     </x:row>
@@ -7038,13 +7038,13 @@
       <x:c r="E122" s="52">
         <x:v>34244</x:v>
       </x:c>
-      <x:c r="F122" s="53" t="n">
+      <x:c r="F122" s="53">
         <x:v>25071</x:v>
       </x:c>
-      <x:c r="G122" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H122" s="53" t="n">
+      <x:c r="G122" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H122" s="53">
         <x:v>25071</x:v>
       </x:c>
     </x:row>
@@ -7061,13 +7061,13 @@
       <x:c r="E123" s="52">
         <x:v>34250</x:v>
       </x:c>
-      <x:c r="F123" s="53" t="n">
+      <x:c r="F123" s="53">
         <x:v>8294</x:v>
       </x:c>
-      <x:c r="G123" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H123" s="53" t="n">
+      <x:c r="G123" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H123" s="53">
         <x:v>8294</x:v>
       </x:c>
     </x:row>
@@ -7084,13 +7084,13 @@
       <x:c r="E124" s="52">
         <x:v>34261</x:v>
       </x:c>
-      <x:c r="F124" s="53" t="n">
+      <x:c r="F124" s="53">
         <x:v>1004.8</x:v>
       </x:c>
-      <x:c r="G124" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H124" s="53" t="n">
+      <x:c r="G124" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H124" s="53">
         <x:v>1004.8</x:v>
       </x:c>
     </x:row>
@@ -7107,13 +7107,13 @@
       <x:c r="E125" s="52">
         <x:v>34268</x:v>
       </x:c>
-      <x:c r="F125" s="53" t="n">
+      <x:c r="F125" s="53">
         <x:v>6300</x:v>
       </x:c>
-      <x:c r="G125" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H125" s="53" t="n">
+      <x:c r="G125" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H125" s="53">
         <x:v>6300</x:v>
       </x:c>
     </x:row>
@@ -7130,13 +7130,13 @@
       <x:c r="E126" s="52">
         <x:v>34274</x:v>
       </x:c>
-      <x:c r="F126" s="53" t="n">
+      <x:c r="F126" s="53">
         <x:v>11989.2</x:v>
       </x:c>
-      <x:c r="G126" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H126" s="53" t="n">
+      <x:c r="G126" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H126" s="53">
         <x:v>11989.2</x:v>
       </x:c>
     </x:row>
@@ -7153,13 +7153,13 @@
       <x:c r="E127" s="52">
         <x:v>34274</x:v>
       </x:c>
-      <x:c r="F127" s="53" t="n">
+      <x:c r="F127" s="53">
         <x:v>906</x:v>
       </x:c>
-      <x:c r="G127" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H127" s="53" t="n">
+      <x:c r="G127" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H127" s="53">
         <x:v>906</x:v>
       </x:c>
     </x:row>
@@ -7176,13 +7176,13 @@
       <x:c r="E128" s="52">
         <x:v>34275</x:v>
       </x:c>
-      <x:c r="F128" s="53" t="n">
+      <x:c r="F128" s="53">
         <x:v>2419</x:v>
       </x:c>
-      <x:c r="G128" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H128" s="53" t="n">
+      <x:c r="G128" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H128" s="53">
         <x:v>2419</x:v>
       </x:c>
     </x:row>
@@ -7199,13 +7199,13 @@
       <x:c r="E129" s="52">
         <x:v>34287</x:v>
       </x:c>
-      <x:c r="F129" s="53" t="n">
+      <x:c r="F129" s="53">
         <x:v>6675.95</x:v>
       </x:c>
-      <x:c r="G129" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H129" s="53" t="n">
+      <x:c r="G129" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H129" s="53">
         <x:v>6675.95</x:v>
       </x:c>
     </x:row>
@@ -7222,13 +7222,13 @@
       <x:c r="E130" s="52">
         <x:v>34300</x:v>
       </x:c>
-      <x:c r="F130" s="53" t="n">
+      <x:c r="F130" s="53">
         <x:v>2971</x:v>
       </x:c>
-      <x:c r="G130" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H130" s="53" t="n">
+      <x:c r="G130" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H130" s="53">
         <x:v>2971</x:v>
       </x:c>
     </x:row>
@@ -7245,13 +7245,13 @@
       <x:c r="E131" s="52">
         <x:v>34300</x:v>
       </x:c>
-      <x:c r="F131" s="53" t="n">
+      <x:c r="F131" s="53">
         <x:v>6785.4</x:v>
       </x:c>
-      <x:c r="G131" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H131" s="53" t="n">
+      <x:c r="G131" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H131" s="53">
         <x:v>6785.4</x:v>
       </x:c>
     </x:row>
@@ -7268,13 +7268,13 @@
       <x:c r="E132" s="52">
         <x:v>34304</x:v>
       </x:c>
-      <x:c r="F132" s="53" t="n">
+      <x:c r="F132" s="53">
         <x:v>47710.75</x:v>
       </x:c>
-      <x:c r="G132" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H132" s="53" t="n">
+      <x:c r="G132" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H132" s="53">
         <x:v>47710.75</x:v>
       </x:c>
     </x:row>
@@ -7291,13 +7291,13 @@
       <x:c r="E133" s="52">
         <x:v>34315</x:v>
       </x:c>
-      <x:c r="F133" s="53" t="n">
+      <x:c r="F133" s="53">
         <x:v>1240</x:v>
       </x:c>
-      <x:c r="G133" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H133" s="53" t="n">
+      <x:c r="G133" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H133" s="53">
         <x:v>1240</x:v>
       </x:c>
     </x:row>
@@ -7314,13 +7314,13 @@
       <x:c r="E134" s="52">
         <x:v>34320</x:v>
       </x:c>
-      <x:c r="F134" s="53" t="n">
+      <x:c r="F134" s="53">
         <x:v>1846</x:v>
       </x:c>
-      <x:c r="G134" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H134" s="53" t="n">
+      <x:c r="G134" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H134" s="53">
         <x:v>1846</x:v>
       </x:c>
     </x:row>
@@ -7337,13 +7337,13 @@
       <x:c r="E135" s="52">
         <x:v>34328</x:v>
       </x:c>
-      <x:c r="F135" s="53" t="n">
+      <x:c r="F135" s="53">
         <x:v>3546</x:v>
       </x:c>
-      <x:c r="G135" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H135" s="53" t="n">
+      <x:c r="G135" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H135" s="53">
         <x:v>3546</x:v>
       </x:c>
     </x:row>
@@ -7360,13 +7360,13 @@
       <x:c r="E136" s="52">
         <x:v>34335</x:v>
       </x:c>
-      <x:c r="F136" s="53" t="n">
+      <x:c r="F136" s="53">
         <x:v>3087</x:v>
       </x:c>
-      <x:c r="G136" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H136" s="53" t="n">
+      <x:c r="G136" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H136" s="53">
         <x:v>3087</x:v>
       </x:c>
     </x:row>
@@ -7383,13 +7383,13 @@
       <x:c r="E137" s="52">
         <x:v>34343</x:v>
       </x:c>
-      <x:c r="F137" s="53" t="n">
+      <x:c r="F137" s="53">
         <x:v>10054</x:v>
       </x:c>
-      <x:c r="G137" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H137" s="53" t="n">
+      <x:c r="G137" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H137" s="53">
         <x:v>10054</x:v>
       </x:c>
     </x:row>
@@ -7406,13 +7406,13 @@
       <x:c r="E138" s="52">
         <x:v>34351</x:v>
       </x:c>
-      <x:c r="F138" s="53" t="n">
+      <x:c r="F138" s="53">
         <x:v>4229.8</x:v>
       </x:c>
-      <x:c r="G138" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H138" s="53" t="n">
+      <x:c r="G138" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H138" s="53">
         <x:v>4229.8</x:v>
       </x:c>
     </x:row>
@@ -7429,13 +7429,13 @@
       <x:c r="E139" s="52">
         <x:v>34378</x:v>
       </x:c>
-      <x:c r="F139" s="53" t="n">
+      <x:c r="F139" s="53">
         <x:v>15052</x:v>
       </x:c>
-      <x:c r="G139" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H139" s="53" t="n">
+      <x:c r="G139" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H139" s="53">
         <x:v>15052</x:v>
       </x:c>
     </x:row>
@@ -7452,13 +7452,13 @@
       <x:c r="E140" s="52">
         <x:v>34396</x:v>
       </x:c>
-      <x:c r="F140" s="53" t="n">
+      <x:c r="F140" s="53">
         <x:v>5011</x:v>
       </x:c>
-      <x:c r="G140" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H140" s="53" t="n">
+      <x:c r="G140" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H140" s="53">
         <x:v>5011</x:v>
       </x:c>
     </x:row>
@@ -7475,13 +7475,13 @@
       <x:c r="E141" s="52">
         <x:v>34407</x:v>
       </x:c>
-      <x:c r="F141" s="53" t="n">
+      <x:c r="F141" s="53">
         <x:v>12900.75</x:v>
       </x:c>
-      <x:c r="G141" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H141" s="53" t="n">
+      <x:c r="G141" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H141" s="53">
         <x:v>12900.75</x:v>
       </x:c>
     </x:row>
@@ -7498,13 +7498,13 @@
       <x:c r="E142" s="52">
         <x:v>34418</x:v>
       </x:c>
-      <x:c r="F142" s="53" t="n">
+      <x:c r="F142" s="53">
         <x:v>7671.9</x:v>
       </x:c>
-      <x:c r="G142" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H142" s="53" t="n">
+      <x:c r="G142" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H142" s="53">
         <x:v>7671.9</x:v>
       </x:c>
     </x:row>
@@ -7521,13 +7521,13 @@
       <x:c r="E143" s="52">
         <x:v>34431</x:v>
       </x:c>
-      <x:c r="F143" s="53" t="n">
+      <x:c r="F143" s="53">
         <x:v>97698.6</x:v>
       </x:c>
-      <x:c r="G143" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H143" s="53" t="n">
+      <x:c r="G143" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H143" s="53">
         <x:v>97698.6</x:v>
       </x:c>
     </x:row>
@@ -7544,13 +7544,13 @@
       <x:c r="E144" s="52">
         <x:v>34440</x:v>
       </x:c>
-      <x:c r="F144" s="53" t="n">
+      <x:c r="F144" s="53">
         <x:v>3860.85</x:v>
       </x:c>
-      <x:c r="G144" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H144" s="53" t="n">
+      <x:c r="G144" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H144" s="53">
         <x:v>3860.85</x:v>
       </x:c>
     </x:row>
@@ -7567,13 +7567,13 @@
       <x:c r="E145" s="52">
         <x:v>34455</x:v>
       </x:c>
-      <x:c r="F145" s="53" t="n">
+      <x:c r="F145" s="53">
         <x:v>13226.8</x:v>
       </x:c>
-      <x:c r="G145" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H145" s="53" t="n">
+      <x:c r="G145" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H145" s="53">
         <x:v>13226.8</x:v>
       </x:c>
     </x:row>
@@ -7590,13 +7590,13 @@
       <x:c r="E146" s="52">
         <x:v>34459</x:v>
       </x:c>
-      <x:c r="F146" s="53" t="n">
+      <x:c r="F146" s="53">
         <x:v>13935.95</x:v>
       </x:c>
-      <x:c r="G146" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H146" s="53" t="n">
+      <x:c r="G146" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H146" s="53">
         <x:v>13935.95</x:v>
       </x:c>
     </x:row>
@@ -7613,13 +7613,13 @@
       <x:c r="E147" s="52">
         <x:v>34463</x:v>
       </x:c>
-      <x:c r="F147" s="53" t="n">
+      <x:c r="F147" s="53">
         <x:v>12367</x:v>
       </x:c>
-      <x:c r="G147" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H147" s="53" t="n">
+      <x:c r="G147" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H147" s="53">
         <x:v>12367</x:v>
       </x:c>
     </x:row>
@@ -7636,13 +7636,13 @@
       <x:c r="E148" s="52">
         <x:v>34476</x:v>
       </x:c>
-      <x:c r="F148" s="53" t="n">
+      <x:c r="F148" s="53">
         <x:v>9793.55</x:v>
       </x:c>
-      <x:c r="G148" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H148" s="53" t="n">
+      <x:c r="G148" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H148" s="53">
         <x:v>9793.55</x:v>
       </x:c>
     </x:row>
@@ -7659,13 +7659,13 @@
       <x:c r="E149" s="52">
         <x:v>34486</x:v>
       </x:c>
-      <x:c r="F149" s="53" t="n">
+      <x:c r="F149" s="53">
         <x:v>2206.85</x:v>
       </x:c>
-      <x:c r="G149" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H149" s="53" t="n">
+      <x:c r="G149" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H149" s="53">
         <x:v>2206.85</x:v>
       </x:c>
     </x:row>
@@ -7682,13 +7682,13 @@
       <x:c r="E150" s="52">
         <x:v>34489</x:v>
       </x:c>
-      <x:c r="F150" s="53" t="n">
+      <x:c r="F150" s="53">
         <x:v>102453.6</x:v>
       </x:c>
-      <x:c r="G150" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H150" s="53" t="n">
+      <x:c r="G150" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H150" s="53">
         <x:v>102453.6</x:v>
       </x:c>
     </x:row>
@@ -7705,13 +7705,13 @@
       <x:c r="E151" s="52">
         <x:v>34494</x:v>
       </x:c>
-      <x:c r="F151" s="53" t="n">
+      <x:c r="F151" s="53">
         <x:v>3153</x:v>
       </x:c>
-      <x:c r="G151" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H151" s="53" t="n">
+      <x:c r="G151" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H151" s="53">
         <x:v>3153</x:v>
       </x:c>
     </x:row>
@@ -7728,13 +7728,13 @@
       <x:c r="E152" s="52">
         <x:v>34499</x:v>
       </x:c>
-      <x:c r="F152" s="53" t="n">
+      <x:c r="F152" s="53">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="G152" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H152" s="53" t="n">
+      <x:c r="G152" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H152" s="53">
         <x:v>342</x:v>
       </x:c>
     </x:row>
@@ -7751,13 +7751,13 @@
       <x:c r="E153" s="52">
         <x:v>34511</x:v>
       </x:c>
-      <x:c r="F153" s="53" t="n">
+      <x:c r="F153" s="53">
         <x:v>2692.85</x:v>
       </x:c>
-      <x:c r="G153" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H153" s="53" t="n">
+      <x:c r="G153" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H153" s="53">
         <x:v>2692.85</x:v>
       </x:c>
     </x:row>
@@ -7774,13 +7774,13 @@
       <x:c r="E154" s="52">
         <x:v>34516</x:v>
       </x:c>
-      <x:c r="F154" s="53" t="n">
+      <x:c r="F154" s="53">
         <x:v>28862</x:v>
       </x:c>
-      <x:c r="G154" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H154" s="53" t="n">
+      <x:c r="G154" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H154" s="53">
         <x:v>28862</x:v>
       </x:c>
     </x:row>
@@ -7797,13 +7797,13 @@
       <x:c r="E155" s="52">
         <x:v>34519</x:v>
       </x:c>
-      <x:c r="F155" s="53" t="n">
+      <x:c r="F155" s="53">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G155" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H155" s="53" t="n">
+      <x:c r="G155" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H155" s="53">
         <x:v>104</x:v>
       </x:c>
     </x:row>
@@ -7820,13 +7820,13 @@
       <x:c r="E156" s="52">
         <x:v>34521</x:v>
       </x:c>
-      <x:c r="F156" s="53" t="n">
+      <x:c r="F156" s="53">
         <x:v>9471.95</x:v>
       </x:c>
-      <x:c r="G156" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H156" s="53" t="n">
+      <x:c r="G156" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H156" s="53">
         <x:v>9471.95</x:v>
       </x:c>
     </x:row>
@@ -7843,13 +7843,13 @@
       <x:c r="E157" s="52">
         <x:v>34523</x:v>
       </x:c>
-      <x:c r="F157" s="53" t="n">
+      <x:c r="F157" s="53">
         <x:v>5654.8</x:v>
       </x:c>
-      <x:c r="G157" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H157" s="53" t="n">
+      <x:c r="G157" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H157" s="53">
         <x:v>5654.8</x:v>
       </x:c>
     </x:row>
@@ -7866,13 +7866,13 @@
       <x:c r="E158" s="52">
         <x:v>34525</x:v>
       </x:c>
-      <x:c r="F158" s="53" t="n">
+      <x:c r="F158" s="53">
         <x:v>2356.9</x:v>
       </x:c>
-      <x:c r="G158" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H158" s="53" t="n">
+      <x:c r="G158" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H158" s="53">
         <x:v>2356.9</x:v>
       </x:c>
     </x:row>
@@ -7889,13 +7889,13 @@
       <x:c r="E159" s="52">
         <x:v>34531</x:v>
       </x:c>
-      <x:c r="F159" s="53" t="n">
+      <x:c r="F159" s="53">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G159" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H159" s="53" t="n">
+      <x:c r="G159" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H159" s="53">
         <x:v>54</x:v>
       </x:c>
     </x:row>
@@ -7912,13 +7912,13 @@
       <x:c r="E160" s="52">
         <x:v>34537</x:v>
       </x:c>
-      <x:c r="F160" s="53" t="n">
+      <x:c r="F160" s="53">
         <x:v>13814.05</x:v>
       </x:c>
-      <x:c r="G160" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H160" s="53" t="n">
+      <x:c r="G160" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H160" s="53">
         <x:v>13814.05</x:v>
       </x:c>
     </x:row>
@@ -7935,13 +7935,13 @@
       <x:c r="E161" s="52">
         <x:v>34541</x:v>
       </x:c>
-      <x:c r="F161" s="53" t="n">
+      <x:c r="F161" s="53">
         <x:v>4178.85</x:v>
       </x:c>
-      <x:c r="G161" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H161" s="53" t="n">
+      <x:c r="G161" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H161" s="53">
         <x:v>4178.85</x:v>
       </x:c>
     </x:row>
@@ -7958,13 +7958,13 @@
       <x:c r="E162" s="52">
         <x:v>34548</x:v>
       </x:c>
-      <x:c r="F162" s="53" t="n">
+      <x:c r="F162" s="53">
         <x:v>5511.75</x:v>
       </x:c>
-      <x:c r="G162" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H162" s="53" t="n">
+      <x:c r="G162" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H162" s="53">
         <x:v>5511.75</x:v>
       </x:c>
     </x:row>
@@ -7981,13 +7981,13 @@
       <x:c r="E163" s="52">
         <x:v>34552</x:v>
       </x:c>
-      <x:c r="F163" s="53" t="n">
+      <x:c r="F163" s="53">
         <x:v>3640</x:v>
       </x:c>
-      <x:c r="G163" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H163" s="53" t="n">
+      <x:c r="G163" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H163" s="53">
         <x:v>3640</x:v>
       </x:c>
     </x:row>
@@ -8004,13 +8004,13 @@
       <x:c r="E164" s="52">
         <x:v>34556</x:v>
       </x:c>
-      <x:c r="F164" s="53" t="n">
+      <x:c r="F164" s="53">
         <x:v>3650</x:v>
       </x:c>
-      <x:c r="G164" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H164" s="53" t="n">
+      <x:c r="G164" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H164" s="53">
         <x:v>3650</x:v>
       </x:c>
     </x:row>
@@ -8027,13 +8027,13 @@
       <x:c r="E165" s="52">
         <x:v>34583</x:v>
       </x:c>
-      <x:c r="F165" s="53" t="n">
+      <x:c r="F165" s="53">
         <x:v>7868</x:v>
       </x:c>
-      <x:c r="G165" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H165" s="53" t="n">
+      <x:c r="G165" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H165" s="53">
         <x:v>7868</x:v>
       </x:c>
     </x:row>
@@ -8050,13 +8050,13 @@
       <x:c r="E166" s="52">
         <x:v>34585</x:v>
       </x:c>
-      <x:c r="F166" s="53" t="n">
+      <x:c r="F166" s="53">
         <x:v>5983</x:v>
       </x:c>
-      <x:c r="G166" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H166" s="53" t="n">
+      <x:c r="G166" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H166" s="53">
         <x:v>5983</x:v>
       </x:c>
     </x:row>
@@ -8073,13 +8073,13 @@
       <x:c r="E167" s="52">
         <x:v>34589</x:v>
       </x:c>
-      <x:c r="F167" s="53" t="n">
+      <x:c r="F167" s="53">
         <x:v>6731</x:v>
       </x:c>
-      <x:c r="G167" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H167" s="53" t="n">
+      <x:c r="G167" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H167" s="53">
         <x:v>6731</x:v>
       </x:c>
     </x:row>
@@ -8096,13 +8096,13 @@
       <x:c r="E168" s="52">
         <x:v>34591</x:v>
       </x:c>
-      <x:c r="F168" s="53" t="n">
+      <x:c r="F168" s="53">
         <x:v>72089.9</x:v>
       </x:c>
-      <x:c r="G168" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H168" s="53" t="n">
+      <x:c r="G168" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H168" s="53">
         <x:v>72089.9</x:v>
       </x:c>
     </x:row>
@@ -8119,13 +8119,13 @@
       <x:c r="E169" s="52">
         <x:v>34593</x:v>
       </x:c>
-      <x:c r="F169" s="53" t="n">
+      <x:c r="F169" s="53">
         <x:v>716</x:v>
       </x:c>
-      <x:c r="G169" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H169" s="53" t="n">
+      <x:c r="G169" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H169" s="53">
         <x:v>716</x:v>
       </x:c>
     </x:row>
@@ -8142,13 +8142,13 @@
       <x:c r="E170" s="52">
         <x:v>34597</x:v>
       </x:c>
-      <x:c r="F170" s="53" t="n">
+      <x:c r="F170" s="53">
         <x:v>1827</x:v>
       </x:c>
-      <x:c r="G170" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H170" s="53" t="n">
+      <x:c r="G170" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H170" s="53">
         <x:v>1827</x:v>
       </x:c>
     </x:row>
@@ -8165,13 +8165,13 @@
       <x:c r="E171" s="52">
         <x:v>34611</x:v>
       </x:c>
-      <x:c r="F171" s="53" t="n">
+      <x:c r="F171" s="53">
         <x:v>7990</x:v>
       </x:c>
-      <x:c r="G171" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H171" s="53" t="n">
+      <x:c r="G171" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H171" s="53">
         <x:v>7990</x:v>
       </x:c>
     </x:row>
@@ -8188,13 +8188,13 @@
       <x:c r="E172" s="52">
         <x:v>34613</x:v>
       </x:c>
-      <x:c r="F172" s="53" t="n">
+      <x:c r="F172" s="53">
         <x:v>4205</x:v>
       </x:c>
-      <x:c r="G172" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H172" s="53" t="n">
+      <x:c r="G172" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H172" s="53">
         <x:v>4205</x:v>
       </x:c>
     </x:row>
@@ -8211,13 +8211,13 @@
       <x:c r="E173" s="52">
         <x:v>34625</x:v>
       </x:c>
-      <x:c r="F173" s="53" t="n">
+      <x:c r="F173" s="53">
         <x:v>10263.75</x:v>
       </x:c>
-      <x:c r="G173" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H173" s="53" t="n">
+      <x:c r="G173" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H173" s="53">
         <x:v>10263.75</x:v>
       </x:c>
     </x:row>
@@ -8234,13 +8234,13 @@
       <x:c r="E174" s="52">
         <x:v>34628</x:v>
       </x:c>
-      <x:c r="F174" s="53" t="n">
+      <x:c r="F174" s="53">
         <x:v>4029.55</x:v>
       </x:c>
-      <x:c r="G174" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H174" s="53" t="n">
+      <x:c r="G174" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H174" s="53">
         <x:v>4029.55</x:v>
       </x:c>
     </x:row>
@@ -8257,13 +8257,13 @@
       <x:c r="E175" s="52">
         <x:v>34649</x:v>
       </x:c>
-      <x:c r="F175" s="53" t="n">
+      <x:c r="F175" s="53">
         <x:v>12949.7</x:v>
       </x:c>
-      <x:c r="G175" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H175" s="53" t="n">
+      <x:c r="G175" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H175" s="53">
         <x:v>12949.7</x:v>
       </x:c>
     </x:row>
@@ -8280,13 +8280,13 @@
       <x:c r="E176" s="52">
         <x:v>34650</x:v>
       </x:c>
-      <x:c r="F176" s="53" t="n">
+      <x:c r="F176" s="53">
         <x:v>20711.9</x:v>
       </x:c>
-      <x:c r="G176" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H176" s="53" t="n">
+      <x:c r="G176" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H176" s="53">
         <x:v>20711.9</x:v>
       </x:c>
     </x:row>
@@ -8303,13 +8303,13 @@
       <x:c r="E177" s="52">
         <x:v>34652</x:v>
       </x:c>
-      <x:c r="F177" s="53" t="n">
+      <x:c r="F177" s="53">
         <x:v>3975.75</x:v>
       </x:c>
-      <x:c r="G177" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H177" s="53" t="n">
+      <x:c r="G177" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H177" s="53">
         <x:v>3975.75</x:v>
       </x:c>
     </x:row>
@@ -8326,13 +8326,13 @@
       <x:c r="E178" s="52">
         <x:v>34654</x:v>
       </x:c>
-      <x:c r="F178" s="53" t="n">
+      <x:c r="F178" s="53">
         <x:v>8305.95</x:v>
       </x:c>
-      <x:c r="G178" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H178" s="53" t="n">
+      <x:c r="G178" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H178" s="53">
         <x:v>8305.95</x:v>
       </x:c>
     </x:row>
@@ -8349,13 +8349,13 @@
       <x:c r="E179" s="52">
         <x:v>34660</x:v>
       </x:c>
-      <x:c r="F179" s="53" t="n">
+      <x:c r="F179" s="53">
         <x:v>51730.8</x:v>
       </x:c>
-      <x:c r="G179" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H179" s="53" t="n">
+      <x:c r="G179" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H179" s="53">
         <x:v>51730.8</x:v>
       </x:c>
     </x:row>
@@ -8372,13 +8372,13 @@
       <x:c r="E180" s="52">
         <x:v>34661</x:v>
       </x:c>
-      <x:c r="F180" s="53" t="n">
+      <x:c r="F180" s="53">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="G180" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H180" s="53" t="n">
+      <x:c r="G180" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H180" s="53">
         <x:v>2099</x:v>
       </x:c>
     </x:row>
@@ -8395,13 +8395,13 @@
       <x:c r="E181" s="52">
         <x:v>34662</x:v>
       </x:c>
-      <x:c r="F181" s="53" t="n">
+      <x:c r="F181" s="53">
         <x:v>45160.1</x:v>
       </x:c>
-      <x:c r="G181" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H181" s="53" t="n">
+      <x:c r="G181" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H181" s="53">
         <x:v>45160.1</x:v>
       </x:c>
     </x:row>
@@ -8418,13 +8418,13 @@
       <x:c r="E182" s="52">
         <x:v>34664</x:v>
       </x:c>
-      <x:c r="F182" s="53" t="n">
+      <x:c r="F182" s="53">
         <x:v>4774.85</x:v>
       </x:c>
-      <x:c r="G182" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H182" s="53" t="n">
+      <x:c r="G182" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H182" s="53">
         <x:v>4774.85</x:v>
       </x:c>
     </x:row>
@@ -8441,13 +8441,13 @@
       <x:c r="E183" s="52">
         <x:v>34677</x:v>
       </x:c>
-      <x:c r="F183" s="53" t="n">
+      <x:c r="F183" s="53">
         <x:v>64115.75</x:v>
       </x:c>
-      <x:c r="G183" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H183" s="53" t="n">
+      <x:c r="G183" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H183" s="53">
         <x:v>64115.75</x:v>
       </x:c>
     </x:row>
@@ -8464,13 +8464,13 @@
       <x:c r="E184" s="52">
         <x:v>34678</x:v>
       </x:c>
-      <x:c r="F184" s="53" t="n">
+      <x:c r="F184" s="53">
         <x:v>2577.85</x:v>
       </x:c>
-      <x:c r="G184" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H184" s="53" t="n">
+      <x:c r="G184" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H184" s="53">
         <x:v>2577.85</x:v>
       </x:c>
     </x:row>
@@ -8487,13 +8487,13 @@
       <x:c r="E185" s="52">
         <x:v>34679</x:v>
       </x:c>
-      <x:c r="F185" s="53" t="n">
+      <x:c r="F185" s="53">
         <x:v>1999</x:v>
       </x:c>
-      <x:c r="G185" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H185" s="53" t="n">
+      <x:c r="G185" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H185" s="53">
         <x:v>1999</x:v>
       </x:c>
     </x:row>
@@ -8510,13 +8510,13 @@
       <x:c r="E186" s="52">
         <x:v>34682</x:v>
       </x:c>
-      <x:c r="F186" s="53" t="n">
+      <x:c r="F186" s="53">
         <x:v>158922.65</x:v>
       </x:c>
-      <x:c r="G186" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H186" s="53" t="n">
+      <x:c r="G186" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H186" s="53">
         <x:v>158922.65</x:v>
       </x:c>
     </x:row>
@@ -8533,13 +8533,13 @@
       <x:c r="E187" s="52">
         <x:v>34683</x:v>
       </x:c>
-      <x:c r="F187" s="53" t="n">
+      <x:c r="F187" s="53">
         <x:v>6935</x:v>
       </x:c>
-      <x:c r="G187" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H187" s="53" t="n">
+      <x:c r="G187" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H187" s="53">
         <x:v>6935</x:v>
       </x:c>
     </x:row>
@@ -8556,13 +8556,13 @@
       <x:c r="E188" s="52">
         <x:v>34684</x:v>
       </x:c>
-      <x:c r="F188" s="53" t="n">
+      <x:c r="F188" s="53">
         <x:v>1400</x:v>
       </x:c>
-      <x:c r="G188" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H188" s="53" t="n">
+      <x:c r="G188" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H188" s="53">
         <x:v>1400</x:v>
       </x:c>
     </x:row>
@@ -8579,13 +8579,13 @@
       <x:c r="E189" s="52">
         <x:v>34688</x:v>
       </x:c>
-      <x:c r="F189" s="53" t="n">
+      <x:c r="F189" s="53">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="G189" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H189" s="53" t="n">
+      <x:c r="G189" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H189" s="53">
         <x:v>304</x:v>
       </x:c>
     </x:row>
@@ -8602,13 +8602,13 @@
       <x:c r="E190" s="52">
         <x:v>34690</x:v>
       </x:c>
-      <x:c r="F190" s="53" t="n">
+      <x:c r="F190" s="53">
         <x:v>16939.5</x:v>
       </x:c>
-      <x:c r="G190" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H190" s="53" t="n">
+      <x:c r="G190" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H190" s="53">
         <x:v>16939.5</x:v>
       </x:c>
     </x:row>
@@ -8625,13 +8625,13 @@
       <x:c r="E191" s="52">
         <x:v>34691</x:v>
       </x:c>
-      <x:c r="F191" s="53" t="n">
+      <x:c r="F191" s="53">
         <x:v>11568</x:v>
       </x:c>
-      <x:c r="G191" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H191" s="53" t="n">
+      <x:c r="G191" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H191" s="53">
         <x:v>11568</x:v>
       </x:c>
     </x:row>
@@ -8648,13 +8648,13 @@
       <x:c r="E192" s="52">
         <x:v>34694</x:v>
       </x:c>
-      <x:c r="F192" s="53" t="n">
+      <x:c r="F192" s="53">
         <x:v>4317.75</x:v>
       </x:c>
-      <x:c r="G192" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H192" s="53" t="n">
+      <x:c r="G192" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H192" s="53">
         <x:v>4317.75</x:v>
       </x:c>
     </x:row>
@@ -8671,13 +8671,13 @@
       <x:c r="E193" s="52">
         <x:v>34698</x:v>
       </x:c>
-      <x:c r="F193" s="53" t="n">
+      <x:c r="F193" s="53">
         <x:v>7134</x:v>
       </x:c>
-      <x:c r="G193" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H193" s="53" t="n">
+      <x:c r="G193" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H193" s="53">
         <x:v>7134</x:v>
       </x:c>
     </x:row>
@@ -8694,13 +8694,13 @@
       <x:c r="E194" s="52">
         <x:v>34700</x:v>
       </x:c>
-      <x:c r="F194" s="53" t="n">
+      <x:c r="F194" s="53">
         <x:v>7986.9</x:v>
       </x:c>
-      <x:c r="G194" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H194" s="53" t="n">
+      <x:c r="G194" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H194" s="53">
         <x:v>7986.9</x:v>
       </x:c>
     </x:row>
@@ -8717,13 +8717,13 @@
       <x:c r="E195" s="52">
         <x:v>34703</x:v>
       </x:c>
-      <x:c r="F195" s="53" t="n">
+      <x:c r="F195" s="53">
         <x:v>3304.85</x:v>
       </x:c>
-      <x:c r="G195" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H195" s="53" t="n">
+      <x:c r="G195" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H195" s="53">
         <x:v>3304.85</x:v>
       </x:c>
     </x:row>
@@ -8740,13 +8740,13 @@
       <x:c r="E196" s="52">
         <x:v>34705</x:v>
       </x:c>
-      <x:c r="F196" s="53" t="n">
+      <x:c r="F196" s="53">
         <x:v>17917</x:v>
       </x:c>
-      <x:c r="G196" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H196" s="53" t="n">
+      <x:c r="G196" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H196" s="53">
         <x:v>17917</x:v>
       </x:c>
     </x:row>
@@ -8763,13 +8763,13 @@
       <x:c r="E197" s="52">
         <x:v>34707</x:v>
       </x:c>
-      <x:c r="F197" s="53" t="n">
+      <x:c r="F197" s="53">
         <x:v>7423.35</x:v>
       </x:c>
-      <x:c r="G197" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H197" s="53" t="n">
+      <x:c r="G197" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H197" s="53">
         <x:v>7423.35</x:v>
       </x:c>
     </x:row>
@@ -8786,13 +8786,13 @@
       <x:c r="E198" s="52">
         <x:v>34708</x:v>
       </x:c>
-      <x:c r="F198" s="53" t="n">
+      <x:c r="F198" s="53">
         <x:v>9897</x:v>
       </x:c>
-      <x:c r="G198" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H198" s="53" t="n">
+      <x:c r="G198" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H198" s="53">
         <x:v>9897</x:v>
       </x:c>
     </x:row>
@@ -8809,13 +8809,13 @@
       <x:c r="E199" s="52">
         <x:v>34709</x:v>
       </x:c>
-      <x:c r="F199" s="53" t="n">
+      <x:c r="F199" s="53">
         <x:v>52729.25</x:v>
       </x:c>
-      <x:c r="G199" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H199" s="53" t="n">
+      <x:c r="G199" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H199" s="53">
         <x:v>52729.25</x:v>
       </x:c>
     </x:row>
@@ -8832,13 +8832,13 @@
       <x:c r="E200" s="52">
         <x:v>34715</x:v>
       </x:c>
-      <x:c r="F200" s="53" t="n">
+      <x:c r="F200" s="53">
         <x:v>24485</x:v>
       </x:c>
-      <x:c r="G200" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H200" s="53" t="n">
+      <x:c r="G200" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H200" s="53">
         <x:v>24485</x:v>
       </x:c>
     </x:row>
@@ -8855,13 +8855,13 @@
       <x:c r="E201" s="52">
         <x:v>34719</x:v>
       </x:c>
-      <x:c r="F201" s="53" t="n">
+      <x:c r="F201" s="53">
         <x:v>3065</x:v>
       </x:c>
-      <x:c r="G201" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H201" s="53" t="n">
+      <x:c r="G201" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H201" s="53">
         <x:v>3065</x:v>
       </x:c>
     </x:row>
@@ -8878,13 +8878,13 @@
       <x:c r="E202" s="52">
         <x:v>34721</x:v>
       </x:c>
-      <x:c r="F202" s="53" t="n">
+      <x:c r="F202" s="53">
         <x:v>465</x:v>
       </x:c>
-      <x:c r="G202" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H202" s="53" t="n">
+      <x:c r="G202" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H202" s="53">
         <x:v>465</x:v>
       </x:c>
     </x:row>
@@ -8901,13 +8901,13 @@
       <x:c r="E203" s="52">
         <x:v>34725</x:v>
       </x:c>
-      <x:c r="F203" s="53" t="n">
+      <x:c r="F203" s="53">
         <x:v>5037.1</x:v>
       </x:c>
-      <x:c r="G203" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H203" s="53" t="n">
+      <x:c r="G203" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H203" s="53">
         <x:v>5037.1</x:v>
       </x:c>
     </x:row>
@@ -8924,13 +8924,13 @@
       <x:c r="E204" s="52">
         <x:v>34731</x:v>
       </x:c>
-      <x:c r="F204" s="53" t="n">
+      <x:c r="F204" s="53">
         <x:v>7572</x:v>
       </x:c>
-      <x:c r="G204" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H204" s="53" t="n">
+      <x:c r="G204" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H204" s="53">
         <x:v>7572</x:v>
       </x:c>
     </x:row>
@@ -8947,13 +8947,13 @@
       <x:c r="E205" s="52">
         <x:v>34732</x:v>
       </x:c>
-      <x:c r="F205" s="53" t="n">
+      <x:c r="F205" s="53">
         <x:v>8939.6</x:v>
       </x:c>
-      <x:c r="G205" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H205" s="53" t="n">
+      <x:c r="G205" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H205" s="53">
         <x:v>8939.6</x:v>
       </x:c>
     </x:row>
@@ -8970,13 +8970,13 @@
       <x:c r="E206" s="52">
         <x:v>34735</x:v>
       </x:c>
-      <x:c r="F206" s="53" t="n">
+      <x:c r="F206" s="53">
         <x:v>13908</x:v>
       </x:c>
-      <x:c r="G206" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H206" s="53" t="n">
+      <x:c r="G206" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H206" s="53">
         <x:v>13908</x:v>
       </x:c>
     </x:row>
@@ -8990,14 +8990,14 @@
       <x:c r="D207" s="51" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="E207" s="52" t="s"/>
-      <x:c r="F207" s="53" t="n">
+      <x:c r="E207" s="52"/>
+      <x:c r="F207" s="53">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G207" s="54" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H207" s="53" t="n">
+      <x:c r="G207" s="54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H207" s="53">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -9032,11 +9032,8 @@
     <x:col min="6" max="6" width="13.832031" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="3" spans="1:6"/>
     <x:row r="4" spans="1:6" ht="11.25" customHeight="1"/>
     <x:row r="5" spans="1:6" ht="25.5" customHeight="1"/>
-    <x:row r="6" spans="1:6"/>
-    <x:row r="7" spans="1:6"/>
     <x:row r="8" spans="1:6" ht="12" customHeight="1"/>
     <x:row r="9" spans="1:6" ht="12.75" customHeight="1"/>
   </x:sheetData>
@@ -9064,13 +9061,7 @@
     <x:col min="5" max="5" width="11" style="0" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5"/>
-    <x:row r="4" spans="1:5"/>
-    <x:row r="5" spans="1:5"/>
-    <x:row r="6" spans="1:5"/>
     <x:row r="7" spans="1:5" ht="11.25" customHeight="1"/>
-    <x:row r="8" spans="1:5"/>
-    <x:row r="9" spans="1:5"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -9054,7 +9054,7 @@
   <x:dimension ref="B1:E9"/>
   <x:sheetFormatPr defaultRowHeight="11.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.210625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="17.164062" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="14.5" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="20.5" style="0" customWidth="1"/>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -16,13 +16,13 @@
   </x:definedNames>
   <x:calcPr calcId="125725"/>
   <x:pivotCaches>
-    <x:pivotCache cacheId="0" r:id="rId4"/>
+    <x:pivotCache cacheId="0" r:id="rId8"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Company</x:t>
   </x:si>
@@ -1290,314 +1290,6 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy=" " refreshedDate="43579.724609375" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="1">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="B2:H207" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields count="7">
-    <x:cacheField name="Company">
-      <x:sharedItems count="54">
-        <x:s v="Sight Diver"/>
-        <x:s v="Davy Jones' Locker"/>
-        <x:s v="Tom Sawyer Diving Centre"/>
-        <x:s v="Blue Jack Aqua Center"/>
-        <x:s v="VIP Divers Club"/>
-        <x:s v="Ocean Paradise"/>
-        <x:s v="Fantastique Aquatica"/>
-        <x:s v="Marmot Divers Club"/>
-        <x:s v="The Depth Charge"/>
-        <x:s v="Blue Sports"/>
-        <x:s v="Makai SCUBA Club"/>
-        <x:s v="Action Club"/>
-        <x:s v="Jamaica SCUBA Centre"/>
-        <x:s v="Island Finders"/>
-        <x:s v="Adventure Undersea"/>
-        <x:s v="Blue Sports Club"/>
-        <x:s v="Frank's Divers Supply"/>
-        <x:s v="SCUBA Heaven"/>
-        <x:s v="Kauai Dive Shoppe"/>
-        <x:s v="Fisherman's Eye"/>
-        <x:s v="Marina SCUBA Center"/>
-        <x:s v="Tora Tora Tora"/>
-        <x:s v="Action Diver Supply"/>
-        <x:s v="Waterspout SCUBA Center"/>
-        <x:s v="Jamaica Sun, Inc."/>
-        <x:s v="Blue Glass Happiness"/>
-        <x:s v="Princess Island SCUBA"/>
-        <x:s v="Ocean Adventures"/>
-        <x:s v="Neptune's Trident Supply"/>
-        <x:s v="Divers of Corfu, Inc."/>
-        <x:s v="Divers-for-Hire"/>
-        <x:s v="Underwater Sports Co."/>
-        <x:s v="Shangri-La Sports Center"/>
-        <x:s v="The Diving Company"/>
-        <x:s v="Unisco"/>
-        <x:s v="Gold Coast Supply"/>
-        <x:s v="Aquatic Drama"/>
-        <x:s v="Catamaran Dive Club"/>
-        <x:s v="On-Target SCUBA"/>
-        <x:s v="George Bean &amp; Co."/>
-        <x:s v="Underwater SCUBA Company"/>
-        <x:s v="Divers of Blue-green"/>
-        <x:s v="Norwest'er SCUBA Limited"/>
-        <x:s v="Safari Under the Sea"/>
-        <x:s v="Kirk Enterprises"/>
-        <x:s v="Cayman Divers World Unlimited"/>
-        <x:s v="Underwater Fantasy"/>
-        <x:s v="Divers of Venice"/>
-        <x:s v="Central Underwater Supplies"/>
-        <x:s v="Larry's Diving School"/>
-        <x:s v="San Pablo Dive Center"/>
-        <x:s v="Professional Divers, Ltd."/>
-        <x:s v="American SCUBA Supply"/>
-        <x:s v="Vashon Ventures"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Payment method">
-      <x:sharedItems count="7">
-        <x:s v="Credit"/>
-        <x:s v="Check"/>
-        <x:s v="Visa"/>
-        <x:s v="COD"/>
-        <x:s v="MC"/>
-        <x:s v="AmEx"/>
-        <x:s v="Cash"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="OrderNo">
-      <x:sharedItems count="205">
-        <x:s v="1003"/>
-        <x:s v="1004"/>
-        <x:s v="1005"/>
-        <x:s v="1006"/>
-        <x:s v="1007"/>
-        <x:s v="1008"/>
-        <x:s v="1009"/>
-        <x:s v="1010"/>
-        <x:s v="1011"/>
-        <x:s v="1012"/>
-        <x:s v="1013"/>
-        <x:s v="1014"/>
-        <x:s v="1015"/>
-        <x:s v="1016"/>
-        <x:s v="1017"/>
-        <x:s v="1018"/>
-        <x:s v="1019"/>
-        <x:s v="1020"/>
-        <x:s v="1021"/>
-        <x:s v="1022"/>
-        <x:s v="1023"/>
-        <x:s v="1024"/>
-        <x:s v="1025"/>
-        <x:s v="1026"/>
-        <x:s v="1027"/>
-        <x:s v="1028"/>
-        <x:s v="1029"/>
-        <x:s v="1030"/>
-        <x:s v="1031"/>
-        <x:s v="1032"/>
-        <x:s v="1033"/>
-        <x:s v="1034"/>
-        <x:s v="1035"/>
-        <x:s v="1036"/>
-        <x:s v="1037"/>
-        <x:s v="1038"/>
-        <x:s v="1039"/>
-        <x:s v="1040"/>
-        <x:s v="1041"/>
-        <x:s v="1042"/>
-        <x:s v="1043"/>
-        <x:s v="1044"/>
-        <x:s v="1045"/>
-        <x:s v="1046"/>
-        <x:s v="1047"/>
-        <x:s v="1048"/>
-        <x:s v="1049"/>
-        <x:s v="1050"/>
-        <x:s v="1051"/>
-        <x:s v="1052"/>
-        <x:s v="1053"/>
-        <x:s v="1054"/>
-        <x:s v="1055"/>
-        <x:s v="1056"/>
-        <x:s v="1057"/>
-        <x:s v="1058"/>
-        <x:s v="1059"/>
-        <x:s v="1060"/>
-        <x:s v="1061"/>
-        <x:s v="1062"/>
-        <x:s v="1063"/>
-        <x:s v="1064"/>
-        <x:s v="1065"/>
-        <x:s v="1066"/>
-        <x:s v="1067"/>
-        <x:s v="1068"/>
-        <x:s v="1069"/>
-        <x:s v="1070"/>
-        <x:s v="1071"/>
-        <x:s v="1072"/>
-        <x:s v="1073"/>
-        <x:s v="1074"/>
-        <x:s v="1075"/>
-        <x:s v="1076"/>
-        <x:s v="1077"/>
-        <x:s v="1078"/>
-        <x:s v="1079"/>
-        <x:s v="1080"/>
-        <x:s v="1081"/>
-        <x:s v="1082"/>
-        <x:s v="1083"/>
-        <x:s v="1084"/>
-        <x:s v="1086"/>
-        <x:s v="1087"/>
-        <x:s v="1089"/>
-        <x:s v="1090"/>
-        <x:s v="1091"/>
-        <x:s v="1092"/>
-        <x:s v="1093"/>
-        <x:s v="1094"/>
-        <x:s v="1095"/>
-        <x:s v="1096"/>
-        <x:s v="1097"/>
-        <x:s v="1098"/>
-        <x:s v="1099"/>
-        <x:s v="1100"/>
-        <x:s v="1101"/>
-        <x:s v="1102"/>
-        <x:s v="1103"/>
-        <x:s v="1104"/>
-        <x:s v="1105"/>
-        <x:s v="1106"/>
-        <x:s v="1107"/>
-        <x:s v="1109"/>
-        <x:s v="1111"/>
-        <x:s v="1112"/>
-        <x:s v="1113"/>
-        <x:s v="1115"/>
-        <x:s v="1116"/>
-        <x:s v="1117"/>
-        <x:s v="1118"/>
-        <x:s v="1119"/>
-        <x:s v="1120"/>
-        <x:s v="1121"/>
-        <x:s v="1122"/>
-        <x:s v="1123"/>
-        <x:s v="1124"/>
-        <x:s v="1125"/>
-        <x:s v="1126"/>
-        <x:s v="1127"/>
-        <x:s v="1128"/>
-        <x:s v="1129"/>
-        <x:s v="1130"/>
-        <x:s v="1131"/>
-        <x:s v="1132"/>
-        <x:s v="1133"/>
-        <x:s v="1134"/>
-        <x:s v="1136"/>
-        <x:s v="1137"/>
-        <x:s v="1139"/>
-        <x:s v="1140"/>
-        <x:s v="1141"/>
-        <x:s v="1142"/>
-        <x:s v="1143"/>
-        <x:s v="1144"/>
-        <x:s v="1145"/>
-        <x:s v="1146"/>
-        <x:s v="1148"/>
-        <x:s v="1149"/>
-        <x:s v="1150"/>
-        <x:s v="1152"/>
-        <x:s v="1153"/>
-        <x:s v="1154"/>
-        <x:s v="1155"/>
-        <x:s v="1156"/>
-        <x:s v="1158"/>
-        <x:s v="1160"/>
-        <x:s v="1161"/>
-        <x:s v="1162"/>
-        <x:s v="1163"/>
-        <x:s v="1165"/>
-        <x:s v="1166"/>
-        <x:s v="1168"/>
-        <x:s v="1169"/>
-        <x:s v="1170"/>
-        <x:s v="1171"/>
-        <x:s v="1173"/>
-        <x:s v="1175"/>
-        <x:s v="1176"/>
-        <x:s v="1178"/>
-        <x:s v="1180"/>
-        <x:s v="1183"/>
-        <x:s v="1195"/>
-        <x:s v="1196"/>
-        <x:s v="1197"/>
-        <x:s v="1198"/>
-        <x:s v="1199"/>
-        <x:s v="1200"/>
-        <x:s v="1201"/>
-        <x:s v="1202"/>
-        <x:s v="1204"/>
-        <x:s v="1205"/>
-        <x:s v="1207"/>
-        <x:s v="1209"/>
-        <x:s v="1212"/>
-        <x:s v="1215"/>
-        <x:s v="1217"/>
-        <x:s v="1221"/>
-        <x:s v="1250"/>
-        <x:s v="1253"/>
-        <x:s v="1255"/>
-        <x:s v="1260"/>
-        <x:s v="1261"/>
-        <x:s v="1263"/>
-        <x:s v="1266"/>
-        <x:s v="1269"/>
-        <x:s v="1271"/>
-        <x:s v="1275"/>
-        <x:s v="1278"/>
-        <x:s v="1280"/>
-        <x:s v="1283"/>
-        <x:s v="1292"/>
-        <x:s v="1294"/>
-        <x:s v="1295"/>
-        <x:s v="1296"/>
-        <x:s v="1298"/>
-        <x:s v="1300"/>
-        <x:s v="1302"/>
-        <x:s v="1305"/>
-        <x:s v="1309"/>
-        <x:s v="1315"/>
-        <x:s v="1317"/>
-        <x:s v="1350"/>
-        <x:s v="1355"/>
-        <x:s v="1860"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Ship date">
-      <x:sharedItems containsSemiMixedTypes="1" containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="1988-01-21T00:00:00" maxDate="1995-02-05T00:00:00" count="191"/>
-    </x:cacheField>
-    <x:cacheField name="Items total">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="54" maxValue="158922.65" count="205"/>
-    </x:cacheField>
-    <x:cacheField name="Tax rate">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="8.5" count="3">
-        <x:n v="4.5"/>
-        <x:n v="0"/>
-        <x:n v="8.5"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Amount paid">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="158922.65" count="184"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataCaption="Values" showError="0" missingCaption="" showMissing="1" pageWrap="0" pageOverThenDown="0" itemPrintTitles="1" mergeItem="1" indent="0" compact="0" compactData="0" gridDropZones="1">
   <x:location ref="B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
@@ -9069,4 +8761,896 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3">
+  <x:cacheSource type="worksheet">
+    <x:worksheetSource ref="B2:H207" sheet="Sheet1"/>
+  </x:cacheSource>
+  <x:cacheFields>
+    <x:cacheField name="Company">
+      <x:sharedItems count="54">
+        <x:s v="Sight Diver"/>
+        <x:s v="Davy Jones' Locker"/>
+        <x:s v="Tom Sawyer Diving Centre"/>
+        <x:s v="Blue Jack Aqua Center"/>
+        <x:s v="VIP Divers Club"/>
+        <x:s v="Ocean Paradise"/>
+        <x:s v="Fantastique Aquatica"/>
+        <x:s v="Marmot Divers Club"/>
+        <x:s v="The Depth Charge"/>
+        <x:s v="Blue Sports"/>
+        <x:s v="Makai SCUBA Club"/>
+        <x:s v="Action Club"/>
+        <x:s v="Jamaica SCUBA Centre"/>
+        <x:s v="Island Finders"/>
+        <x:s v="Adventure Undersea"/>
+        <x:s v="Blue Sports Club"/>
+        <x:s v="Frank's Divers Supply"/>
+        <x:s v="SCUBA Heaven"/>
+        <x:s v="Kauai Dive Shoppe"/>
+        <x:s v="Fisherman's Eye"/>
+        <x:s v="Marina SCUBA Center"/>
+        <x:s v="Tora Tora Tora"/>
+        <x:s v="Action Diver Supply"/>
+        <x:s v="Waterspout SCUBA Center"/>
+        <x:s v="Jamaica Sun, Inc."/>
+        <x:s v="Blue Glass Happiness"/>
+        <x:s v="Princess Island SCUBA"/>
+        <x:s v="Ocean Adventures"/>
+        <x:s v="Neptune's Trident Supply"/>
+        <x:s v="Divers of Corfu, Inc."/>
+        <x:s v="Divers-for-Hire"/>
+        <x:s v="Underwater Sports Co."/>
+        <x:s v="Shangri-La Sports Center"/>
+        <x:s v="The Diving Company"/>
+        <x:s v="Unisco"/>
+        <x:s v="Gold Coast Supply"/>
+        <x:s v="Aquatic Drama"/>
+        <x:s v="Catamaran Dive Club"/>
+        <x:s v="On-Target SCUBA"/>
+        <x:s v="George Bean &amp; Co."/>
+        <x:s v="Underwater SCUBA Company"/>
+        <x:s v="Divers of Blue-green"/>
+        <x:s v="Norwest'er SCUBA Limited"/>
+        <x:s v="Safari Under the Sea"/>
+        <x:s v="Kirk Enterprises"/>
+        <x:s v="Cayman Divers World Unlimited"/>
+        <x:s v="Underwater Fantasy"/>
+        <x:s v="Divers of Venice"/>
+        <x:s v="Central Underwater Supplies"/>
+        <x:s v="Larry's Diving School"/>
+        <x:s v="San Pablo Dive Center"/>
+        <x:s v="Professional Divers, Ltd."/>
+        <x:s v="American SCUBA Supply"/>
+        <x:s v="Vashon Ventures"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Payment method">
+      <x:sharedItems count="7">
+        <x:s v="Credit"/>
+        <x:s v="Check"/>
+        <x:s v="Visa"/>
+        <x:s v="COD"/>
+        <x:s v="MC"/>
+        <x:s v="AmEx"/>
+        <x:s v="Cash"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="OrderNo">
+      <x:sharedItems count="205">
+        <x:s v="1003"/>
+        <x:s v="1004"/>
+        <x:s v="1005"/>
+        <x:s v="1006"/>
+        <x:s v="1007"/>
+        <x:s v="1008"/>
+        <x:s v="1009"/>
+        <x:s v="1010"/>
+        <x:s v="1011"/>
+        <x:s v="1012"/>
+        <x:s v="1013"/>
+        <x:s v="1014"/>
+        <x:s v="1015"/>
+        <x:s v="1016"/>
+        <x:s v="1017"/>
+        <x:s v="1018"/>
+        <x:s v="1019"/>
+        <x:s v="1020"/>
+        <x:s v="1021"/>
+        <x:s v="1022"/>
+        <x:s v="1023"/>
+        <x:s v="1024"/>
+        <x:s v="1025"/>
+        <x:s v="1026"/>
+        <x:s v="1027"/>
+        <x:s v="1028"/>
+        <x:s v="1029"/>
+        <x:s v="1030"/>
+        <x:s v="1031"/>
+        <x:s v="1032"/>
+        <x:s v="1033"/>
+        <x:s v="1034"/>
+        <x:s v="1035"/>
+        <x:s v="1036"/>
+        <x:s v="1037"/>
+        <x:s v="1038"/>
+        <x:s v="1039"/>
+        <x:s v="1040"/>
+        <x:s v="1041"/>
+        <x:s v="1042"/>
+        <x:s v="1043"/>
+        <x:s v="1044"/>
+        <x:s v="1045"/>
+        <x:s v="1046"/>
+        <x:s v="1047"/>
+        <x:s v="1048"/>
+        <x:s v="1049"/>
+        <x:s v="1050"/>
+        <x:s v="1051"/>
+        <x:s v="1052"/>
+        <x:s v="1053"/>
+        <x:s v="1054"/>
+        <x:s v="1055"/>
+        <x:s v="1056"/>
+        <x:s v="1057"/>
+        <x:s v="1058"/>
+        <x:s v="1059"/>
+        <x:s v="1060"/>
+        <x:s v="1061"/>
+        <x:s v="1062"/>
+        <x:s v="1063"/>
+        <x:s v="1064"/>
+        <x:s v="1065"/>
+        <x:s v="1066"/>
+        <x:s v="1067"/>
+        <x:s v="1068"/>
+        <x:s v="1069"/>
+        <x:s v="1070"/>
+        <x:s v="1071"/>
+        <x:s v="1072"/>
+        <x:s v="1073"/>
+        <x:s v="1074"/>
+        <x:s v="1075"/>
+        <x:s v="1076"/>
+        <x:s v="1077"/>
+        <x:s v="1078"/>
+        <x:s v="1079"/>
+        <x:s v="1080"/>
+        <x:s v="1081"/>
+        <x:s v="1082"/>
+        <x:s v="1083"/>
+        <x:s v="1084"/>
+        <x:s v="1086"/>
+        <x:s v="1087"/>
+        <x:s v="1089"/>
+        <x:s v="1090"/>
+        <x:s v="1091"/>
+        <x:s v="1092"/>
+        <x:s v="1093"/>
+        <x:s v="1094"/>
+        <x:s v="1095"/>
+        <x:s v="1096"/>
+        <x:s v="1097"/>
+        <x:s v="1098"/>
+        <x:s v="1099"/>
+        <x:s v="1100"/>
+        <x:s v="1101"/>
+        <x:s v="1102"/>
+        <x:s v="1103"/>
+        <x:s v="1104"/>
+        <x:s v="1105"/>
+        <x:s v="1106"/>
+        <x:s v="1107"/>
+        <x:s v="1109"/>
+        <x:s v="1111"/>
+        <x:s v="1112"/>
+        <x:s v="1113"/>
+        <x:s v="1115"/>
+        <x:s v="1116"/>
+        <x:s v="1117"/>
+        <x:s v="1118"/>
+        <x:s v="1119"/>
+        <x:s v="1120"/>
+        <x:s v="1121"/>
+        <x:s v="1122"/>
+        <x:s v="1123"/>
+        <x:s v="1124"/>
+        <x:s v="1125"/>
+        <x:s v="1126"/>
+        <x:s v="1127"/>
+        <x:s v="1128"/>
+        <x:s v="1129"/>
+        <x:s v="1130"/>
+        <x:s v="1131"/>
+        <x:s v="1132"/>
+        <x:s v="1133"/>
+        <x:s v="1134"/>
+        <x:s v="1136"/>
+        <x:s v="1137"/>
+        <x:s v="1139"/>
+        <x:s v="1140"/>
+        <x:s v="1141"/>
+        <x:s v="1142"/>
+        <x:s v="1143"/>
+        <x:s v="1144"/>
+        <x:s v="1145"/>
+        <x:s v="1146"/>
+        <x:s v="1148"/>
+        <x:s v="1149"/>
+        <x:s v="1150"/>
+        <x:s v="1152"/>
+        <x:s v="1153"/>
+        <x:s v="1154"/>
+        <x:s v="1155"/>
+        <x:s v="1156"/>
+        <x:s v="1158"/>
+        <x:s v="1160"/>
+        <x:s v="1161"/>
+        <x:s v="1162"/>
+        <x:s v="1163"/>
+        <x:s v="1165"/>
+        <x:s v="1166"/>
+        <x:s v="1168"/>
+        <x:s v="1169"/>
+        <x:s v="1170"/>
+        <x:s v="1171"/>
+        <x:s v="1173"/>
+        <x:s v="1175"/>
+        <x:s v="1176"/>
+        <x:s v="1178"/>
+        <x:s v="1180"/>
+        <x:s v="1183"/>
+        <x:s v="1195"/>
+        <x:s v="1196"/>
+        <x:s v="1197"/>
+        <x:s v="1198"/>
+        <x:s v="1199"/>
+        <x:s v="1200"/>
+        <x:s v="1201"/>
+        <x:s v="1202"/>
+        <x:s v="1204"/>
+        <x:s v="1205"/>
+        <x:s v="1207"/>
+        <x:s v="1209"/>
+        <x:s v="1212"/>
+        <x:s v="1215"/>
+        <x:s v="1217"/>
+        <x:s v="1221"/>
+        <x:s v="1250"/>
+        <x:s v="1253"/>
+        <x:s v="1255"/>
+        <x:s v="1260"/>
+        <x:s v="1261"/>
+        <x:s v="1263"/>
+        <x:s v="1266"/>
+        <x:s v="1269"/>
+        <x:s v="1271"/>
+        <x:s v="1275"/>
+        <x:s v="1278"/>
+        <x:s v="1280"/>
+        <x:s v="1283"/>
+        <x:s v="1292"/>
+        <x:s v="1294"/>
+        <x:s v="1295"/>
+        <x:s v="1296"/>
+        <x:s v="1298"/>
+        <x:s v="1300"/>
+        <x:s v="1302"/>
+        <x:s v="1305"/>
+        <x:s v="1309"/>
+        <x:s v="1315"/>
+        <x:s v="1317"/>
+        <x:s v="1350"/>
+        <x:s v="1355"/>
+        <x:s v="1860"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Ship date">
+      <x:sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="1988-01-21T00:00:00" maxDate="1995-02-05T00:00:00" count="192">
+        <x:d v="1988-05-03T00:00:00"/>
+        <x:d v="1988-04-18T00:00:00"/>
+        <x:d v="1988-01-21T00:00:00"/>
+        <x:d v="1988-11-07T00:00:00"/>
+        <x:d v="1988-05-02T00:00:00"/>
+        <x:d v="1988-05-04T00:00:00"/>
+        <x:d v="1988-05-12T00:00:00"/>
+        <x:d v="1988-05-19T00:00:00"/>
+        <x:d v="1988-05-20T00:00:00"/>
+        <x:d v="1988-05-26T00:00:00"/>
+        <x:d v="1988-06-03T00:00:00"/>
+        <x:d v="1988-06-13T00:00:00"/>
+        <x:d v="1988-06-19T00:00:00"/>
+        <x:d v="1988-06-25T00:00:00"/>
+        <x:d v="1988-07-01T00:00:00"/>
+        <x:d v="1988-07-02T00:00:00"/>
+        <x:d v="1988-07-03T00:00:00"/>
+        <x:d v="1988-07-04T00:00:00"/>
+        <x:d v="1988-07-08T00:00:00"/>
+        <x:d v="1988-07-19T00:00:00"/>
+        <x:d v="1988-07-26T00:00:00"/>
+        <x:d v="1988-08-01T00:00:00"/>
+        <x:d v="1988-08-02T00:00:00"/>
+        <x:d v="1988-08-14T00:00:00"/>
+        <x:d v="1988-08-17T00:00:00"/>
+        <x:d v="1988-08-26T00:00:00"/>
+        <x:d v="1988-08-27T00:00:00"/>
+        <x:d v="1988-09-01T00:00:00"/>
+        <x:d v="1988-09-05T00:00:00"/>
+        <x:d v="1988-09-17T00:00:00"/>
+        <x:d v="1988-09-25T00:00:00"/>
+        <x:d v="1988-10-01T00:00:00"/>
+        <x:d v="1988-10-09T00:00:00"/>
+        <x:d v="1988-10-17T00:00:00"/>
+        <x:d v="1988-11-13T00:00:00"/>
+        <x:d v="1988-11-28T00:00:00"/>
+        <x:d v="1988-12-03T00:00:00"/>
+        <x:d v="1988-12-14T00:00:00"/>
+        <x:d v="1988-12-25T00:00:00"/>
+        <x:d v="1989-01-05T00:00:00"/>
+        <x:d v="1989-01-07T00:00:00"/>
+        <x:d v="1989-01-16T00:00:00"/>
+        <x:d v="1989-02-01T00:00:00"/>
+        <x:d v="1989-02-05T00:00:00"/>
+        <x:d v="1989-02-09T00:00:00"/>
+        <x:d v="1989-02-19T00:00:00"/>
+        <x:d v="1989-02-22T00:00:00"/>
+        <x:d v="1989-02-25T00:00:00"/>
+        <x:d v="1989-03-01T00:00:00"/>
+        <x:d v="1989-03-04T00:00:00"/>
+        <x:d v="1989-03-09T00:00:00"/>
+        <x:d v="1989-03-14T00:00:00"/>
+        <x:d v="1989-03-25T00:00:00"/>
+        <x:d v="1989-03-26T00:00:00"/>
+        <x:d v="1989-03-27T00:00:00"/>
+        <x:d v="1989-04-02T00:00:00"/>
+        <x:d v="1989-04-04T00:00:00"/>
+        <x:d v="1989-04-06T00:00:00"/>
+        <x:d v="1989-04-08T00:00:00"/>
+        <x:d v="1989-04-10T00:00:00"/>
+        <x:d v="1989-04-12T00:00:00"/>
+        <x:d v="1989-04-16T00:00:00"/>
+        <x:d v="1989-04-20T00:00:00"/>
+        <x:d v="1989-04-22T00:00:00"/>
+        <x:d v="1989-04-26T00:00:00"/>
+        <x:d v="1989-05-01T00:00:00"/>
+        <x:d v="1989-05-02T00:00:00"/>
+        <x:d v="1989-05-04T00:00:00"/>
+        <x:d v="1989-05-06T00:00:00"/>
+        <x:d v="1989-05-08T00:00:00"/>
+        <x:d v="1989-05-10T00:00:00"/>
+        <x:d v="1989-05-12T00:00:00"/>
+        <x:d v="1989-05-19T00:00:00"/>
+        <x:d v="1989-05-21T00:00:00"/>
+        <x:d v="1989-05-23T00:00:00"/>
+        <x:d v="1989-05-26T00:00:00"/>
+        <x:d v="1989-06-01T00:00:00"/>
+        <x:d v="1989-06-02T00:00:00"/>
+        <x:d v="1989-06-04T00:00:00"/>
+        <x:d v="1989-06-06T00:00:00"/>
+        <x:d v="1989-06-09T00:00:00"/>
+        <x:d v="1989-06-12T00:00:00"/>
+        <x:d v="1989-06-14T00:00:00"/>
+        <x:d v="1989-06-16T00:00:00"/>
+        <x:d v="1989-06-20T00:00:00"/>
+        <x:d v="1989-07-04T00:00:00"/>
+        <x:d v="1992-06-06T00:00:00"/>
+        <x:d v="1992-07-13T00:00:00"/>
+        <x:d v="1992-07-18T00:00:00"/>
+        <x:d v="1992-07-21T00:00:00"/>
+        <x:d v="1992-09-23T00:00:00"/>
+        <x:d v="1992-10-24T00:00:00"/>
+        <x:d v="1992-11-13T00:00:00"/>
+        <x:d v="1992-12-14T00:00:00"/>
+        <x:d v="1993-01-02T00:00:00"/>
+        <x:d v="1993-02-12T00:00:00"/>
+        <x:d v="1993-03-13T00:00:00"/>
+        <x:d v="1993-03-21T00:00:00"/>
+        <x:d v="1993-04-13T00:00:00"/>
+        <x:d v="1993-04-23T00:00:00"/>
+        <x:d v="1993-05-15T00:00:00"/>
+        <x:d v="1993-05-25T00:00:00"/>
+        <x:d v="1993-06-02T00:00:00"/>
+        <x:d v="1993-07-23T00:00:00"/>
+        <x:d v="1993-08-24T00:00:00"/>
+        <x:d v="1993-09-01T00:00:00"/>
+        <x:d v="1993-09-04T00:00:00"/>
+        <x:d v="1993-10-01T00:00:00"/>
+        <x:d v="1993-10-02T00:00:00"/>
+        <x:d v="1993-10-08T00:00:00"/>
+        <x:d v="1993-10-19T00:00:00"/>
+        <x:d v="1993-10-26T00:00:00"/>
+        <x:d v="1993-11-01T00:00:00"/>
+        <x:d v="1993-11-02T00:00:00"/>
+        <x:d v="1993-11-14T00:00:00"/>
+        <x:d v="1993-11-27T00:00:00"/>
+        <x:d v="1993-12-01T00:00:00"/>
+        <x:d v="1993-12-12T00:00:00"/>
+        <x:d v="1993-12-17T00:00:00"/>
+        <x:d v="1993-12-25T00:00:00"/>
+        <x:d v="1994-01-01T00:00:00"/>
+        <x:d v="1994-01-09T00:00:00"/>
+        <x:d v="1994-01-17T00:00:00"/>
+        <x:d v="1994-02-13T00:00:00"/>
+        <x:d v="1994-03-03T00:00:00"/>
+        <x:d v="1994-03-14T00:00:00"/>
+        <x:d v="1994-03-25T00:00:00"/>
+        <x:d v="1994-04-07T00:00:00"/>
+        <x:d v="1994-04-16T00:00:00"/>
+        <x:d v="1994-05-01T00:00:00"/>
+        <x:d v="1994-05-05T00:00:00"/>
+        <x:d v="1994-05-09T00:00:00"/>
+        <x:d v="1994-05-22T00:00:00"/>
+        <x:d v="1994-06-01T00:00:00"/>
+        <x:d v="1994-06-04T00:00:00"/>
+        <x:d v="1994-06-09T00:00:00"/>
+        <x:d v="1994-06-14T00:00:00"/>
+        <x:d v="1994-06-26T00:00:00"/>
+        <x:d v="1994-07-01T00:00:00"/>
+        <x:d v="1994-07-04T00:00:00"/>
+        <x:d v="1994-07-06T00:00:00"/>
+        <x:d v="1994-07-08T00:00:00"/>
+        <x:d v="1994-07-10T00:00:00"/>
+        <x:d v="1994-07-16T00:00:00"/>
+        <x:d v="1994-07-22T00:00:00"/>
+        <x:d v="1994-07-26T00:00:00"/>
+        <x:d v="1994-08-02T00:00:00"/>
+        <x:d v="1994-08-06T00:00:00"/>
+        <x:d v="1994-08-10T00:00:00"/>
+        <x:d v="1994-09-06T00:00:00"/>
+        <x:d v="1994-09-08T00:00:00"/>
+        <x:d v="1994-09-12T00:00:00"/>
+        <x:d v="1994-09-14T00:00:00"/>
+        <x:d v="1994-09-16T00:00:00"/>
+        <x:d v="1994-09-20T00:00:00"/>
+        <x:d v="1994-10-04T00:00:00"/>
+        <x:d v="1994-10-06T00:00:00"/>
+        <x:d v="1994-10-18T00:00:00"/>
+        <x:d v="1994-10-21T00:00:00"/>
+        <x:d v="1994-11-11T00:00:00"/>
+        <x:d v="1994-11-12T00:00:00"/>
+        <x:d v="1994-11-14T00:00:00"/>
+        <x:d v="1994-11-16T00:00:00"/>
+        <x:d v="1994-11-22T00:00:00"/>
+        <x:d v="1994-11-23T00:00:00"/>
+        <x:d v="1994-11-24T00:00:00"/>
+        <x:d v="1994-11-26T00:00:00"/>
+        <x:d v="1994-12-09T00:00:00"/>
+        <x:d v="1994-12-10T00:00:00"/>
+        <x:d v="1994-12-11T00:00:00"/>
+        <x:d v="1994-12-14T00:00:00"/>
+        <x:d v="1994-12-15T00:00:00"/>
+        <x:d v="1994-12-16T00:00:00"/>
+        <x:d v="1994-12-20T00:00:00"/>
+        <x:d v="1994-12-22T00:00:00"/>
+        <x:d v="1994-12-23T00:00:00"/>
+        <x:d v="1994-12-26T00:00:00"/>
+        <x:d v="1994-12-30T00:00:00"/>
+        <x:d v="1995-01-01T00:00:00"/>
+        <x:d v="1995-01-04T00:00:00"/>
+        <x:d v="1995-01-06T00:00:00"/>
+        <x:d v="1995-01-08T00:00:00"/>
+        <x:d v="1995-01-09T00:00:00"/>
+        <x:d v="1995-01-10T00:00:00"/>
+        <x:d v="1995-01-16T00:00:00"/>
+        <x:d v="1995-01-20T00:00:00"/>
+        <x:d v="1995-01-22T00:00:00"/>
+        <x:d v="1995-01-26T00:00:00"/>
+        <x:d v="1995-02-01T00:00:00"/>
+        <x:d v="1995-02-02T00:00:00"/>
+        <x:d v="1995-02-05T00:00:00"/>
+        <x:m/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Items total">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="54" maxValue="158922.65" count="205">
+        <x:n v="1250"/>
+        <x:n v="7885"/>
+        <x:n v="4807"/>
+        <x:n v="31987"/>
+        <x:n v="6500"/>
+        <x:n v="1449.5"/>
+        <x:n v="5587"/>
+        <x:n v="4996"/>
+        <x:n v="2679.85"/>
+        <x:n v="5201"/>
+        <x:n v="3115"/>
+        <x:n v="134.85"/>
+        <x:n v="20321.75"/>
+        <x:n v="2605"/>
+        <x:n v="10195"/>
+        <x:n v="5256"/>
+        <x:n v="20602"/>
+        <x:n v="9955"/>
+        <x:n v="3719"/>
+        <x:n v="10064.65"/>
+        <x:n v="4674"/>
+        <x:n v="6897"/>
+        <x:n v="930"/>
+        <x:n v="2920"/>
+        <x:n v="25210"/>
+        <x:n v="343.8"/>
+        <x:n v="20108"/>
+        <x:n v="559.6"/>
+        <x:n v="12685"/>
+        <x:n v="775"/>
+        <x:n v="1238"/>
+        <x:n v="18532"/>
+        <x:n v="560"/>
+        <x:n v="4110"/>
+        <x:n v="3117"/>
+        <x:n v="10152"/>
+        <x:n v="536.8"/>
+        <x:n v="3632"/>
+        <x:n v="7807"/>
+        <x:n v="971.7"/>
+        <x:n v="12455"/>
+        <x:n v="64050"/>
+        <x:n v="787.8"/>
+        <x:n v="766.8"/>
+        <x:n v="15365"/>
+        <x:n v="7346"/>
+        <x:n v="1809.85"/>
+        <x:n v="6287.85"/>
+        <x:n v="325"/>
+        <x:n v="16788"/>
+        <x:n v="24650"/>
+        <x:n v="14188"/>
+        <x:n v="23406"/>
+        <x:n v="19293.7"/>
+        <x:n v="1975"/>
+        <x:n v="12736"/>
+        <x:n v="2150"/>
+        <x:n v="15355"/>
+        <x:n v="24277.3"/>
+        <x:n v="18320"/>
+        <x:n v="61869.3"/>
+        <x:n v="395"/>
+        <x:n v="17814"/>
+        <x:n v="19812"/>
+        <x:n v="4495"/>
+        <x:n v="31847"/>
+        <x:n v="33829.45"/>
+        <x:n v="22354"/>
+        <x:n v="103041"/>
+        <x:n v="3596"/>
+        <x:n v="19414"/>
+        <x:n v="2195"/>
+        <x:n v="8560"/>
+        <x:n v="17781"/>
+        <x:n v="156"/>
+        <x:n v="79116"/>
+        <x:n v="4445"/>
+        <x:n v="9634"/>
+        <x:n v="30566"/>
+        <x:n v="1416.45"/>
+        <x:n v="11164.8"/>
+        <x:n v="1185"/>
+        <x:n v="14049.95"/>
+        <x:n v="14045"/>
+        <x:n v="2706"/>
+        <x:n v="8507"/>
+        <x:n v="1950"/>
+        <x:n v="76698.75"/>
+        <x:n v="479.8"/>
+        <x:n v="4113.75"/>
+        <x:n v="7531.75"/>
+        <x:n v="123740"/>
+        <x:n v="12953.6"/>
+        <x:n v="472.9"/>
+        <x:n v="859.95"/>
+        <x:n v="6094.8"/>
+        <x:n v="11629.85"/>
+        <x:n v="2844"/>
+        <x:n v="39797.7"/>
+        <x:n v="51673.15"/>
+        <x:n v="31219.95"/>
+        <x:n v="3531.8"/>
+        <x:n v="28389"/>
+        <x:n v="203"/>
+        <x:n v="4720.8"/>
+        <x:n v="5565"/>
+        <x:n v="2514.65"/>
+        <x:n v="4894.95"/>
+        <x:n v="23104"/>
+        <x:n v="6734.85"/>
+        <x:n v="21614"/>
+        <x:n v="14557.95"/>
+        <x:n v="784.9"/>
+        <x:n v="820"/>
+        <x:n v="44854"/>
+        <x:n v="13945"/>
+        <x:n v="33071"/>
+        <x:n v="6583.8"/>
+        <x:n v="10107"/>
+        <x:n v="25071"/>
+        <x:n v="8294"/>
+        <x:n v="1004.8"/>
+        <x:n v="6300"/>
+        <x:n v="11989.2"/>
+        <x:n v="906"/>
+        <x:n v="2419"/>
+        <x:n v="6675.95"/>
+        <x:n v="2971"/>
+        <x:n v="6785.4"/>
+        <x:n v="47710.75"/>
+        <x:n v="1240"/>
+        <x:n v="1846"/>
+        <x:n v="3546"/>
+        <x:n v="3087"/>
+        <x:n v="10054"/>
+        <x:n v="4229.8"/>
+        <x:n v="15052"/>
+        <x:n v="5011"/>
+        <x:n v="12900.75"/>
+        <x:n v="7671.9"/>
+        <x:n v="97698.6"/>
+        <x:n v="3860.85"/>
+        <x:n v="13226.8"/>
+        <x:n v="13935.95"/>
+        <x:n v="12367"/>
+        <x:n v="9793.55"/>
+        <x:n v="2206.85"/>
+        <x:n v="102453.6"/>
+        <x:n v="3153"/>
+        <x:n v="342"/>
+        <x:n v="2692.85"/>
+        <x:n v="28862"/>
+        <x:n v="104"/>
+        <x:n v="9471.95"/>
+        <x:n v="5654.8"/>
+        <x:n v="2356.9"/>
+        <x:n v="54"/>
+        <x:n v="13814.05"/>
+        <x:n v="4178.85"/>
+        <x:n v="5511.75"/>
+        <x:n v="3640"/>
+        <x:n v="3650"/>
+        <x:n v="7868"/>
+        <x:n v="5983"/>
+        <x:n v="6731"/>
+        <x:n v="72089.9"/>
+        <x:n v="716"/>
+        <x:n v="1827"/>
+        <x:n v="7990"/>
+        <x:n v="4205"/>
+        <x:n v="10263.75"/>
+        <x:n v="4029.55"/>
+        <x:n v="12949.7"/>
+        <x:n v="20711.9"/>
+        <x:n v="3975.75"/>
+        <x:n v="8305.95"/>
+        <x:n v="51730.8"/>
+        <x:n v="2099"/>
+        <x:n v="45160.1"/>
+        <x:n v="4774.85"/>
+        <x:n v="64115.75"/>
+        <x:n v="2577.85"/>
+        <x:n v="1999"/>
+        <x:n v="158922.65"/>
+        <x:n v="6935"/>
+        <x:n v="1400"/>
+        <x:n v="304"/>
+        <x:n v="16939.5"/>
+        <x:n v="11568"/>
+        <x:n v="4317.75"/>
+        <x:n v="7134"/>
+        <x:n v="7986.9"/>
+        <x:n v="3304.85"/>
+        <x:n v="17917"/>
+        <x:n v="7423.35"/>
+        <x:n v="9897"/>
+        <x:n v="52729.25"/>
+        <x:n v="24485"/>
+        <x:n v="3065"/>
+        <x:n v="465"/>
+        <x:n v="5037.1"/>
+        <x:n v="7572"/>
+        <x:n v="8939.6"/>
+        <x:n v="13908"/>
+        <x:n v="65"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Tax rate">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="8.5" count="3">
+        <x:n v="4.5"/>
+        <x:n v="0"/>
+        <x:n v="8.5"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Amount paid">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="158922.65" count="184">
+        <x:n v="0"/>
+        <x:n v="7885"/>
+        <x:n v="4807"/>
+        <x:n v="6500"/>
+        <x:n v="4996"/>
+        <x:n v="2679.85"/>
+        <x:n v="5201"/>
+        <x:n v="3115"/>
+        <x:n v="134.85"/>
+        <x:n v="20321.75"/>
+        <x:n v="9955"/>
+        <x:n v="3719"/>
+        <x:n v="10064.65"/>
+        <x:n v="4674"/>
+        <x:n v="6897"/>
+        <x:n v="930"/>
+        <x:n v="2920"/>
+        <x:n v="25210"/>
+        <x:n v="343.8"/>
+        <x:n v="20108"/>
+        <x:n v="559.6"/>
+        <x:n v="12685"/>
+        <x:n v="775"/>
+        <x:n v="1238"/>
+        <x:n v="18532"/>
+        <x:n v="560"/>
+        <x:n v="4110"/>
+        <x:n v="3117"/>
+        <x:n v="10152"/>
+        <x:n v="536.8"/>
+        <x:n v="3632"/>
+        <x:n v="7807"/>
+        <x:n v="971.7"/>
+        <x:n v="12455"/>
+        <x:n v="64050"/>
+        <x:n v="787.8"/>
+        <x:n v="766.8"/>
+        <x:n v="15365"/>
+        <x:n v="7346"/>
+        <x:n v="1809.85"/>
+        <x:n v="6287.85"/>
+        <x:n v="325"/>
+        <x:n v="16788"/>
+        <x:n v="24650"/>
+        <x:n v="14188"/>
+        <x:n v="23406"/>
+        <x:n v="19293.7"/>
+        <x:n v="1975"/>
+        <x:n v="12736"/>
+        <x:n v="2150"/>
+        <x:n v="15355"/>
+        <x:n v="24277.3"/>
+        <x:n v="18320"/>
+        <x:n v="61869.3"/>
+        <x:n v="395"/>
+        <x:n v="17814"/>
+        <x:n v="19812"/>
+        <x:n v="4495"/>
+        <x:n v="31847"/>
+        <x:n v="33829.45"/>
+        <x:n v="22354"/>
+        <x:n v="103041"/>
+        <x:n v="3596"/>
+        <x:n v="19414"/>
+        <x:n v="2195"/>
+        <x:n v="8560"/>
+        <x:n v="17781"/>
+        <x:n v="156"/>
+        <x:n v="79116"/>
+        <x:n v="4445"/>
+        <x:n v="9634"/>
+        <x:n v="30566"/>
+        <x:n v="1416.45"/>
+        <x:n v="11164.8"/>
+        <x:n v="1185"/>
+        <x:n v="14049.95"/>
+        <x:n v="14045"/>
+        <x:n v="2706"/>
+        <x:n v="8507"/>
+        <x:n v="1950"/>
+        <x:n v="76698.75"/>
+        <x:n v="479.8"/>
+        <x:n v="2844"/>
+        <x:n v="39797.7"/>
+        <x:n v="51673.15"/>
+        <x:n v="31219.95"/>
+        <x:n v="3531.8"/>
+        <x:n v="28389"/>
+        <x:n v="203"/>
+        <x:n v="4720.8"/>
+        <x:n v="21614"/>
+        <x:n v="14557.95"/>
+        <x:n v="784.9"/>
+        <x:n v="820"/>
+        <x:n v="44854"/>
+        <x:n v="13945"/>
+        <x:n v="33071"/>
+        <x:n v="6583.8"/>
+        <x:n v="10107"/>
+        <x:n v="25071"/>
+        <x:n v="8294"/>
+        <x:n v="1004.8"/>
+        <x:n v="6300"/>
+        <x:n v="11989.2"/>
+        <x:n v="906"/>
+        <x:n v="2419"/>
+        <x:n v="6675.95"/>
+        <x:n v="2971"/>
+        <x:n v="6785.4"/>
+        <x:n v="47710.75"/>
+        <x:n v="1240"/>
+        <x:n v="1846"/>
+        <x:n v="3546"/>
+        <x:n v="3087"/>
+        <x:n v="10054"/>
+        <x:n v="4229.8"/>
+        <x:n v="15052"/>
+        <x:n v="5011"/>
+        <x:n v="12900.75"/>
+        <x:n v="7671.9"/>
+        <x:n v="97698.6"/>
+        <x:n v="3860.85"/>
+        <x:n v="13226.8"/>
+        <x:n v="13935.95"/>
+        <x:n v="12367"/>
+        <x:n v="9793.55"/>
+        <x:n v="2206.85"/>
+        <x:n v="102453.6"/>
+        <x:n v="3153"/>
+        <x:n v="342"/>
+        <x:n v="2692.85"/>
+        <x:n v="28862"/>
+        <x:n v="104"/>
+        <x:n v="9471.95"/>
+        <x:n v="5654.8"/>
+        <x:n v="2356.9"/>
+        <x:n v="54"/>
+        <x:n v="13814.05"/>
+        <x:n v="4178.85"/>
+        <x:n v="5511.75"/>
+        <x:n v="3640"/>
+        <x:n v="3650"/>
+        <x:n v="7868"/>
+        <x:n v="5983"/>
+        <x:n v="6731"/>
+        <x:n v="72089.9"/>
+        <x:n v="716"/>
+        <x:n v="1827"/>
+        <x:n v="7990"/>
+        <x:n v="4205"/>
+        <x:n v="10263.75"/>
+        <x:n v="4029.55"/>
+        <x:n v="12949.7"/>
+        <x:n v="20711.9"/>
+        <x:n v="3975.75"/>
+        <x:n v="8305.95"/>
+        <x:n v="51730.8"/>
+        <x:n v="2099"/>
+        <x:n v="45160.1"/>
+        <x:n v="4774.85"/>
+        <x:n v="64115.75"/>
+        <x:n v="2577.85"/>
+        <x:n v="1999"/>
+        <x:n v="158922.65"/>
+        <x:n v="6935"/>
+        <x:n v="1400"/>
+        <x:n v="304"/>
+        <x:n v="16939.5"/>
+        <x:n v="11568"/>
+        <x:n v="4317.75"/>
+        <x:n v="7134"/>
+        <x:n v="7986.9"/>
+        <x:n v="3304.85"/>
+        <x:n v="17917"/>
+        <x:n v="7423.35"/>
+        <x:n v="9897"/>
+        <x:n v="52729.25"/>
+        <x:n v="24485"/>
+        <x:n v="3065"/>
+        <x:n v="465"/>
+        <x:n v="5037.1"/>
+        <x:n v="7572"/>
+        <x:n v="8939.6"/>
+        <x:n v="13908"/>
+      </x:sharedItems>
+    </x:cacheField>
+  </x:cacheFields>
+</x:pivotCacheDefinition>
+</file>
+
+<file path=pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -8724,10 +8724,10 @@
     <x:col min="6" max="6" width="13.832031" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="4" spans="1:6" ht="11.25" customHeight="1"/>
-    <x:row r="5" spans="1:6" ht="25.5" customHeight="1"/>
-    <x:row r="8" spans="1:6" ht="12" customHeight="1"/>
-    <x:row r="9" spans="1:6" ht="12.75" customHeight="1"/>
+    <x:row r="4" ht="11.25" customHeight="1"/>
+    <x:row r="5" ht="25.5" customHeight="1"/>
+    <x:row r="8" ht="12" customHeight="1"/>
+    <x:row r="9" ht="12.75" customHeight="1"/>
   </x:sheetData>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -3945,7 +3945,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr codeName="Лист3">
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
     <x:pageSetUpPr fitToPage="1"/>
@@ -8709,7 +8709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr codeName="Sheet1">
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -8739,7 +8739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -9652,5 +9652,1851 @@
 </file>
 
 <file path=pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Credit"/>
+    <s v="1003"/>
+    <d v="1988-05-03T00:00:00"/>
+    <n v="1250"/>
+    <n v="4.5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Davy Jones' Locker"/>
+    <s v="Check"/>
+    <s v="1004"/>
+    <d v="1988-04-18T00:00:00"/>
+    <n v="7885"/>
+    <n v="0"/>
+    <n v="7885"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Visa"/>
+    <s v="1005"/>
+    <d v="1988-01-21T00:00:00"/>
+    <n v="4807"/>
+    <n v="0"/>
+    <n v="4807"/>
+  </r>
+  <r>
+    <s v="Blue Jack Aqua Center"/>
+    <s v="Visa"/>
+    <s v="1006"/>
+    <d v="1988-11-07T00:00:00"/>
+    <n v="31987"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Visa"/>
+    <s v="1007"/>
+    <d v="1988-05-02T00:00:00"/>
+    <n v="6500"/>
+    <n v="0"/>
+    <n v="6500"/>
+  </r>
+  <r>
+    <s v="Ocean Paradise"/>
+    <s v="Visa"/>
+    <s v="1008"/>
+    <d v="1988-05-04T00:00:00"/>
+    <n v="1449.5"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="COD"/>
+    <s v="1009"/>
+    <d v="1988-05-12T00:00:00"/>
+    <n v="5587"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Marmot Divers Club"/>
+    <s v="COD"/>
+    <s v="1010"/>
+    <d v="1988-05-12T00:00:00"/>
+    <n v="4996"/>
+    <n v="0"/>
+    <n v="4996"/>
+  </r>
+  <r>
+    <s v="The Depth Charge"/>
+    <s v="COD"/>
+    <s v="1011"/>
+    <d v="1988-05-19T00:00:00"/>
+    <n v="2679.85"/>
+    <n v="0"/>
+    <n v="2679.85"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Credit"/>
+    <s v="1012"/>
+    <d v="1988-05-20T00:00:00"/>
+    <n v="5201"/>
+    <n v="0"/>
+    <n v="5201"/>
+  </r>
+  <r>
+    <s v="Makai SCUBA Club"/>
+    <s v="Credit"/>
+    <s v="1013"/>
+    <d v="1988-05-26T00:00:00"/>
+    <n v="3115"/>
+    <n v="0"/>
+    <n v="3115"/>
+  </r>
+  <r>
+    <s v="Action Club"/>
+    <s v="Credit"/>
+    <s v="1014"/>
+    <d v="1988-05-26T00:00:00"/>
+    <n v="134.85"/>
+    <n v="0"/>
+    <n v="134.85"/>
+  </r>
+  <r>
+    <s v="Jamaica SCUBA Centre"/>
+    <s v="MC"/>
+    <s v="1015"/>
+    <d v="1988-05-26T00:00:00"/>
+    <n v="20321.75"/>
+    <n v="0"/>
+    <n v="20321.75"/>
+  </r>
+  <r>
+    <s v="Island Finders"/>
+    <s v="AmEx"/>
+    <s v="1016"/>
+    <d v="1988-06-03T00:00:00"/>
+    <n v="2605"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="Check"/>
+    <s v="1017"/>
+    <d v="1988-06-13T00:00:00"/>
+    <n v="10195"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Blue Sports Club"/>
+    <s v="Check"/>
+    <s v="1018"/>
+    <d v="1988-06-19T00:00:00"/>
+    <n v="5256"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Frank's Divers Supply"/>
+    <s v="Credit"/>
+    <s v="1019"/>
+    <d v="1988-06-25T00:00:00"/>
+    <n v="20602"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Davy Jones' Locker"/>
+    <s v="Credit"/>
+    <s v="1020"/>
+    <d v="1988-06-25T00:00:00"/>
+    <n v="9955"/>
+    <n v="0"/>
+    <n v="9955"/>
+  </r>
+  <r>
+    <s v="SCUBA Heaven"/>
+    <s v="Credit"/>
+    <s v="1021"/>
+    <d v="1988-06-25T00:00:00"/>
+    <n v="3719"/>
+    <n v="0"/>
+    <n v="3719"/>
+  </r>
+  <r>
+    <s v="SCUBA Heaven"/>
+    <s v="Credit"/>
+    <s v="1022"/>
+    <d v="1988-07-01T00:00:00"/>
+    <n v="10064.65"/>
+    <n v="0"/>
+    <n v="10064.65"/>
+  </r>
+  <r>
+    <s v="Kauai Dive Shoppe"/>
+    <s v="Check"/>
+    <s v="1023"/>
+    <d v="1988-07-02T00:00:00"/>
+    <n v="4674"/>
+    <n v="0"/>
+    <n v="4674"/>
+  </r>
+  <r>
+    <s v="Fisherman's Eye"/>
+    <s v="Check"/>
+    <s v="1024"/>
+    <d v="1988-07-03T00:00:00"/>
+    <n v="6897"/>
+    <n v="0"/>
+    <n v="6897"/>
+  </r>
+  <r>
+    <s v="Ocean Paradise"/>
+    <s v="AmEx"/>
+    <s v="1025"/>
+    <d v="1988-07-04T00:00:00"/>
+    <n v="930"/>
+    <n v="0"/>
+    <n v="930"/>
+  </r>
+  <r>
+    <s v="Makai SCUBA Club"/>
+    <s v="AmEx"/>
+    <s v="1026"/>
+    <d v="1988-07-08T00:00:00"/>
+    <n v="2920"/>
+    <n v="0"/>
+    <n v="2920"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Visa"/>
+    <s v="1027"/>
+    <d v="1988-07-08T00:00:00"/>
+    <n v="25210"/>
+    <n v="0"/>
+    <n v="25210"/>
+  </r>
+  <r>
+    <s v="Jamaica SCUBA Centre"/>
+    <s v="Visa"/>
+    <s v="1028"/>
+    <d v="1988-07-08T00:00:00"/>
+    <n v="343.8"/>
+    <n v="0"/>
+    <n v="343.8"/>
+  </r>
+  <r>
+    <s v="Action Club"/>
+    <s v="MC"/>
+    <s v="1029"/>
+    <d v="1988-07-19T00:00:00"/>
+    <n v="20108"/>
+    <n v="0"/>
+    <n v="20108"/>
+  </r>
+  <r>
+    <s v="Marina SCUBA Center"/>
+    <s v="MC"/>
+    <s v="1030"/>
+    <d v="1988-07-26T00:00:00"/>
+    <n v="559.6"/>
+    <n v="0"/>
+    <n v="559.6"/>
+  </r>
+  <r>
+    <s v="Blue Sports Club"/>
+    <s v="Credit"/>
+    <s v="1031"/>
+    <d v="1988-08-01T00:00:00"/>
+    <n v="12685"/>
+    <n v="0"/>
+    <n v="12685"/>
+  </r>
+  <r>
+    <s v="SCUBA Heaven"/>
+    <s v="Credit"/>
+    <s v="1032"/>
+    <d v="1988-08-01T00:00:00"/>
+    <n v="775"/>
+    <n v="0"/>
+    <n v="775"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Cash"/>
+    <s v="1033"/>
+    <d v="1988-08-02T00:00:00"/>
+    <n v="1238"/>
+    <n v="0"/>
+    <n v="1238"/>
+  </r>
+  <r>
+    <s v="Island Finders"/>
+    <s v="Check"/>
+    <s v="1034"/>
+    <d v="1988-08-14T00:00:00"/>
+    <n v="18532"/>
+    <n v="0"/>
+    <n v="18532"/>
+  </r>
+  <r>
+    <s v="The Depth Charge"/>
+    <s v="Credit"/>
+    <s v="1035"/>
+    <d v="1988-08-17T00:00:00"/>
+    <n v="560"/>
+    <n v="0"/>
+    <n v="560"/>
+  </r>
+  <r>
+    <s v="Tora Tora Tora"/>
+    <s v="Credit"/>
+    <s v="1036"/>
+    <d v="1988-08-26T00:00:00"/>
+    <n v="4110"/>
+    <n v="0"/>
+    <n v="4110"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="Credit"/>
+    <s v="1037"/>
+    <d v="1988-08-27T00:00:00"/>
+    <n v="3117"/>
+    <n v="0"/>
+    <n v="3117"/>
+  </r>
+  <r>
+    <s v="Action Club"/>
+    <s v="Visa"/>
+    <s v="1038"/>
+    <d v="1988-08-27T00:00:00"/>
+    <n v="10152"/>
+    <n v="0"/>
+    <n v="10152"/>
+  </r>
+  <r>
+    <s v="Action Diver Supply"/>
+    <s v="Visa"/>
+    <s v="1039"/>
+    <d v="1988-09-01T00:00:00"/>
+    <n v="536.8"/>
+    <n v="0"/>
+    <n v="536.8"/>
+  </r>
+  <r>
+    <s v="Waterspout SCUBA Center"/>
+    <s v="Visa"/>
+    <s v="1040"/>
+    <d v="1988-09-05T00:00:00"/>
+    <n v="3632"/>
+    <n v="0"/>
+    <n v="3632"/>
+  </r>
+  <r>
+    <s v="Jamaica Sun, Inc."/>
+    <s v="AmEx"/>
+    <s v="1041"/>
+    <d v="1988-09-17T00:00:00"/>
+    <n v="7807"/>
+    <n v="0"/>
+    <n v="7807"/>
+  </r>
+  <r>
+    <s v="Blue Glass Happiness"/>
+    <s v="AmEx"/>
+    <s v="1042"/>
+    <d v="1988-09-25T00:00:00"/>
+    <n v="971.7"/>
+    <n v="0"/>
+    <n v="971.7"/>
+  </r>
+  <r>
+    <s v="Princess Island SCUBA"/>
+    <s v="Credit"/>
+    <s v="1043"/>
+    <d v="1988-10-01T00:00:00"/>
+    <n v="12455"/>
+    <n v="0"/>
+    <n v="12455"/>
+  </r>
+  <r>
+    <s v="Ocean Adventures"/>
+    <s v="Credit"/>
+    <s v="1044"/>
+    <d v="1988-10-09T00:00:00"/>
+    <n v="64050"/>
+    <n v="0"/>
+    <n v="64050"/>
+  </r>
+  <r>
+    <s v="Neptune's Trident Supply"/>
+    <s v="Credit"/>
+    <s v="1045"/>
+    <d v="1988-10-17T00:00:00"/>
+    <n v="787.8"/>
+    <n v="0"/>
+    <n v="787.8"/>
+  </r>
+  <r>
+    <s v="Divers of Corfu, Inc."/>
+    <s v="Check"/>
+    <s v="1046"/>
+    <d v="1988-11-13T00:00:00"/>
+    <n v="766.8"/>
+    <n v="0"/>
+    <n v="766.8"/>
+  </r>
+  <r>
+    <s v="Ocean Adventures"/>
+    <s v="Cash"/>
+    <s v="1047"/>
+    <d v="1988-11-28T00:00:00"/>
+    <n v="15365"/>
+    <n v="0"/>
+    <n v="15365"/>
+  </r>
+  <r>
+    <s v="Divers-for-Hire"/>
+    <s v="Visa"/>
+    <s v="1048"/>
+    <d v="1988-12-03T00:00:00"/>
+    <n v="7346"/>
+    <n v="0"/>
+    <n v="7346"/>
+  </r>
+  <r>
+    <s v="Neptune's Trident Supply"/>
+    <s v="MC"/>
+    <s v="1049"/>
+    <d v="1988-12-14T00:00:00"/>
+    <n v="1809.85"/>
+    <n v="0"/>
+    <n v="1809.85"/>
+  </r>
+  <r>
+    <s v="Underwater Sports Co."/>
+    <s v="AmEx"/>
+    <s v="1050"/>
+    <d v="1988-12-25T00:00:00"/>
+    <n v="6287.85"/>
+    <n v="0"/>
+    <n v="6287.85"/>
+  </r>
+  <r>
+    <s v="Shangri-La Sports Center"/>
+    <s v="Credit"/>
+    <s v="1051"/>
+    <d v="1989-01-05T00:00:00"/>
+    <n v="325"/>
+    <n v="0"/>
+    <n v="325"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Credit"/>
+    <s v="1052"/>
+    <d v="1989-01-07T00:00:00"/>
+    <n v="16788"/>
+    <n v="0"/>
+    <n v="16788"/>
+  </r>
+  <r>
+    <s v="The Diving Company"/>
+    <s v="Credit"/>
+    <s v="1053"/>
+    <d v="1989-01-16T00:00:00"/>
+    <n v="24650"/>
+    <n v="0"/>
+    <n v="24650"/>
+  </r>
+  <r>
+    <s v="Divers-for-Hire"/>
+    <s v="Visa"/>
+    <s v="1054"/>
+    <d v="1989-02-01T00:00:00"/>
+    <n v="14188"/>
+    <n v="0"/>
+    <n v="14188"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Credit"/>
+    <s v="1055"/>
+    <d v="1989-02-05T00:00:00"/>
+    <n v="23406"/>
+    <n v="0"/>
+    <n v="23406"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="MC"/>
+    <s v="1056"/>
+    <d v="1989-02-09T00:00:00"/>
+    <n v="19293.7"/>
+    <n v="0"/>
+    <n v="19293.7"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Credit"/>
+    <s v="1057"/>
+    <d v="1989-02-19T00:00:00"/>
+    <n v="1975"/>
+    <n v="0"/>
+    <n v="1975"/>
+  </r>
+  <r>
+    <s v="Blue Sports Club"/>
+    <s v="Credit"/>
+    <s v="1058"/>
+    <d v="1989-02-22T00:00:00"/>
+    <n v="12736"/>
+    <n v="0"/>
+    <n v="12736"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Cash"/>
+    <s v="1059"/>
+    <d v="1989-02-25T00:00:00"/>
+    <n v="2150"/>
+    <n v="8.5"/>
+    <n v="2150"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="Check"/>
+    <s v="1060"/>
+    <d v="1989-03-01T00:00:00"/>
+    <n v="15355"/>
+    <n v="0"/>
+    <n v="15355"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Credit"/>
+    <s v="1061"/>
+    <d v="1989-03-04T00:00:00"/>
+    <n v="24277.3"/>
+    <n v="0"/>
+    <n v="24277.3"/>
+  </r>
+  <r>
+    <s v="Blue Sports Club"/>
+    <s v="Credit"/>
+    <s v="1062"/>
+    <d v="1989-03-09T00:00:00"/>
+    <n v="18320"/>
+    <n v="0"/>
+    <n v="18320"/>
+  </r>
+  <r>
+    <s v="Gold Coast Supply"/>
+    <s v="Credit"/>
+    <s v="1063"/>
+    <d v="1989-03-14T00:00:00"/>
+    <n v="61869.3"/>
+    <n v="0"/>
+    <n v="61869.3"/>
+  </r>
+  <r>
+    <s v="Blue Sports Club"/>
+    <s v="Credit"/>
+    <s v="1064"/>
+    <d v="1989-03-25T00:00:00"/>
+    <n v="395"/>
+    <n v="0"/>
+    <n v="395"/>
+  </r>
+  <r>
+    <s v="Aquatic Drama"/>
+    <s v="Visa"/>
+    <s v="1065"/>
+    <d v="1989-03-26T00:00:00"/>
+    <n v="17814"/>
+    <n v="0"/>
+    <n v="17814"/>
+  </r>
+  <r>
+    <s v="Catamaran Dive Club"/>
+    <s v="Visa"/>
+    <s v="1066"/>
+    <d v="1989-03-27T00:00:00"/>
+    <n v="19812"/>
+    <n v="0"/>
+    <n v="19812"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Visa"/>
+    <s v="1067"/>
+    <d v="1989-04-02T00:00:00"/>
+    <n v="4495"/>
+    <n v="0"/>
+    <n v="4495"/>
+  </r>
+  <r>
+    <s v="On-Target SCUBA"/>
+    <s v="MC"/>
+    <s v="1068"/>
+    <d v="1989-04-04T00:00:00"/>
+    <n v="31847"/>
+    <n v="0"/>
+    <n v="31847"/>
+  </r>
+  <r>
+    <s v="George Bean &amp; Co."/>
+    <s v="Credit"/>
+    <s v="1069"/>
+    <d v="1989-04-06T00:00:00"/>
+    <n v="33829.45"/>
+    <n v="0"/>
+    <n v="33829.45"/>
+  </r>
+  <r>
+    <s v="Underwater SCUBA Company"/>
+    <s v="Credit"/>
+    <s v="1070"/>
+    <d v="1989-04-08T00:00:00"/>
+    <n v="22354"/>
+    <n v="0"/>
+    <n v="22354"/>
+  </r>
+  <r>
+    <s v="The Depth Charge"/>
+    <s v="Cash"/>
+    <s v="1071"/>
+    <d v="1989-04-10T00:00:00"/>
+    <n v="103041"/>
+    <n v="0"/>
+    <n v="103041"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Cash"/>
+    <s v="1072"/>
+    <d v="1989-04-12T00:00:00"/>
+    <n v="3596"/>
+    <n v="0"/>
+    <n v="3596"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="MC"/>
+    <s v="1073"/>
+    <d v="1989-04-16T00:00:00"/>
+    <n v="19414"/>
+    <n v="0"/>
+    <n v="19414"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="MC"/>
+    <s v="1074"/>
+    <d v="1989-04-20T00:00:00"/>
+    <n v="2195"/>
+    <n v="0"/>
+    <n v="2195"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="MC"/>
+    <s v="1075"/>
+    <d v="1989-04-22T00:00:00"/>
+    <n v="8560"/>
+    <n v="0"/>
+    <n v="8560"/>
+  </r>
+  <r>
+    <s v="Kauai Dive Shoppe"/>
+    <s v="Visa"/>
+    <s v="1076"/>
+    <d v="1989-04-26T00:00:00"/>
+    <n v="17781"/>
+    <n v="0"/>
+    <n v="17781"/>
+  </r>
+  <r>
+    <s v="Marmot Divers Club"/>
+    <s v="Credit"/>
+    <s v="1077"/>
+    <d v="1989-05-01T00:00:00"/>
+    <n v="156"/>
+    <n v="0"/>
+    <n v="156"/>
+  </r>
+  <r>
+    <s v="Divers of Blue-green"/>
+    <s v="Credit"/>
+    <s v="1078"/>
+    <d v="1989-05-02T00:00:00"/>
+    <n v="79116"/>
+    <n v="0"/>
+    <n v="79116"/>
+  </r>
+  <r>
+    <s v="Blue Jack Aqua Center"/>
+    <s v="Credit"/>
+    <s v="1079"/>
+    <d v="1989-05-04T00:00:00"/>
+    <n v="4445"/>
+    <n v="0"/>
+    <n v="4445"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Credit"/>
+    <s v="1080"/>
+    <d v="1989-05-06T00:00:00"/>
+    <n v="9634"/>
+    <n v="0"/>
+    <n v="9634"/>
+  </r>
+  <r>
+    <s v="Gold Coast Supply"/>
+    <s v="AmEx"/>
+    <s v="1081"/>
+    <d v="1989-05-08T00:00:00"/>
+    <n v="30566"/>
+    <n v="0"/>
+    <n v="30566"/>
+  </r>
+  <r>
+    <s v="Marmot Divers Club"/>
+    <s v="AmEx"/>
+    <s v="1082"/>
+    <d v="1989-05-10T00:00:00"/>
+    <n v="1416.45"/>
+    <n v="0"/>
+    <n v="1416.45"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Cash"/>
+    <s v="1083"/>
+    <d v="1989-05-10T00:00:00"/>
+    <n v="11164.8"/>
+    <n v="0"/>
+    <n v="11164.8"/>
+  </r>
+  <r>
+    <s v="Island Finders"/>
+    <s v="Cash"/>
+    <s v="1084"/>
+    <d v="1989-05-12T00:00:00"/>
+    <n v="1185"/>
+    <n v="0"/>
+    <n v="1185"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="Cash"/>
+    <s v="1086"/>
+    <d v="1989-05-19T00:00:00"/>
+    <n v="14049.95"/>
+    <n v="0"/>
+    <n v="14049.95"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Credit"/>
+    <s v="1087"/>
+    <d v="1989-05-21T00:00:00"/>
+    <n v="14045"/>
+    <n v="0"/>
+    <n v="14045"/>
+  </r>
+  <r>
+    <s v="Fisherman's Eye"/>
+    <s v="Credit"/>
+    <s v="1089"/>
+    <d v="1989-05-23T00:00:00"/>
+    <n v="2706"/>
+    <n v="0"/>
+    <n v="2706"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="Credit"/>
+    <s v="1090"/>
+    <d v="1989-05-26T00:00:00"/>
+    <n v="8507"/>
+    <n v="0"/>
+    <n v="8507"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Credit"/>
+    <s v="1091"/>
+    <d v="1989-06-01T00:00:00"/>
+    <n v="1950"/>
+    <n v="0"/>
+    <n v="1950"/>
+  </r>
+  <r>
+    <s v="Norwest'er SCUBA Limited"/>
+    <s v="Visa"/>
+    <s v="1092"/>
+    <d v="1989-06-01T00:00:00"/>
+    <n v="76698.75"/>
+    <n v="0"/>
+    <n v="76698.75"/>
+  </r>
+  <r>
+    <s v="Island Finders"/>
+    <s v="Visa"/>
+    <s v="1093"/>
+    <d v="1989-06-02T00:00:00"/>
+    <n v="479.8"/>
+    <n v="0"/>
+    <n v="479.8"/>
+  </r>
+  <r>
+    <s v="Safari Under the Sea"/>
+    <s v="MC"/>
+    <s v="1094"/>
+    <d v="1989-06-04T00:00:00"/>
+    <n v="4113.75"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Davy Jones' Locker"/>
+    <s v="MC"/>
+    <s v="1095"/>
+    <d v="1989-06-06T00:00:00"/>
+    <n v="7531.75"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Kirk Enterprises"/>
+    <s v="MC"/>
+    <s v="1096"/>
+    <d v="1989-06-09T00:00:00"/>
+    <n v="123740"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Marina SCUBA Center"/>
+    <s v="MC"/>
+    <s v="1097"/>
+    <d v="1989-06-12T00:00:00"/>
+    <n v="12953.6"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Divers of Corfu, Inc."/>
+    <s v="Credit"/>
+    <s v="1098"/>
+    <d v="1989-06-14T00:00:00"/>
+    <n v="472.9"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="Credit"/>
+    <s v="1099"/>
+    <d v="1989-06-16T00:00:00"/>
+    <n v="859.95"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Credit"/>
+    <s v="1100"/>
+    <d v="1989-06-20T00:00:00"/>
+    <n v="6094.8"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Shangri-La Sports Center"/>
+    <s v="Credit"/>
+    <s v="1101"/>
+    <d v="1989-07-04T00:00:00"/>
+    <n v="11629.85"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="Credit"/>
+    <s v="1102"/>
+    <d v="1992-06-06T00:00:00"/>
+    <n v="2844"/>
+    <n v="0"/>
+    <n v="2844"/>
+  </r>
+  <r>
+    <s v="Gold Coast Supply"/>
+    <s v="Credit"/>
+    <s v="1103"/>
+    <d v="1992-07-13T00:00:00"/>
+    <n v="39797.7"/>
+    <n v="0"/>
+    <n v="39797.7"/>
+  </r>
+  <r>
+    <s v="Cayman Divers World Unlimited"/>
+    <s v="Check"/>
+    <s v="1104"/>
+    <d v="1992-07-18T00:00:00"/>
+    <n v="51673.15"/>
+    <n v="0"/>
+    <n v="51673.15"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Visa"/>
+    <s v="1105"/>
+    <d v="1992-07-21T00:00:00"/>
+    <n v="31219.95"/>
+    <n v="0"/>
+    <n v="31219.95"/>
+  </r>
+  <r>
+    <s v="Blue Jack Aqua Center"/>
+    <s v="Visa"/>
+    <s v="1106"/>
+    <d v="1992-09-23T00:00:00"/>
+    <n v="3531.8"/>
+    <n v="0"/>
+    <n v="3531.8"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Visa"/>
+    <s v="1107"/>
+    <d v="1992-10-24T00:00:00"/>
+    <n v="28389"/>
+    <n v="0"/>
+    <n v="28389"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="COD"/>
+    <s v="1109"/>
+    <d v="1992-11-13T00:00:00"/>
+    <n v="203"/>
+    <n v="0"/>
+    <n v="203"/>
+  </r>
+  <r>
+    <s v="The Depth Charge"/>
+    <s v="COD"/>
+    <s v="1111"/>
+    <d v="1992-12-14T00:00:00"/>
+    <n v="4720.8"/>
+    <n v="0"/>
+    <n v="4720.8"/>
+  </r>
+  <r>
+    <s v="On-Target SCUBA"/>
+    <s v="Credit"/>
+    <s v="1112"/>
+    <d v="1993-01-02T00:00:00"/>
+    <n v="5565"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Makai SCUBA Club"/>
+    <s v="Credit"/>
+    <s v="1113"/>
+    <d v="1993-02-12T00:00:00"/>
+    <n v="2514.65"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Underwater Fantasy"/>
+    <s v="MC"/>
+    <s v="1115"/>
+    <d v="1993-03-13T00:00:00"/>
+    <n v="4894.95"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Island Finders"/>
+    <s v="AmEx"/>
+    <s v="1116"/>
+    <d v="1993-03-21T00:00:00"/>
+    <n v="23104"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="Check"/>
+    <s v="1117"/>
+    <d v="1993-04-13T00:00:00"/>
+    <n v="6734.85"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <s v="Blue Sports Club"/>
+    <s v="Check"/>
+    <s v="1118"/>
+    <d v="1993-04-23T00:00:00"/>
+    <n v="21614"/>
+    <n v="0"/>
+    <n v="21614"/>
+  </r>
+  <r>
+    <s v="Tora Tora Tora"/>
+    <s v="Credit"/>
+    <s v="1119"/>
+    <d v="1993-05-15T00:00:00"/>
+    <n v="14557.95"/>
+    <n v="0"/>
+    <n v="14557.95"/>
+  </r>
+  <r>
+    <s v="Davy Jones' Locker"/>
+    <s v="Credit"/>
+    <s v="1120"/>
+    <d v="1993-05-25T00:00:00"/>
+    <n v="784.9"/>
+    <n v="0"/>
+    <n v="784.9"/>
+  </r>
+  <r>
+    <s v="SCUBA Heaven"/>
+    <s v="Credit"/>
+    <s v="1121"/>
+    <d v="1993-06-02T00:00:00"/>
+    <n v="820"/>
+    <n v="0"/>
+    <n v="820"/>
+  </r>
+  <r>
+    <s v="SCUBA Heaven"/>
+    <s v="Credit"/>
+    <s v="1122"/>
+    <d v="1993-07-23T00:00:00"/>
+    <n v="44854"/>
+    <n v="0"/>
+    <n v="44854"/>
+  </r>
+  <r>
+    <s v="Kauai Dive Shoppe"/>
+    <s v="Check"/>
+    <s v="1123"/>
+    <d v="1993-08-24T00:00:00"/>
+    <n v="13945"/>
+    <n v="0"/>
+    <n v="13945"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Check"/>
+    <s v="1124"/>
+    <d v="1993-09-01T00:00:00"/>
+    <n v="33071"/>
+    <n v="0"/>
+    <n v="33071"/>
+  </r>
+  <r>
+    <s v="Ocean Paradise"/>
+    <s v="AmEx"/>
+    <s v="1125"/>
+    <d v="1993-09-04T00:00:00"/>
+    <n v="6583.8"/>
+    <n v="0"/>
+    <n v="6583.8"/>
+  </r>
+  <r>
+    <s v="Makai SCUBA Club"/>
+    <s v="AmEx"/>
+    <s v="1126"/>
+    <d v="1993-10-01T00:00:00"/>
+    <n v="10107"/>
+    <n v="0"/>
+    <n v="10107"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Visa"/>
+    <s v="1127"/>
+    <d v="1993-10-02T00:00:00"/>
+    <n v="25071"/>
+    <n v="0"/>
+    <n v="25071"/>
+  </r>
+  <r>
+    <s v="Jamaica SCUBA Centre"/>
+    <s v="Visa"/>
+    <s v="1128"/>
+    <d v="1993-10-08T00:00:00"/>
+    <n v="8294"/>
+    <n v="0"/>
+    <n v="8294"/>
+  </r>
+  <r>
+    <s v="Action Club"/>
+    <s v="MC"/>
+    <s v="1129"/>
+    <d v="1993-10-19T00:00:00"/>
+    <n v="1004.8"/>
+    <n v="0"/>
+    <n v="1004.8"/>
+  </r>
+  <r>
+    <s v="Divers of Venice"/>
+    <s v="MC"/>
+    <s v="1130"/>
+    <d v="1993-10-26T00:00:00"/>
+    <n v="6300"/>
+    <n v="0"/>
+    <n v="6300"/>
+  </r>
+  <r>
+    <s v="Blue Sports Club"/>
+    <s v="Credit"/>
+    <s v="1131"/>
+    <d v="1993-11-01T00:00:00"/>
+    <n v="11989.2"/>
+    <n v="0"/>
+    <n v="11989.2"/>
+  </r>
+  <r>
+    <s v="SCUBA Heaven"/>
+    <s v="Credit"/>
+    <s v="1132"/>
+    <d v="1993-11-01T00:00:00"/>
+    <n v="906"/>
+    <n v="0"/>
+    <n v="906"/>
+  </r>
+  <r>
+    <s v="Fisherman's Eye"/>
+    <s v="Cash"/>
+    <s v="1133"/>
+    <d v="1993-11-02T00:00:00"/>
+    <n v="2419"/>
+    <n v="0"/>
+    <n v="2419"/>
+  </r>
+  <r>
+    <s v="Central Underwater Supplies"/>
+    <s v="Check"/>
+    <s v="1134"/>
+    <d v="1993-11-14T00:00:00"/>
+    <n v="6675.95"/>
+    <n v="0"/>
+    <n v="6675.95"/>
+  </r>
+  <r>
+    <s v="SCUBA Heaven"/>
+    <s v="Credit"/>
+    <s v="1136"/>
+    <d v="1993-11-27T00:00:00"/>
+    <n v="2971"/>
+    <n v="0"/>
+    <n v="2971"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="Credit"/>
+    <s v="1137"/>
+    <d v="1993-11-27T00:00:00"/>
+    <n v="6785.4"/>
+    <n v="0"/>
+    <n v="6785.4"/>
+  </r>
+  <r>
+    <s v="Ocean Paradise"/>
+    <s v="Visa"/>
+    <s v="1139"/>
+    <d v="1993-12-01T00:00:00"/>
+    <n v="47710.75"/>
+    <n v="0"/>
+    <n v="47710.75"/>
+  </r>
+  <r>
+    <s v="Waterspout SCUBA Center"/>
+    <s v="Visa"/>
+    <s v="1140"/>
+    <d v="1993-12-12T00:00:00"/>
+    <n v="1240"/>
+    <n v="0"/>
+    <n v="1240"/>
+  </r>
+  <r>
+    <s v="Jamaica Sun, Inc."/>
+    <s v="AmEx"/>
+    <s v="1141"/>
+    <d v="1993-12-17T00:00:00"/>
+    <n v="1846"/>
+    <n v="0"/>
+    <n v="1846"/>
+  </r>
+  <r>
+    <s v="Blue Glass Happiness"/>
+    <s v="AmEx"/>
+    <s v="1142"/>
+    <d v="1993-12-25T00:00:00"/>
+    <n v="3546"/>
+    <n v="0"/>
+    <n v="3546"/>
+  </r>
+  <r>
+    <s v="Princess Island SCUBA"/>
+    <s v="Credit"/>
+    <s v="1143"/>
+    <d v="1994-01-01T00:00:00"/>
+    <n v="3087"/>
+    <n v="0"/>
+    <n v="3087"/>
+  </r>
+  <r>
+    <s v="Ocean Adventures"/>
+    <s v="Credit"/>
+    <s v="1144"/>
+    <d v="1994-01-09T00:00:00"/>
+    <n v="10054"/>
+    <n v="0"/>
+    <n v="10054"/>
+  </r>
+  <r>
+    <s v="Neptune's Trident Supply"/>
+    <s v="Credit"/>
+    <s v="1145"/>
+    <d v="1994-01-17T00:00:00"/>
+    <n v="4229.8"/>
+    <n v="0"/>
+    <n v="4229.8"/>
+  </r>
+  <r>
+    <s v="Divers of Corfu, Inc."/>
+    <s v="Check"/>
+    <s v="1146"/>
+    <d v="1994-02-13T00:00:00"/>
+    <n v="15052"/>
+    <n v="0"/>
+    <n v="15052"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Visa"/>
+    <s v="1148"/>
+    <d v="1994-03-03T00:00:00"/>
+    <n v="5011"/>
+    <n v="0"/>
+    <n v="5011"/>
+  </r>
+  <r>
+    <s v="Neptune's Trident Supply"/>
+    <s v="MC"/>
+    <s v="1149"/>
+    <d v="1994-03-14T00:00:00"/>
+    <n v="12900.75"/>
+    <n v="0"/>
+    <n v="12900.75"/>
+  </r>
+  <r>
+    <s v="Underwater Sports Co."/>
+    <s v="AmEx"/>
+    <s v="1150"/>
+    <d v="1994-03-25T00:00:00"/>
+    <n v="7671.9"/>
+    <n v="0"/>
+    <n v="7671.9"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Credit"/>
+    <s v="1152"/>
+    <d v="1994-04-07T00:00:00"/>
+    <n v="97698.6"/>
+    <n v="0"/>
+    <n v="97698.6"/>
+  </r>
+  <r>
+    <s v="Blue Jack Aqua Center"/>
+    <s v="Credit"/>
+    <s v="1153"/>
+    <d v="1994-04-16T00:00:00"/>
+    <n v="3860.85"/>
+    <n v="0"/>
+    <n v="3860.85"/>
+  </r>
+  <r>
+    <s v="The Depth Charge"/>
+    <s v="Visa"/>
+    <s v="1154"/>
+    <d v="1994-05-01T00:00:00"/>
+    <n v="13226.8"/>
+    <n v="0"/>
+    <n v="13226.8"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Credit"/>
+    <s v="1155"/>
+    <d v="1994-05-05T00:00:00"/>
+    <n v="13935.95"/>
+    <n v="0"/>
+    <n v="13935.95"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="MC"/>
+    <s v="1156"/>
+    <d v="1994-05-09T00:00:00"/>
+    <n v="12367"/>
+    <n v="0"/>
+    <n v="12367"/>
+  </r>
+  <r>
+    <s v="Larry's Diving School"/>
+    <s v="Credit"/>
+    <s v="1158"/>
+    <d v="1994-05-22T00:00:00"/>
+    <n v="9793.55"/>
+    <n v="0"/>
+    <n v="9793.55"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="Check"/>
+    <s v="1160"/>
+    <d v="1994-06-01T00:00:00"/>
+    <n v="2206.85"/>
+    <n v="0"/>
+    <n v="2206.85"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Credit"/>
+    <s v="1161"/>
+    <d v="1994-06-04T00:00:00"/>
+    <n v="102453.6"/>
+    <n v="0"/>
+    <n v="102453.6"/>
+  </r>
+  <r>
+    <s v="Blue Sports Club"/>
+    <s v="Credit"/>
+    <s v="1162"/>
+    <d v="1994-06-09T00:00:00"/>
+    <n v="3153"/>
+    <n v="0"/>
+    <n v="3153"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Credit"/>
+    <s v="1163"/>
+    <d v="1994-06-14T00:00:00"/>
+    <n v="342"/>
+    <n v="0"/>
+    <n v="342"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="Visa"/>
+    <s v="1165"/>
+    <d v="1994-06-26T00:00:00"/>
+    <n v="2692.85"/>
+    <n v="0"/>
+    <n v="2692.85"/>
+  </r>
+  <r>
+    <s v="Catamaran Dive Club"/>
+    <s v="Visa"/>
+    <s v="1166"/>
+    <d v="1994-07-01T00:00:00"/>
+    <n v="28862"/>
+    <n v="0"/>
+    <n v="28862"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="MC"/>
+    <s v="1168"/>
+    <d v="1994-07-04T00:00:00"/>
+    <n v="104"/>
+    <n v="0"/>
+    <n v="104"/>
+  </r>
+  <r>
+    <s v="Kauai Dive Shoppe"/>
+    <s v="Credit"/>
+    <s v="1169"/>
+    <d v="1994-07-06T00:00:00"/>
+    <n v="9471.95"/>
+    <n v="0"/>
+    <n v="9471.95"/>
+  </r>
+  <r>
+    <s v="Marmot Divers Club"/>
+    <s v="Credit"/>
+    <s v="1170"/>
+    <d v="1994-07-08T00:00:00"/>
+    <n v="5654.8"/>
+    <n v="0"/>
+    <n v="5654.8"/>
+  </r>
+  <r>
+    <s v="The Depth Charge"/>
+    <s v="Cash"/>
+    <s v="1171"/>
+    <d v="1994-07-10T00:00:00"/>
+    <n v="2356.9"/>
+    <n v="0"/>
+    <n v="2356.9"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="MC"/>
+    <s v="1173"/>
+    <d v="1994-07-16T00:00:00"/>
+    <n v="54"/>
+    <n v="0"/>
+    <n v="54"/>
+  </r>
+  <r>
+    <s v="San Pablo Dive Center"/>
+    <s v="MC"/>
+    <s v="1175"/>
+    <d v="1994-07-22T00:00:00"/>
+    <n v="13814.05"/>
+    <n v="0"/>
+    <n v="13814.05"/>
+  </r>
+  <r>
+    <s v="Kauai Dive Shoppe"/>
+    <s v="Visa"/>
+    <s v="1176"/>
+    <d v="1994-07-26T00:00:00"/>
+    <n v="4178.85"/>
+    <n v="0"/>
+    <n v="4178.85"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="Credit"/>
+    <s v="1178"/>
+    <d v="1994-08-02T00:00:00"/>
+    <n v="5511.75"/>
+    <n v="0"/>
+    <n v="5511.75"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Credit"/>
+    <s v="1180"/>
+    <d v="1994-08-06T00:00:00"/>
+    <n v="3640"/>
+    <n v="0"/>
+    <n v="3640"/>
+  </r>
+  <r>
+    <s v="On-Target SCUBA"/>
+    <s v="Cash"/>
+    <s v="1183"/>
+    <d v="1994-08-10T00:00:00"/>
+    <n v="3650"/>
+    <n v="0"/>
+    <n v="3650"/>
+  </r>
+  <r>
+    <s v="Tora Tora Tora"/>
+    <s v="MC"/>
+    <s v="1195"/>
+    <d v="1994-09-06T00:00:00"/>
+    <n v="7868"/>
+    <n v="0"/>
+    <n v="7868"/>
+  </r>
+  <r>
+    <s v="Kirk Enterprises"/>
+    <s v="MC"/>
+    <s v="1196"/>
+    <d v="1994-09-08T00:00:00"/>
+    <n v="5983"/>
+    <n v="0"/>
+    <n v="5983"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="MC"/>
+    <s v="1197"/>
+    <d v="1994-09-12T00:00:00"/>
+    <n v="6731"/>
+    <n v="0"/>
+    <n v="6731"/>
+  </r>
+  <r>
+    <s v="Divers of Corfu, Inc."/>
+    <s v="Credit"/>
+    <s v="1198"/>
+    <d v="1994-09-14T00:00:00"/>
+    <n v="72089.9"/>
+    <n v="0"/>
+    <n v="72089.9"/>
+  </r>
+  <r>
+    <s v="Safari Under the Sea"/>
+    <s v="Credit"/>
+    <s v="1199"/>
+    <d v="1994-09-16T00:00:00"/>
+    <n v="716"/>
+    <n v="0"/>
+    <n v="716"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Credit"/>
+    <s v="1200"/>
+    <d v="1994-09-20T00:00:00"/>
+    <n v="1827"/>
+    <n v="0"/>
+    <n v="1827"/>
+  </r>
+  <r>
+    <s v="Professional Divers, Ltd."/>
+    <s v="Credit"/>
+    <s v="1201"/>
+    <d v="1994-10-04T00:00:00"/>
+    <n v="7990"/>
+    <n v="0"/>
+    <n v="7990"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="Credit"/>
+    <s v="1202"/>
+    <d v="1994-10-06T00:00:00"/>
+    <n v="4205"/>
+    <n v="0"/>
+    <n v="4205"/>
+  </r>
+  <r>
+    <s v="American SCUBA Supply"/>
+    <s v="Check"/>
+    <s v="1204"/>
+    <d v="1994-10-18T00:00:00"/>
+    <n v="10263.75"/>
+    <n v="0"/>
+    <n v="10263.75"/>
+  </r>
+  <r>
+    <s v="Catamaran Dive Club"/>
+    <s v="Visa"/>
+    <s v="1205"/>
+    <d v="1994-10-21T00:00:00"/>
+    <n v="4029.55"/>
+    <n v="0"/>
+    <n v="4029.55"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Visa"/>
+    <s v="1207"/>
+    <d v="1994-11-11T00:00:00"/>
+    <n v="12949.7"/>
+    <n v="0"/>
+    <n v="12949.7"/>
+  </r>
+  <r>
+    <s v="Fantastique Aquatica"/>
+    <s v="COD"/>
+    <s v="1209"/>
+    <d v="1994-11-12T00:00:00"/>
+    <n v="20711.9"/>
+    <n v="0"/>
+    <n v="20711.9"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Credit"/>
+    <s v="1212"/>
+    <d v="1994-11-14T00:00:00"/>
+    <n v="3975.75"/>
+    <n v="0"/>
+    <n v="3975.75"/>
+  </r>
+  <r>
+    <s v="Jamaica SCUBA Centre"/>
+    <s v="MC"/>
+    <s v="1215"/>
+    <d v="1994-11-16T00:00:00"/>
+    <n v="8305.95"/>
+    <n v="0"/>
+    <n v="8305.95"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="Check"/>
+    <s v="1217"/>
+    <d v="1994-11-22T00:00:00"/>
+    <n v="51730.8"/>
+    <n v="0"/>
+    <n v="51730.8"/>
+  </r>
+  <r>
+    <s v="SCUBA Heaven"/>
+    <s v="Credit"/>
+    <s v="1221"/>
+    <d v="1994-11-23T00:00:00"/>
+    <n v="2099"/>
+    <n v="0"/>
+    <n v="2099"/>
+  </r>
+  <r>
+    <s v="Underwater Sports Co."/>
+    <s v="AmEx"/>
+    <s v="1250"/>
+    <d v="1994-11-24T00:00:00"/>
+    <n v="45160.1"/>
+    <n v="0"/>
+    <n v="45160.1"/>
+  </r>
+  <r>
+    <s v="Blue Jack Aqua Center"/>
+    <s v="Credit"/>
+    <s v="1253"/>
+    <d v="1994-11-26T00:00:00"/>
+    <n v="4774.85"/>
+    <n v="0"/>
+    <n v="4774.85"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="Credit"/>
+    <s v="1255"/>
+    <d v="1994-12-09T00:00:00"/>
+    <n v="64115.75"/>
+    <n v="0"/>
+    <n v="64115.75"/>
+  </r>
+  <r>
+    <s v="Divers of Blue-green"/>
+    <s v="Check"/>
+    <s v="1260"/>
+    <d v="1994-12-10T00:00:00"/>
+    <n v="2577.85"/>
+    <n v="0"/>
+    <n v="2577.85"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Credit"/>
+    <s v="1261"/>
+    <d v="1994-12-11T00:00:00"/>
+    <n v="1999"/>
+    <n v="0"/>
+    <n v="1999"/>
+  </r>
+  <r>
+    <s v="American SCUBA Supply"/>
+    <s v="Credit"/>
+    <s v="1263"/>
+    <d v="1994-12-14T00:00:00"/>
+    <n v="158922.65"/>
+    <n v="0"/>
+    <n v="158922.65"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Visa"/>
+    <s v="1266"/>
+    <d v="1994-12-15T00:00:00"/>
+    <n v="6935"/>
+    <n v="0"/>
+    <n v="6935"/>
+  </r>
+  <r>
+    <s v="Kauai Dive Shoppe"/>
+    <s v="Credit"/>
+    <s v="1269"/>
+    <d v="1994-12-16T00:00:00"/>
+    <n v="1400"/>
+    <n v="0"/>
+    <n v="1400"/>
+  </r>
+  <r>
+    <s v="The Depth Charge"/>
+    <s v="Cash"/>
+    <s v="1271"/>
+    <d v="1994-12-20T00:00:00"/>
+    <n v="304"/>
+    <n v="0"/>
+    <n v="304"/>
+  </r>
+  <r>
+    <s v="Sight Diver"/>
+    <s v="MC"/>
+    <s v="1275"/>
+    <d v="1994-12-22T00:00:00"/>
+    <n v="16939.5"/>
+    <n v="0"/>
+    <n v="16939.5"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="Credit"/>
+    <s v="1278"/>
+    <d v="1994-12-23T00:00:00"/>
+    <n v="11568"/>
+    <n v="0"/>
+    <n v="11568"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Credit"/>
+    <s v="1280"/>
+    <d v="1994-12-26T00:00:00"/>
+    <n v="4317.75"/>
+    <n v="0"/>
+    <n v="4317.75"/>
+  </r>
+  <r>
+    <s v="Blue Sports"/>
+    <s v="Cash"/>
+    <s v="1283"/>
+    <d v="1994-12-30T00:00:00"/>
+    <n v="7134"/>
+    <n v="0"/>
+    <n v="7134"/>
+  </r>
+  <r>
+    <s v="Cayman Divers World Unlimited"/>
+    <s v="Visa"/>
+    <s v="1292"/>
+    <d v="1995-01-01T00:00:00"/>
+    <n v="7986.9"/>
+    <n v="0"/>
+    <n v="7986.9"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="MC"/>
+    <s v="1294"/>
+    <d v="1995-01-04T00:00:00"/>
+    <n v="3304.85"/>
+    <n v="0"/>
+    <n v="3304.85"/>
+  </r>
+  <r>
+    <s v="Davy Jones' Locker"/>
+    <s v="MC"/>
+    <s v="1295"/>
+    <d v="1995-01-06T00:00:00"/>
+    <n v="17917"/>
+    <n v="0"/>
+    <n v="17917"/>
+  </r>
+  <r>
+    <s v="Vashon Ventures"/>
+    <s v="MC"/>
+    <s v="1296"/>
+    <d v="1995-01-08T00:00:00"/>
+    <n v="7423.35"/>
+    <n v="0"/>
+    <n v="7423.35"/>
+  </r>
+  <r>
+    <s v="Divers of Corfu, Inc."/>
+    <s v="Credit"/>
+    <s v="1298"/>
+    <d v="1995-01-09T00:00:00"/>
+    <n v="9897"/>
+    <n v="0"/>
+    <n v="9897"/>
+  </r>
+  <r>
+    <s v="VIP Divers Club"/>
+    <s v="Credit"/>
+    <s v="1300"/>
+    <d v="1995-01-10T00:00:00"/>
+    <n v="52729.25"/>
+    <n v="0"/>
+    <n v="52729.25"/>
+  </r>
+  <r>
+    <s v="Unisco"/>
+    <s v="Credit"/>
+    <s v="1302"/>
+    <d v="1995-01-16T00:00:00"/>
+    <n v="24485"/>
+    <n v="0"/>
+    <n v="24485"/>
+  </r>
+  <r>
+    <s v="Tom Sawyer Diving Centre"/>
+    <s v="Visa"/>
+    <s v="1305"/>
+    <d v="1995-01-20T00:00:00"/>
+    <n v="3065"/>
+    <n v="0"/>
+    <n v="3065"/>
+  </r>
+  <r>
+    <s v="Marina SCUBA Center"/>
+    <s v="COD"/>
+    <s v="1309"/>
+    <d v="1995-01-22T00:00:00"/>
+    <n v="465"/>
+    <n v="0"/>
+    <n v="465"/>
+  </r>
+  <r>
+    <s v="Jamaica SCUBA Centre"/>
+    <s v="MC"/>
+    <s v="1315"/>
+    <d v="1995-01-26T00:00:00"/>
+    <n v="5037.1"/>
+    <n v="0"/>
+    <n v="5037.1"/>
+  </r>
+  <r>
+    <s v="Adventure Undersea"/>
+    <s v="Check"/>
+    <s v="1317"/>
+    <d v="1995-02-01T00:00:00"/>
+    <n v="7572"/>
+    <n v="0"/>
+    <n v="7572"/>
+  </r>
+  <r>
+    <s v="Underwater Sports Co."/>
+    <s v="AmEx"/>
+    <s v="1350"/>
+    <d v="1995-02-02T00:00:00"/>
+    <n v="8939.6"/>
+    <n v="0"/>
+    <n v="8939.6"/>
+  </r>
+  <r>
+    <s v="American SCUBA Supply"/>
+    <s v="Credit"/>
+    <s v="1355"/>
+    <d v="1995-02-05T00:00:00"/>
+    <n v="13908"/>
+    <n v="0"/>
+    <n v="13908"/>
+  </r>
+  <r>
+    <s v="Marina SCUBA Center"/>
+    <s v="Check"/>
+    <s v="1860"/>
+    <m/>
+    <n v="65"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+</pivotCacheRecords>
 </file>
--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -1291,2311 +1291,649 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataCaption="Values" showError="0" missingCaption="" showMissing="1" pageWrap="0" pageOverThenDown="0" itemPrintTitles="1" mergeItem="1" indent="0" compact="0" compactData="0" gridDropZones="1">
-  <x:location ref="B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <x:pivotFields count="7">
-    <x:pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1">
-      <x:items count="55">
-        <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
-        <x:item x="4"/>
-        <x:item x="5"/>
-        <x:item x="6"/>
-        <x:item x="7"/>
-        <x:item x="8"/>
-        <x:item x="9"/>
-        <x:item x="10"/>
-        <x:item x="11"/>
-        <x:item x="12"/>
-        <x:item x="13"/>
-        <x:item x="14"/>
-        <x:item x="15"/>
-        <x:item x="16"/>
-        <x:item x="17"/>
-        <x:item x="18"/>
-        <x:item x="19"/>
-        <x:item x="20"/>
-        <x:item x="21"/>
-        <x:item x="22"/>
-        <x:item x="23"/>
-        <x:item x="24"/>
-        <x:item x="25"/>
-        <x:item x="26"/>
-        <x:item x="27"/>
-        <x:item x="28"/>
-        <x:item x="29"/>
-        <x:item x="30"/>
-        <x:item x="31"/>
-        <x:item x="32"/>
-        <x:item x="33"/>
-        <x:item x="34"/>
-        <x:item x="35"/>
-        <x:item x="36"/>
-        <x:item x="37"/>
-        <x:item x="38"/>
-        <x:item x="39"/>
-        <x:item x="40"/>
-        <x:item x="41"/>
-        <x:item x="42"/>
-        <x:item x="43"/>
-        <x:item x="44"/>
-        <x:item x="45"/>
-        <x:item x="46"/>
-        <x:item x="47"/>
-        <x:item x="48"/>
-        <x:item x="49"/>
-        <x:item x="50"/>
-        <x:item x="51"/>
-        <x:item x="52"/>
-        <x:item x="53"/>
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Payment method" axis="axisRow" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1">
-      <x:items count="8">
-        <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
-        <x:item x="4"/>
-        <x:item x="5"/>
-        <x:item x="6"/>
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="OrderNo" axis="axisRow" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1">
-      <x:items count="206">
-        <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
-        <x:item x="4"/>
-        <x:item x="5"/>
-        <x:item x="6"/>
-        <x:item x="7"/>
-        <x:item x="8"/>
-        <x:item x="9"/>
-        <x:item x="10"/>
-        <x:item x="11"/>
-        <x:item x="12"/>
-        <x:item x="13"/>
-        <x:item x="14"/>
-        <x:item x="15"/>
-        <x:item x="16"/>
-        <x:item x="17"/>
-        <x:item x="18"/>
-        <x:item x="19"/>
-        <x:item x="20"/>
-        <x:item x="21"/>
-        <x:item x="22"/>
-        <x:item x="23"/>
-        <x:item x="24"/>
-        <x:item x="25"/>
-        <x:item x="26"/>
-        <x:item x="27"/>
-        <x:item x="28"/>
-        <x:item x="29"/>
-        <x:item x="30"/>
-        <x:item x="31"/>
-        <x:item x="32"/>
-        <x:item x="33"/>
-        <x:item x="34"/>
-        <x:item x="35"/>
-        <x:item x="36"/>
-        <x:item x="37"/>
-        <x:item x="38"/>
-        <x:item x="39"/>
-        <x:item x="40"/>
-        <x:item x="41"/>
-        <x:item x="42"/>
-        <x:item x="43"/>
-        <x:item x="44"/>
-        <x:item x="45"/>
-        <x:item x="46"/>
-        <x:item x="47"/>
-        <x:item x="48"/>
-        <x:item x="49"/>
-        <x:item x="50"/>
-        <x:item x="51"/>
-        <x:item x="52"/>
-        <x:item x="53"/>
-        <x:item x="54"/>
-        <x:item x="55"/>
-        <x:item x="56"/>
-        <x:item x="57"/>
-        <x:item x="58"/>
-        <x:item x="59"/>
-        <x:item x="60"/>
-        <x:item x="61"/>
-        <x:item x="62"/>
-        <x:item x="63"/>
-        <x:item x="64"/>
-        <x:item x="65"/>
-        <x:item x="66"/>
-        <x:item x="67"/>
-        <x:item x="68"/>
-        <x:item x="69"/>
-        <x:item x="70"/>
-        <x:item x="71"/>
-        <x:item x="72"/>
-        <x:item x="73"/>
-        <x:item x="74"/>
-        <x:item x="75"/>
-        <x:item x="76"/>
-        <x:item x="77"/>
-        <x:item x="78"/>
-        <x:item x="79"/>
-        <x:item x="80"/>
-        <x:item x="81"/>
-        <x:item x="82"/>
-        <x:item x="83"/>
-        <x:item x="84"/>
-        <x:item x="85"/>
-        <x:item x="86"/>
-        <x:item x="87"/>
-        <x:item x="88"/>
-        <x:item x="89"/>
-        <x:item x="90"/>
-        <x:item x="91"/>
-        <x:item x="92"/>
-        <x:item x="93"/>
-        <x:item x="94"/>
-        <x:item x="95"/>
-        <x:item x="96"/>
-        <x:item x="97"/>
-        <x:item x="98"/>
-        <x:item x="99"/>
-        <x:item x="100"/>
-        <x:item x="101"/>
-        <x:item x="102"/>
-        <x:item x="103"/>
-        <x:item x="104"/>
-        <x:item x="105"/>
-        <x:item x="106"/>
-        <x:item x="107"/>
-        <x:item x="108"/>
-        <x:item x="109"/>
-        <x:item x="110"/>
-        <x:item x="111"/>
-        <x:item x="112"/>
-        <x:item x="113"/>
-        <x:item x="114"/>
-        <x:item x="115"/>
-        <x:item x="116"/>
-        <x:item x="117"/>
-        <x:item x="118"/>
-        <x:item x="119"/>
-        <x:item x="120"/>
-        <x:item x="121"/>
-        <x:item x="122"/>
-        <x:item x="123"/>
-        <x:item x="124"/>
-        <x:item x="125"/>
-        <x:item x="126"/>
-        <x:item x="127"/>
-        <x:item x="128"/>
-        <x:item x="129"/>
-        <x:item x="130"/>
-        <x:item x="131"/>
-        <x:item x="132"/>
-        <x:item x="133"/>
-        <x:item x="134"/>
-        <x:item x="135"/>
-        <x:item x="136"/>
-        <x:item x="137"/>
-        <x:item x="138"/>
-        <x:item x="139"/>
-        <x:item x="140"/>
-        <x:item x="141"/>
-        <x:item x="142"/>
-        <x:item x="143"/>
-        <x:item x="144"/>
-        <x:item x="145"/>
-        <x:item x="146"/>
-        <x:item x="147"/>
-        <x:item x="148"/>
-        <x:item x="149"/>
-        <x:item x="150"/>
-        <x:item x="151"/>
-        <x:item x="152"/>
-        <x:item x="153"/>
-        <x:item x="154"/>
-        <x:item x="155"/>
-        <x:item x="156"/>
-        <x:item x="157"/>
-        <x:item x="158"/>
-        <x:item x="159"/>
-        <x:item x="160"/>
-        <x:item x="161"/>
-        <x:item x="162"/>
-        <x:item x="163"/>
-        <x:item x="164"/>
-        <x:item x="165"/>
-        <x:item x="166"/>
-        <x:item x="167"/>
-        <x:item x="168"/>
-        <x:item x="169"/>
-        <x:item x="170"/>
-        <x:item x="171"/>
-        <x:item x="172"/>
-        <x:item x="173"/>
-        <x:item x="174"/>
-        <x:item x="175"/>
-        <x:item x="176"/>
-        <x:item x="177"/>
-        <x:item x="178"/>
-        <x:item x="179"/>
-        <x:item x="180"/>
-        <x:item x="181"/>
-        <x:item x="182"/>
-        <x:item x="183"/>
-        <x:item x="184"/>
-        <x:item x="185"/>
-        <x:item x="186"/>
-        <x:item x="187"/>
-        <x:item x="188"/>
-        <x:item x="189"/>
-        <x:item x="190"/>
-        <x:item x="191"/>
-        <x:item x="192"/>
-        <x:item x="193"/>
-        <x:item x="194"/>
-        <x:item x="195"/>
-        <x:item x="196"/>
-        <x:item x="197"/>
-        <x:item x="198"/>
-        <x:item x="199"/>
-        <x:item x="200"/>
-        <x:item x="201"/>
-        <x:item x="202"/>
-        <x:item x="203"/>
-        <x:item x="204"/>
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Ship date" compact="0" outline="0">
-      <x:items count="1">
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Items total" dataField="1" compact="0" outline="0">
-      <x:items count="1">
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Tax rate" axis="axisCol" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1">
-      <x:items count="4">
-        <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Amount paid" dataField="1" compact="0" outline="0">
-      <x:items count="1">
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-  </x:pivotFields>
-  <x:rowFields count="3">
-    <x:field x="0"/>
-    <x:field x="1"/>
-    <x:field x="2"/>
-  </x:rowFields>
-  <x:rowItems count="269">
-    <x:i>
-      <x:x v="0"/>
-    </x:i>
-    <x:i>
-      <x:x v="1"/>
-    </x:i>
-    <x:i>
-      <x:x v="2"/>
-    </x:i>
-    <x:i>
-      <x:x v="3"/>
-    </x:i>
-    <x:i>
-      <x:x v="4"/>
-    </x:i>
-    <x:i>
-      <x:x v="5"/>
-    </x:i>
-    <x:i>
-      <x:x v="6"/>
-    </x:i>
-    <x:i>
-      <x:x v="7"/>
-    </x:i>
-    <x:i>
-      <x:x v="8"/>
-    </x:i>
-    <x:i>
-      <x:x v="9"/>
-    </x:i>
-    <x:i>
-      <x:x v="10"/>
-    </x:i>
-    <x:i>
-      <x:x v="11"/>
-    </x:i>
-    <x:i>
-      <x:x v="12"/>
-    </x:i>
-    <x:i>
-      <x:x v="13"/>
-    </x:i>
-    <x:i>
-      <x:x v="14"/>
-    </x:i>
-    <x:i>
-      <x:x v="15"/>
-    </x:i>
-    <x:i>
-      <x:x v="16"/>
-    </x:i>
-    <x:i>
-      <x:x v="17"/>
-    </x:i>
-    <x:i>
-      <x:x v="18"/>
-    </x:i>
-    <x:i>
-      <x:x v="19"/>
-    </x:i>
-    <x:i>
-      <x:x v="20"/>
-    </x:i>
-    <x:i>
-      <x:x v="21"/>
-    </x:i>
-    <x:i>
-      <x:x v="22"/>
-    </x:i>
-    <x:i>
-      <x:x v="23"/>
-    </x:i>
-    <x:i>
-      <x:x v="24"/>
-    </x:i>
-    <x:i>
-      <x:x v="25"/>
-    </x:i>
-    <x:i>
-      <x:x v="26"/>
-    </x:i>
-    <x:i>
-      <x:x v="27"/>
-    </x:i>
-    <x:i>
-      <x:x v="28"/>
-    </x:i>
-    <x:i>
-      <x:x v="29"/>
-    </x:i>
-    <x:i>
-      <x:x v="30"/>
-    </x:i>
-    <x:i>
-      <x:x v="31"/>
-    </x:i>
-    <x:i>
-      <x:x v="32"/>
-    </x:i>
-    <x:i>
-      <x:x v="33"/>
-    </x:i>
-    <x:i>
-      <x:x v="34"/>
-    </x:i>
-    <x:i>
-      <x:x v="35"/>
-    </x:i>
-    <x:i>
-      <x:x v="36"/>
-    </x:i>
-    <x:i>
-      <x:x v="37"/>
-    </x:i>
-    <x:i>
-      <x:x v="38"/>
-    </x:i>
-    <x:i>
-      <x:x v="39"/>
-    </x:i>
-    <x:i>
-      <x:x v="40"/>
-    </x:i>
-    <x:i>
-      <x:x v="41"/>
-    </x:i>
-    <x:i>
-      <x:x v="42"/>
-    </x:i>
-    <x:i>
-      <x:x v="43"/>
-    </x:i>
-    <x:i>
-      <x:x v="44"/>
-    </x:i>
-    <x:i>
-      <x:x v="45"/>
-    </x:i>
-    <x:i>
-      <x:x v="46"/>
-    </x:i>
-    <x:i>
-      <x:x v="47"/>
-    </x:i>
-    <x:i>
-      <x:x v="48"/>
-    </x:i>
-    <x:i>
-      <x:x v="49"/>
-    </x:i>
-    <x:i>
-      <x:x v="50"/>
-    </x:i>
-    <x:i>
-      <x:x v="51"/>
-    </x:i>
-    <x:i>
-      <x:x v="52"/>
-    </x:i>
-    <x:i>
-      <x:x v="53"/>
-    </x:i>
-    <x:i t="grand">
-      <x:x/>
-    </x:i>
-    <x:i>
-      <x:x v="0"/>
-    </x:i>
-    <x:i>
-      <x:x v="1"/>
-    </x:i>
-    <x:i>
-      <x:x v="2"/>
-    </x:i>
-    <x:i>
-      <x:x v="3"/>
-    </x:i>
-    <x:i>
-      <x:x v="4"/>
-    </x:i>
-    <x:i>
-      <x:x v="5"/>
-    </x:i>
-    <x:i>
-      <x:x v="6"/>
-    </x:i>
-    <x:i t="grand">
-      <x:x/>
-    </x:i>
-    <x:i>
-      <x:x v="0"/>
-    </x:i>
-    <x:i>
-      <x:x v="1"/>
-    </x:i>
-    <x:i>
-      <x:x v="2"/>
-    </x:i>
-    <x:i>
-      <x:x v="3"/>
-    </x:i>
-    <x:i>
-      <x:x v="4"/>
-    </x:i>
-    <x:i>
-      <x:x v="5"/>
-    </x:i>
-    <x:i>
-      <x:x v="6"/>
-    </x:i>
-    <x:i>
-      <x:x v="7"/>
-    </x:i>
-    <x:i>
-      <x:x v="8"/>
-    </x:i>
-    <x:i>
-      <x:x v="9"/>
-    </x:i>
-    <x:i>
-      <x:x v="10"/>
-    </x:i>
-    <x:i>
-      <x:x v="11"/>
-    </x:i>
-    <x:i>
-      <x:x v="12"/>
-    </x:i>
-    <x:i>
-      <x:x v="13"/>
-    </x:i>
-    <x:i>
-      <x:x v="14"/>
-    </x:i>
-    <x:i>
-      <x:x v="15"/>
-    </x:i>
-    <x:i>
-      <x:x v="16"/>
-    </x:i>
-    <x:i>
-      <x:x v="17"/>
-    </x:i>
-    <x:i>
-      <x:x v="18"/>
-    </x:i>
-    <x:i>
-      <x:x v="19"/>
-    </x:i>
-    <x:i>
-      <x:x v="20"/>
-    </x:i>
-    <x:i>
-      <x:x v="21"/>
-    </x:i>
-    <x:i>
-      <x:x v="22"/>
-    </x:i>
-    <x:i>
-      <x:x v="23"/>
-    </x:i>
-    <x:i>
-      <x:x v="24"/>
-    </x:i>
-    <x:i>
-      <x:x v="25"/>
-    </x:i>
-    <x:i>
-      <x:x v="26"/>
-    </x:i>
-    <x:i>
-      <x:x v="27"/>
-    </x:i>
-    <x:i>
-      <x:x v="28"/>
-    </x:i>
-    <x:i>
-      <x:x v="29"/>
-    </x:i>
-    <x:i>
-      <x:x v="30"/>
-    </x:i>
-    <x:i>
-      <x:x v="31"/>
-    </x:i>
-    <x:i>
-      <x:x v="32"/>
-    </x:i>
-    <x:i>
-      <x:x v="33"/>
-    </x:i>
-    <x:i>
-      <x:x v="34"/>
-    </x:i>
-    <x:i>
-      <x:x v="35"/>
-    </x:i>
-    <x:i>
-      <x:x v="36"/>
-    </x:i>
-    <x:i>
-      <x:x v="37"/>
-    </x:i>
-    <x:i>
-      <x:x v="38"/>
-    </x:i>
-    <x:i>
-      <x:x v="39"/>
-    </x:i>
-    <x:i>
-      <x:x v="40"/>
-    </x:i>
-    <x:i>
-      <x:x v="41"/>
-    </x:i>
-    <x:i>
-      <x:x v="42"/>
-    </x:i>
-    <x:i>
-      <x:x v="43"/>
-    </x:i>
-    <x:i>
-      <x:x v="44"/>
-    </x:i>
-    <x:i>
-      <x:x v="45"/>
-    </x:i>
-    <x:i>
-      <x:x v="46"/>
-    </x:i>
-    <x:i>
-      <x:x v="47"/>
-    </x:i>
-    <x:i>
-      <x:x v="48"/>
-    </x:i>
-    <x:i>
-      <x:x v="49"/>
-    </x:i>
-    <x:i>
-      <x:x v="50"/>
-    </x:i>
-    <x:i>
-      <x:x v="51"/>
-    </x:i>
-    <x:i>
-      <x:x v="52"/>
-    </x:i>
-    <x:i>
-      <x:x v="53"/>
-    </x:i>
-    <x:i>
-      <x:x v="54"/>
-    </x:i>
-    <x:i>
-      <x:x v="55"/>
-    </x:i>
-    <x:i>
-      <x:x v="56"/>
-    </x:i>
-    <x:i>
-      <x:x v="57"/>
-    </x:i>
-    <x:i>
-      <x:x v="58"/>
-    </x:i>
-    <x:i>
-      <x:x v="59"/>
-    </x:i>
-    <x:i>
-      <x:x v="60"/>
-    </x:i>
-    <x:i>
-      <x:x v="61"/>
-    </x:i>
-    <x:i>
-      <x:x v="62"/>
-    </x:i>
-    <x:i>
-      <x:x v="63"/>
-    </x:i>
-    <x:i>
-      <x:x v="64"/>
-    </x:i>
-    <x:i>
-      <x:x v="65"/>
-    </x:i>
-    <x:i>
-      <x:x v="66"/>
-    </x:i>
-    <x:i>
-      <x:x v="67"/>
-    </x:i>
-    <x:i>
-      <x:x v="68"/>
-    </x:i>
-    <x:i>
-      <x:x v="69"/>
-    </x:i>
-    <x:i>
-      <x:x v="70"/>
-    </x:i>
-    <x:i>
-      <x:x v="71"/>
-    </x:i>
-    <x:i>
-      <x:x v="72"/>
-    </x:i>
-    <x:i>
-      <x:x v="73"/>
-    </x:i>
-    <x:i>
-      <x:x v="74"/>
-    </x:i>
-    <x:i>
-      <x:x v="75"/>
-    </x:i>
-    <x:i>
-      <x:x v="76"/>
-    </x:i>
-    <x:i>
-      <x:x v="77"/>
-    </x:i>
-    <x:i>
-      <x:x v="78"/>
-    </x:i>
-    <x:i>
-      <x:x v="79"/>
-    </x:i>
-    <x:i>
-      <x:x v="80"/>
-    </x:i>
-    <x:i>
-      <x:x v="81"/>
-    </x:i>
-    <x:i>
-      <x:x v="82"/>
-    </x:i>
-    <x:i>
-      <x:x v="83"/>
-    </x:i>
-    <x:i>
-      <x:x v="84"/>
-    </x:i>
-    <x:i>
-      <x:x v="85"/>
-    </x:i>
-    <x:i>
-      <x:x v="86"/>
-    </x:i>
-    <x:i>
-      <x:x v="87"/>
-    </x:i>
-    <x:i>
-      <x:x v="88"/>
-    </x:i>
-    <x:i>
-      <x:x v="89"/>
-    </x:i>
-    <x:i>
-      <x:x v="90"/>
-    </x:i>
-    <x:i>
-      <x:x v="91"/>
-    </x:i>
-    <x:i>
-      <x:x v="92"/>
-    </x:i>
-    <x:i>
-      <x:x v="93"/>
-    </x:i>
-    <x:i>
-      <x:x v="94"/>
-    </x:i>
-    <x:i>
-      <x:x v="95"/>
-    </x:i>
-    <x:i>
-      <x:x v="96"/>
-    </x:i>
-    <x:i>
-      <x:x v="97"/>
-    </x:i>
-    <x:i>
-      <x:x v="98"/>
-    </x:i>
-    <x:i>
-      <x:x v="99"/>
-    </x:i>
-    <x:i>
-      <x:x v="100"/>
-    </x:i>
-    <x:i>
-      <x:x v="101"/>
-    </x:i>
-    <x:i>
-      <x:x v="102"/>
-    </x:i>
-    <x:i>
-      <x:x v="103"/>
-    </x:i>
-    <x:i>
-      <x:x v="104"/>
-    </x:i>
-    <x:i>
-      <x:x v="105"/>
-    </x:i>
-    <x:i>
-      <x:x v="106"/>
-    </x:i>
-    <x:i>
-      <x:x v="107"/>
-    </x:i>
-    <x:i>
-      <x:x v="108"/>
-    </x:i>
-    <x:i>
-      <x:x v="109"/>
-    </x:i>
-    <x:i>
-      <x:x v="110"/>
-    </x:i>
-    <x:i>
-      <x:x v="111"/>
-    </x:i>
-    <x:i>
-      <x:x v="112"/>
-    </x:i>
-    <x:i>
-      <x:x v="113"/>
-    </x:i>
-    <x:i>
-      <x:x v="114"/>
-    </x:i>
-    <x:i>
-      <x:x v="115"/>
-    </x:i>
-    <x:i>
-      <x:x v="116"/>
-    </x:i>
-    <x:i>
-      <x:x v="117"/>
-    </x:i>
-    <x:i>
-      <x:x v="118"/>
-    </x:i>
-    <x:i>
-      <x:x v="119"/>
-    </x:i>
-    <x:i>
-      <x:x v="120"/>
-    </x:i>
-    <x:i>
-      <x:x v="121"/>
-    </x:i>
-    <x:i>
-      <x:x v="122"/>
-    </x:i>
-    <x:i>
-      <x:x v="123"/>
-    </x:i>
-    <x:i>
-      <x:x v="124"/>
-    </x:i>
-    <x:i>
-      <x:x v="125"/>
-    </x:i>
-    <x:i>
-      <x:x v="126"/>
-    </x:i>
-    <x:i>
-      <x:x v="127"/>
-    </x:i>
-    <x:i>
-      <x:x v="128"/>
-    </x:i>
-    <x:i>
-      <x:x v="129"/>
-    </x:i>
-    <x:i>
-      <x:x v="130"/>
-    </x:i>
-    <x:i>
-      <x:x v="131"/>
-    </x:i>
-    <x:i>
-      <x:x v="132"/>
-    </x:i>
-    <x:i>
-      <x:x v="133"/>
-    </x:i>
-    <x:i>
-      <x:x v="134"/>
-    </x:i>
-    <x:i>
-      <x:x v="135"/>
-    </x:i>
-    <x:i>
-      <x:x v="136"/>
-    </x:i>
-    <x:i>
-      <x:x v="137"/>
-    </x:i>
-    <x:i>
-      <x:x v="138"/>
-    </x:i>
-    <x:i>
-      <x:x v="139"/>
-    </x:i>
-    <x:i>
-      <x:x v="140"/>
-    </x:i>
-    <x:i>
-      <x:x v="141"/>
-    </x:i>
-    <x:i>
-      <x:x v="142"/>
-    </x:i>
-    <x:i>
-      <x:x v="143"/>
-    </x:i>
-    <x:i>
-      <x:x v="144"/>
-    </x:i>
-    <x:i>
-      <x:x v="145"/>
-    </x:i>
-    <x:i>
-      <x:x v="146"/>
-    </x:i>
-    <x:i>
-      <x:x v="147"/>
-    </x:i>
-    <x:i>
-      <x:x v="148"/>
-    </x:i>
-    <x:i>
-      <x:x v="149"/>
-    </x:i>
-    <x:i>
-      <x:x v="150"/>
-    </x:i>
-    <x:i>
-      <x:x v="151"/>
-    </x:i>
-    <x:i>
-      <x:x v="152"/>
-    </x:i>
-    <x:i>
-      <x:x v="153"/>
-    </x:i>
-    <x:i>
-      <x:x v="154"/>
-    </x:i>
-    <x:i>
-      <x:x v="155"/>
-    </x:i>
-    <x:i>
-      <x:x v="156"/>
-    </x:i>
-    <x:i>
-      <x:x v="157"/>
-    </x:i>
-    <x:i>
-      <x:x v="158"/>
-    </x:i>
-    <x:i>
-      <x:x v="159"/>
-    </x:i>
-    <x:i>
-      <x:x v="160"/>
-    </x:i>
-    <x:i>
-      <x:x v="161"/>
-    </x:i>
-    <x:i>
-      <x:x v="162"/>
-    </x:i>
-    <x:i>
-      <x:x v="163"/>
-    </x:i>
-    <x:i>
-      <x:x v="164"/>
-    </x:i>
-    <x:i>
-      <x:x v="165"/>
-    </x:i>
-    <x:i>
-      <x:x v="166"/>
-    </x:i>
-    <x:i>
-      <x:x v="167"/>
-    </x:i>
-    <x:i>
-      <x:x v="168"/>
-    </x:i>
-    <x:i>
-      <x:x v="169"/>
-    </x:i>
-    <x:i>
-      <x:x v="170"/>
-    </x:i>
-    <x:i>
-      <x:x v="171"/>
-    </x:i>
-    <x:i>
-      <x:x v="172"/>
-    </x:i>
-    <x:i>
-      <x:x v="173"/>
-    </x:i>
-    <x:i>
-      <x:x v="174"/>
-    </x:i>
-    <x:i>
-      <x:x v="175"/>
-    </x:i>
-    <x:i>
-      <x:x v="176"/>
-    </x:i>
-    <x:i>
-      <x:x v="177"/>
-    </x:i>
-    <x:i>
-      <x:x v="178"/>
-    </x:i>
-    <x:i>
-      <x:x v="179"/>
-    </x:i>
-    <x:i>
-      <x:x v="180"/>
-    </x:i>
-    <x:i>
-      <x:x v="181"/>
-    </x:i>
-    <x:i>
-      <x:x v="182"/>
-    </x:i>
-    <x:i>
-      <x:x v="183"/>
-    </x:i>
-    <x:i>
-      <x:x v="184"/>
-    </x:i>
-    <x:i>
-      <x:x v="185"/>
-    </x:i>
-    <x:i>
-      <x:x v="186"/>
-    </x:i>
-    <x:i>
-      <x:x v="187"/>
-    </x:i>
-    <x:i>
-      <x:x v="188"/>
-    </x:i>
-    <x:i>
-      <x:x v="189"/>
-    </x:i>
-    <x:i>
-      <x:x v="190"/>
-    </x:i>
-    <x:i>
-      <x:x v="191"/>
-    </x:i>
-    <x:i>
-      <x:x v="192"/>
-    </x:i>
-    <x:i>
-      <x:x v="193"/>
-    </x:i>
-    <x:i>
-      <x:x v="194"/>
-    </x:i>
-    <x:i>
-      <x:x v="195"/>
-    </x:i>
-    <x:i>
-      <x:x v="196"/>
-    </x:i>
-    <x:i>
-      <x:x v="197"/>
-    </x:i>
-    <x:i>
-      <x:x v="198"/>
-    </x:i>
-    <x:i>
-      <x:x v="199"/>
-    </x:i>
-    <x:i>
-      <x:x v="200"/>
-    </x:i>
-    <x:i>
-      <x:x v="201"/>
-    </x:i>
-    <x:i>
-      <x:x v="202"/>
-    </x:i>
-    <x:i>
-      <x:x v="203"/>
-    </x:i>
-    <x:i>
-      <x:x v="204"/>
-    </x:i>
-    <x:i t="grand">
-      <x:x/>
-    </x:i>
-  </x:rowItems>
-  <x:colFields count="2">
-    <x:field x="5"/>
-    <x:field x="-2"/>
-  </x:colFields>
-  <x:colItems count="4">
-    <x:i>
-      <x:x v="0"/>
-    </x:i>
-    <x:i>
-      <x:x v="1"/>
-    </x:i>
-    <x:i>
-      <x:x v="2"/>
-    </x:i>
-    <x:i t="grand">
-      <x:x/>
-    </x:i>
-  </x:colItems>
-  <x:dataFields count="2">
-    <x:dataField name="Sum Amount paid" fld="6" subtotal="sum" showDataAs="normal" baseField="0" baseItem="0" numFmtId="0"/>
-    <x:dataField name="Sum Items total" fld="4" subtotal="sum" showDataAs="normal" baseField="0" baseItem="0" numFmtId="0"/>
-  </x:dataFields>
-  <x:formats count="1">
-    <x:format dxfId="1">
-      <x:pivotArea type="normal" dataOnly="0" labelOnly="1" fieldPosition="0">
-        <x:references count="1">
-          <x:reference field="1"/>
-        </x:references>
-      </x:pivotArea>
-    </x:format>
-  </x:formats>
-  <x:pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0"/>
-  <x:extLst>
-    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" enableEdit="0" hideValuesRow="1"/>
-    </x:ext>
-  </x:extLst>
-</x:pivotTableDefinition>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataPosition="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" itemPrintTitles="1" mergeItem="1" createdVersion="3" indent="0" compact="0" compactData="0" gridDropZones="1">
+  <location ref="B3:H9" firstHeaderRow="1" firstDataRow="3" firstDataCol="3"/>
+  <pivotFields count="7">
+    <pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="55">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Payment method" axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="OrderNo" axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="206">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField name="Tax rate" axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="0"/>
+    <field x="1"/>
+    <field x="2"/>
+  </rowFields>
+  <colFields count="2">
+    <field x="5"/>
+    <field x="-2"/>
+  </colFields>
+  <dataFields count="2">
+    <dataField name="Sum Amount paid" fld="6"/>
+    <dataField name="Sum Items total" fld="4"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" dataCaption="Values" showError="0" missingCaption="" showMissing="1" useAutoFormatting="1" pageWrap="0" pageOverThenDown="0" itemPrintTitles="1" mergeItem="1" indent="0" compact="0" compactData="0" gridDropZones="1">
-  <x:location ref="B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <x:pivotFields count="7">
-    <x:pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0">
-      <x:items count="55">
-        <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
-        <x:item x="4"/>
-        <x:item x="5"/>
-        <x:item x="6"/>
-        <x:item x="7"/>
-        <x:item x="8"/>
-        <x:item x="9"/>
-        <x:item x="10"/>
-        <x:item x="11"/>
-        <x:item x="12"/>
-        <x:item x="13"/>
-        <x:item x="14"/>
-        <x:item x="15"/>
-        <x:item x="16"/>
-        <x:item x="17"/>
-        <x:item x="18"/>
-        <x:item x="19"/>
-        <x:item x="20"/>
-        <x:item x="21"/>
-        <x:item x="22"/>
-        <x:item x="23"/>
-        <x:item x="24"/>
-        <x:item x="25"/>
-        <x:item x="26"/>
-        <x:item x="27"/>
-        <x:item x="28"/>
-        <x:item x="29"/>
-        <x:item x="30"/>
-        <x:item x="31"/>
-        <x:item x="32"/>
-        <x:item x="33"/>
-        <x:item x="34"/>
-        <x:item x="35"/>
-        <x:item x="36"/>
-        <x:item x="37"/>
-        <x:item x="38"/>
-        <x:item x="39"/>
-        <x:item x="40"/>
-        <x:item x="41"/>
-        <x:item x="42"/>
-        <x:item x="43"/>
-        <x:item x="44"/>
-        <x:item x="45"/>
-        <x:item x="46"/>
-        <x:item x="47"/>
-        <x:item x="48"/>
-        <x:item x="49"/>
-        <x:item x="50"/>
-        <x:item x="51"/>
-        <x:item x="52"/>
-        <x:item x="53"/>
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Payment method" axis="axisCol" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1">
-      <x:items count="8">
-        <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
-        <x:item x="4"/>
-        <x:item x="5"/>
-        <x:item x="6"/>
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="OrderNo" axis="axisRow" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1">
-      <x:items count="206">
-        <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
-        <x:item x="4"/>
-        <x:item x="5"/>
-        <x:item x="6"/>
-        <x:item x="7"/>
-        <x:item x="8"/>
-        <x:item x="9"/>
-        <x:item x="10"/>
-        <x:item x="11"/>
-        <x:item x="12"/>
-        <x:item x="13"/>
-        <x:item x="14"/>
-        <x:item x="15"/>
-        <x:item x="16"/>
-        <x:item x="17"/>
-        <x:item x="18"/>
-        <x:item x="19"/>
-        <x:item x="20"/>
-        <x:item x="21"/>
-        <x:item x="22"/>
-        <x:item x="23"/>
-        <x:item x="24"/>
-        <x:item x="25"/>
-        <x:item x="26"/>
-        <x:item x="27"/>
-        <x:item x="28"/>
-        <x:item x="29"/>
-        <x:item x="30"/>
-        <x:item x="31"/>
-        <x:item x="32"/>
-        <x:item x="33"/>
-        <x:item x="34"/>
-        <x:item x="35"/>
-        <x:item x="36"/>
-        <x:item x="37"/>
-        <x:item x="38"/>
-        <x:item x="39"/>
-        <x:item x="40"/>
-        <x:item x="41"/>
-        <x:item x="42"/>
-        <x:item x="43"/>
-        <x:item x="44"/>
-        <x:item x="45"/>
-        <x:item x="46"/>
-        <x:item x="47"/>
-        <x:item x="48"/>
-        <x:item x="49"/>
-        <x:item x="50"/>
-        <x:item x="51"/>
-        <x:item x="52"/>
-        <x:item x="53"/>
-        <x:item x="54"/>
-        <x:item x="55"/>
-        <x:item x="56"/>
-        <x:item x="57"/>
-        <x:item x="58"/>
-        <x:item x="59"/>
-        <x:item x="60"/>
-        <x:item x="61"/>
-        <x:item x="62"/>
-        <x:item x="63"/>
-        <x:item x="64"/>
-        <x:item x="65"/>
-        <x:item x="66"/>
-        <x:item x="67"/>
-        <x:item x="68"/>
-        <x:item x="69"/>
-        <x:item x="70"/>
-        <x:item x="71"/>
-        <x:item x="72"/>
-        <x:item x="73"/>
-        <x:item x="74"/>
-        <x:item x="75"/>
-        <x:item x="76"/>
-        <x:item x="77"/>
-        <x:item x="78"/>
-        <x:item x="79"/>
-        <x:item x="80"/>
-        <x:item x="81"/>
-        <x:item x="82"/>
-        <x:item x="83"/>
-        <x:item x="84"/>
-        <x:item x="85"/>
-        <x:item x="86"/>
-        <x:item x="87"/>
-        <x:item x="88"/>
-        <x:item x="89"/>
-        <x:item x="90"/>
-        <x:item x="91"/>
-        <x:item x="92"/>
-        <x:item x="93"/>
-        <x:item x="94"/>
-        <x:item x="95"/>
-        <x:item x="96"/>
-        <x:item x="97"/>
-        <x:item x="98"/>
-        <x:item x="99"/>
-        <x:item x="100"/>
-        <x:item x="101"/>
-        <x:item x="102"/>
-        <x:item x="103"/>
-        <x:item x="104"/>
-        <x:item x="105"/>
-        <x:item x="106"/>
-        <x:item x="107"/>
-        <x:item x="108"/>
-        <x:item x="109"/>
-        <x:item x="110"/>
-        <x:item x="111"/>
-        <x:item x="112"/>
-        <x:item x="113"/>
-        <x:item x="114"/>
-        <x:item x="115"/>
-        <x:item x="116"/>
-        <x:item x="117"/>
-        <x:item x="118"/>
-        <x:item x="119"/>
-        <x:item x="120"/>
-        <x:item x="121"/>
-        <x:item x="122"/>
-        <x:item x="123"/>
-        <x:item x="124"/>
-        <x:item x="125"/>
-        <x:item x="126"/>
-        <x:item x="127"/>
-        <x:item x="128"/>
-        <x:item x="129"/>
-        <x:item x="130"/>
-        <x:item x="131"/>
-        <x:item x="132"/>
-        <x:item x="133"/>
-        <x:item x="134"/>
-        <x:item x="135"/>
-        <x:item x="136"/>
-        <x:item x="137"/>
-        <x:item x="138"/>
-        <x:item x="139"/>
-        <x:item x="140"/>
-        <x:item x="141"/>
-        <x:item x="142"/>
-        <x:item x="143"/>
-        <x:item x="144"/>
-        <x:item x="145"/>
-        <x:item x="146"/>
-        <x:item x="147"/>
-        <x:item x="148"/>
-        <x:item x="149"/>
-        <x:item x="150"/>
-        <x:item x="151"/>
-        <x:item x="152"/>
-        <x:item x="153"/>
-        <x:item x="154"/>
-        <x:item x="155"/>
-        <x:item x="156"/>
-        <x:item x="157"/>
-        <x:item x="158"/>
-        <x:item x="159"/>
-        <x:item x="160"/>
-        <x:item x="161"/>
-        <x:item x="162"/>
-        <x:item x="163"/>
-        <x:item x="164"/>
-        <x:item x="165"/>
-        <x:item x="166"/>
-        <x:item x="167"/>
-        <x:item x="168"/>
-        <x:item x="169"/>
-        <x:item x="170"/>
-        <x:item x="171"/>
-        <x:item x="172"/>
-        <x:item x="173"/>
-        <x:item x="174"/>
-        <x:item x="175"/>
-        <x:item x="176"/>
-        <x:item x="177"/>
-        <x:item x="178"/>
-        <x:item x="179"/>
-        <x:item x="180"/>
-        <x:item x="181"/>
-        <x:item x="182"/>
-        <x:item x="183"/>
-        <x:item x="184"/>
-        <x:item x="185"/>
-        <x:item x="186"/>
-        <x:item x="187"/>
-        <x:item x="188"/>
-        <x:item x="189"/>
-        <x:item x="190"/>
-        <x:item x="191"/>
-        <x:item x="192"/>
-        <x:item x="193"/>
-        <x:item x="194"/>
-        <x:item x="195"/>
-        <x:item x="196"/>
-        <x:item x="197"/>
-        <x:item x="198"/>
-        <x:item x="199"/>
-        <x:item x="200"/>
-        <x:item x="201"/>
-        <x:item x="202"/>
-        <x:item x="203"/>
-        <x:item x="204"/>
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Ship date" compact="0" outline="0">
-      <x:items count="1">
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Items total" dataField="1" compact="0" outline="0">
-      <x:items count="1">
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Tax rate" compact="0" outline="0">
-      <x:items count="1">
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField name="Amount paid" compact="0" outline="0">
-      <x:items count="1">
-        <x:item t="default"/>
-      </x:items>
-    </x:pivotField>
-  </x:pivotFields>
-  <x:rowFields count="2">
-    <x:field x="0"/>
-    <x:field x="2"/>
-  </x:rowFields>
-  <x:rowItems count="261">
-    <x:i>
-      <x:x v="0"/>
-    </x:i>
-    <x:i>
-      <x:x v="1"/>
-    </x:i>
-    <x:i>
-      <x:x v="2"/>
-    </x:i>
-    <x:i>
-      <x:x v="3"/>
-    </x:i>
-    <x:i>
-      <x:x v="4"/>
-    </x:i>
-    <x:i>
-      <x:x v="5"/>
-    </x:i>
-    <x:i>
-      <x:x v="6"/>
-    </x:i>
-    <x:i>
-      <x:x v="7"/>
-    </x:i>
-    <x:i>
-      <x:x v="8"/>
-    </x:i>
-    <x:i>
-      <x:x v="9"/>
-    </x:i>
-    <x:i>
-      <x:x v="10"/>
-    </x:i>
-    <x:i>
-      <x:x v="11"/>
-    </x:i>
-    <x:i>
-      <x:x v="12"/>
-    </x:i>
-    <x:i>
-      <x:x v="13"/>
-    </x:i>
-    <x:i>
-      <x:x v="14"/>
-    </x:i>
-    <x:i>
-      <x:x v="15"/>
-    </x:i>
-    <x:i>
-      <x:x v="16"/>
-    </x:i>
-    <x:i>
-      <x:x v="17"/>
-    </x:i>
-    <x:i>
-      <x:x v="18"/>
-    </x:i>
-    <x:i>
-      <x:x v="19"/>
-    </x:i>
-    <x:i>
-      <x:x v="20"/>
-    </x:i>
-    <x:i>
-      <x:x v="21"/>
-    </x:i>
-    <x:i>
-      <x:x v="22"/>
-    </x:i>
-    <x:i>
-      <x:x v="23"/>
-    </x:i>
-    <x:i>
-      <x:x v="24"/>
-    </x:i>
-    <x:i>
-      <x:x v="25"/>
-    </x:i>
-    <x:i>
-      <x:x v="26"/>
-    </x:i>
-    <x:i>
-      <x:x v="27"/>
-    </x:i>
-    <x:i>
-      <x:x v="28"/>
-    </x:i>
-    <x:i>
-      <x:x v="29"/>
-    </x:i>
-    <x:i>
-      <x:x v="30"/>
-    </x:i>
-    <x:i>
-      <x:x v="31"/>
-    </x:i>
-    <x:i>
-      <x:x v="32"/>
-    </x:i>
-    <x:i>
-      <x:x v="33"/>
-    </x:i>
-    <x:i>
-      <x:x v="34"/>
-    </x:i>
-    <x:i>
-      <x:x v="35"/>
-    </x:i>
-    <x:i>
-      <x:x v="36"/>
-    </x:i>
-    <x:i>
-      <x:x v="37"/>
-    </x:i>
-    <x:i>
-      <x:x v="38"/>
-    </x:i>
-    <x:i>
-      <x:x v="39"/>
-    </x:i>
-    <x:i>
-      <x:x v="40"/>
-    </x:i>
-    <x:i>
-      <x:x v="41"/>
-    </x:i>
-    <x:i>
-      <x:x v="42"/>
-    </x:i>
-    <x:i>
-      <x:x v="43"/>
-    </x:i>
-    <x:i>
-      <x:x v="44"/>
-    </x:i>
-    <x:i>
-      <x:x v="45"/>
-    </x:i>
-    <x:i>
-      <x:x v="46"/>
-    </x:i>
-    <x:i>
-      <x:x v="47"/>
-    </x:i>
-    <x:i>
-      <x:x v="48"/>
-    </x:i>
-    <x:i>
-      <x:x v="49"/>
-    </x:i>
-    <x:i>
-      <x:x v="50"/>
-    </x:i>
-    <x:i>
-      <x:x v="51"/>
-    </x:i>
-    <x:i>
-      <x:x v="52"/>
-    </x:i>
-    <x:i>
-      <x:x v="53"/>
-    </x:i>
-    <x:i t="grand">
-      <x:x/>
-    </x:i>
-    <x:i>
-      <x:x v="0"/>
-    </x:i>
-    <x:i>
-      <x:x v="1"/>
-    </x:i>
-    <x:i>
-      <x:x v="2"/>
-    </x:i>
-    <x:i>
-      <x:x v="3"/>
-    </x:i>
-    <x:i>
-      <x:x v="4"/>
-    </x:i>
-    <x:i>
-      <x:x v="5"/>
-    </x:i>
-    <x:i>
-      <x:x v="6"/>
-    </x:i>
-    <x:i>
-      <x:x v="7"/>
-    </x:i>
-    <x:i>
-      <x:x v="8"/>
-    </x:i>
-    <x:i>
-      <x:x v="9"/>
-    </x:i>
-    <x:i>
-      <x:x v="10"/>
-    </x:i>
-    <x:i>
-      <x:x v="11"/>
-    </x:i>
-    <x:i>
-      <x:x v="12"/>
-    </x:i>
-    <x:i>
-      <x:x v="13"/>
-    </x:i>
-    <x:i>
-      <x:x v="14"/>
-    </x:i>
-    <x:i>
-      <x:x v="15"/>
-    </x:i>
-    <x:i>
-      <x:x v="16"/>
-    </x:i>
-    <x:i>
-      <x:x v="17"/>
-    </x:i>
-    <x:i>
-      <x:x v="18"/>
-    </x:i>
-    <x:i>
-      <x:x v="19"/>
-    </x:i>
-    <x:i>
-      <x:x v="20"/>
-    </x:i>
-    <x:i>
-      <x:x v="21"/>
-    </x:i>
-    <x:i>
-      <x:x v="22"/>
-    </x:i>
-    <x:i>
-      <x:x v="23"/>
-    </x:i>
-    <x:i>
-      <x:x v="24"/>
-    </x:i>
-    <x:i>
-      <x:x v="25"/>
-    </x:i>
-    <x:i>
-      <x:x v="26"/>
-    </x:i>
-    <x:i>
-      <x:x v="27"/>
-    </x:i>
-    <x:i>
-      <x:x v="28"/>
-    </x:i>
-    <x:i>
-      <x:x v="29"/>
-    </x:i>
-    <x:i>
-      <x:x v="30"/>
-    </x:i>
-    <x:i>
-      <x:x v="31"/>
-    </x:i>
-    <x:i>
-      <x:x v="32"/>
-    </x:i>
-    <x:i>
-      <x:x v="33"/>
-    </x:i>
-    <x:i>
-      <x:x v="34"/>
-    </x:i>
-    <x:i>
-      <x:x v="35"/>
-    </x:i>
-    <x:i>
-      <x:x v="36"/>
-    </x:i>
-    <x:i>
-      <x:x v="37"/>
-    </x:i>
-    <x:i>
-      <x:x v="38"/>
-    </x:i>
-    <x:i>
-      <x:x v="39"/>
-    </x:i>
-    <x:i>
-      <x:x v="40"/>
-    </x:i>
-    <x:i>
-      <x:x v="41"/>
-    </x:i>
-    <x:i>
-      <x:x v="42"/>
-    </x:i>
-    <x:i>
-      <x:x v="43"/>
-    </x:i>
-    <x:i>
-      <x:x v="44"/>
-    </x:i>
-    <x:i>
-      <x:x v="45"/>
-    </x:i>
-    <x:i>
-      <x:x v="46"/>
-    </x:i>
-    <x:i>
-      <x:x v="47"/>
-    </x:i>
-    <x:i>
-      <x:x v="48"/>
-    </x:i>
-    <x:i>
-      <x:x v="49"/>
-    </x:i>
-    <x:i>
-      <x:x v="50"/>
-    </x:i>
-    <x:i>
-      <x:x v="51"/>
-    </x:i>
-    <x:i>
-      <x:x v="52"/>
-    </x:i>
-    <x:i>
-      <x:x v="53"/>
-    </x:i>
-    <x:i>
-      <x:x v="54"/>
-    </x:i>
-    <x:i>
-      <x:x v="55"/>
-    </x:i>
-    <x:i>
-      <x:x v="56"/>
-    </x:i>
-    <x:i>
-      <x:x v="57"/>
-    </x:i>
-    <x:i>
-      <x:x v="58"/>
-    </x:i>
-    <x:i>
-      <x:x v="59"/>
-    </x:i>
-    <x:i>
-      <x:x v="60"/>
-    </x:i>
-    <x:i>
-      <x:x v="61"/>
-    </x:i>
-    <x:i>
-      <x:x v="62"/>
-    </x:i>
-    <x:i>
-      <x:x v="63"/>
-    </x:i>
-    <x:i>
-      <x:x v="64"/>
-    </x:i>
-    <x:i>
-      <x:x v="65"/>
-    </x:i>
-    <x:i>
-      <x:x v="66"/>
-    </x:i>
-    <x:i>
-      <x:x v="67"/>
-    </x:i>
-    <x:i>
-      <x:x v="68"/>
-    </x:i>
-    <x:i>
-      <x:x v="69"/>
-    </x:i>
-    <x:i>
-      <x:x v="70"/>
-    </x:i>
-    <x:i>
-      <x:x v="71"/>
-    </x:i>
-    <x:i>
-      <x:x v="72"/>
-    </x:i>
-    <x:i>
-      <x:x v="73"/>
-    </x:i>
-    <x:i>
-      <x:x v="74"/>
-    </x:i>
-    <x:i>
-      <x:x v="75"/>
-    </x:i>
-    <x:i>
-      <x:x v="76"/>
-    </x:i>
-    <x:i>
-      <x:x v="77"/>
-    </x:i>
-    <x:i>
-      <x:x v="78"/>
-    </x:i>
-    <x:i>
-      <x:x v="79"/>
-    </x:i>
-    <x:i>
-      <x:x v="80"/>
-    </x:i>
-    <x:i>
-      <x:x v="81"/>
-    </x:i>
-    <x:i>
-      <x:x v="82"/>
-    </x:i>
-    <x:i>
-      <x:x v="83"/>
-    </x:i>
-    <x:i>
-      <x:x v="84"/>
-    </x:i>
-    <x:i>
-      <x:x v="85"/>
-    </x:i>
-    <x:i>
-      <x:x v="86"/>
-    </x:i>
-    <x:i>
-      <x:x v="87"/>
-    </x:i>
-    <x:i>
-      <x:x v="88"/>
-    </x:i>
-    <x:i>
-      <x:x v="89"/>
-    </x:i>
-    <x:i>
-      <x:x v="90"/>
-    </x:i>
-    <x:i>
-      <x:x v="91"/>
-    </x:i>
-    <x:i>
-      <x:x v="92"/>
-    </x:i>
-    <x:i>
-      <x:x v="93"/>
-    </x:i>
-    <x:i>
-      <x:x v="94"/>
-    </x:i>
-    <x:i>
-      <x:x v="95"/>
-    </x:i>
-    <x:i>
-      <x:x v="96"/>
-    </x:i>
-    <x:i>
-      <x:x v="97"/>
-    </x:i>
-    <x:i>
-      <x:x v="98"/>
-    </x:i>
-    <x:i>
-      <x:x v="99"/>
-    </x:i>
-    <x:i>
-      <x:x v="100"/>
-    </x:i>
-    <x:i>
-      <x:x v="101"/>
-    </x:i>
-    <x:i>
-      <x:x v="102"/>
-    </x:i>
-    <x:i>
-      <x:x v="103"/>
-    </x:i>
-    <x:i>
-      <x:x v="104"/>
-    </x:i>
-    <x:i>
-      <x:x v="105"/>
-    </x:i>
-    <x:i>
-      <x:x v="106"/>
-    </x:i>
-    <x:i>
-      <x:x v="107"/>
-    </x:i>
-    <x:i>
-      <x:x v="108"/>
-    </x:i>
-    <x:i>
-      <x:x v="109"/>
-    </x:i>
-    <x:i>
-      <x:x v="110"/>
-    </x:i>
-    <x:i>
-      <x:x v="111"/>
-    </x:i>
-    <x:i>
-      <x:x v="112"/>
-    </x:i>
-    <x:i>
-      <x:x v="113"/>
-    </x:i>
-    <x:i>
-      <x:x v="114"/>
-    </x:i>
-    <x:i>
-      <x:x v="115"/>
-    </x:i>
-    <x:i>
-      <x:x v="116"/>
-    </x:i>
-    <x:i>
-      <x:x v="117"/>
-    </x:i>
-    <x:i>
-      <x:x v="118"/>
-    </x:i>
-    <x:i>
-      <x:x v="119"/>
-    </x:i>
-    <x:i>
-      <x:x v="120"/>
-    </x:i>
-    <x:i>
-      <x:x v="121"/>
-    </x:i>
-    <x:i>
-      <x:x v="122"/>
-    </x:i>
-    <x:i>
-      <x:x v="123"/>
-    </x:i>
-    <x:i>
-      <x:x v="124"/>
-    </x:i>
-    <x:i>
-      <x:x v="125"/>
-    </x:i>
-    <x:i>
-      <x:x v="126"/>
-    </x:i>
-    <x:i>
-      <x:x v="127"/>
-    </x:i>
-    <x:i>
-      <x:x v="128"/>
-    </x:i>
-    <x:i>
-      <x:x v="129"/>
-    </x:i>
-    <x:i>
-      <x:x v="130"/>
-    </x:i>
-    <x:i>
-      <x:x v="131"/>
-    </x:i>
-    <x:i>
-      <x:x v="132"/>
-    </x:i>
-    <x:i>
-      <x:x v="133"/>
-    </x:i>
-    <x:i>
-      <x:x v="134"/>
-    </x:i>
-    <x:i>
-      <x:x v="135"/>
-    </x:i>
-    <x:i>
-      <x:x v="136"/>
-    </x:i>
-    <x:i>
-      <x:x v="137"/>
-    </x:i>
-    <x:i>
-      <x:x v="138"/>
-    </x:i>
-    <x:i>
-      <x:x v="139"/>
-    </x:i>
-    <x:i>
-      <x:x v="140"/>
-    </x:i>
-    <x:i>
-      <x:x v="141"/>
-    </x:i>
-    <x:i>
-      <x:x v="142"/>
-    </x:i>
-    <x:i>
-      <x:x v="143"/>
-    </x:i>
-    <x:i>
-      <x:x v="144"/>
-    </x:i>
-    <x:i>
-      <x:x v="145"/>
-    </x:i>
-    <x:i>
-      <x:x v="146"/>
-    </x:i>
-    <x:i>
-      <x:x v="147"/>
-    </x:i>
-    <x:i>
-      <x:x v="148"/>
-    </x:i>
-    <x:i>
-      <x:x v="149"/>
-    </x:i>
-    <x:i>
-      <x:x v="150"/>
-    </x:i>
-    <x:i>
-      <x:x v="151"/>
-    </x:i>
-    <x:i>
-      <x:x v="152"/>
-    </x:i>
-    <x:i>
-      <x:x v="153"/>
-    </x:i>
-    <x:i>
-      <x:x v="154"/>
-    </x:i>
-    <x:i>
-      <x:x v="155"/>
-    </x:i>
-    <x:i>
-      <x:x v="156"/>
-    </x:i>
-    <x:i>
-      <x:x v="157"/>
-    </x:i>
-    <x:i>
-      <x:x v="158"/>
-    </x:i>
-    <x:i>
-      <x:x v="159"/>
-    </x:i>
-    <x:i>
-      <x:x v="160"/>
-    </x:i>
-    <x:i>
-      <x:x v="161"/>
-    </x:i>
-    <x:i>
-      <x:x v="162"/>
-    </x:i>
-    <x:i>
-      <x:x v="163"/>
-    </x:i>
-    <x:i>
-      <x:x v="164"/>
-    </x:i>
-    <x:i>
-      <x:x v="165"/>
-    </x:i>
-    <x:i>
-      <x:x v="166"/>
-    </x:i>
-    <x:i>
-      <x:x v="167"/>
-    </x:i>
-    <x:i>
-      <x:x v="168"/>
-    </x:i>
-    <x:i>
-      <x:x v="169"/>
-    </x:i>
-    <x:i>
-      <x:x v="170"/>
-    </x:i>
-    <x:i>
-      <x:x v="171"/>
-    </x:i>
-    <x:i>
-      <x:x v="172"/>
-    </x:i>
-    <x:i>
-      <x:x v="173"/>
-    </x:i>
-    <x:i>
-      <x:x v="174"/>
-    </x:i>
-    <x:i>
-      <x:x v="175"/>
-    </x:i>
-    <x:i>
-      <x:x v="176"/>
-    </x:i>
-    <x:i>
-      <x:x v="177"/>
-    </x:i>
-    <x:i>
-      <x:x v="178"/>
-    </x:i>
-    <x:i>
-      <x:x v="179"/>
-    </x:i>
-    <x:i>
-      <x:x v="180"/>
-    </x:i>
-    <x:i>
-      <x:x v="181"/>
-    </x:i>
-    <x:i>
-      <x:x v="182"/>
-    </x:i>
-    <x:i>
-      <x:x v="183"/>
-    </x:i>
-    <x:i>
-      <x:x v="184"/>
-    </x:i>
-    <x:i>
-      <x:x v="185"/>
-    </x:i>
-    <x:i>
-      <x:x v="186"/>
-    </x:i>
-    <x:i>
-      <x:x v="187"/>
-    </x:i>
-    <x:i>
-      <x:x v="188"/>
-    </x:i>
-    <x:i>
-      <x:x v="189"/>
-    </x:i>
-    <x:i>
-      <x:x v="190"/>
-    </x:i>
-    <x:i>
-      <x:x v="191"/>
-    </x:i>
-    <x:i>
-      <x:x v="192"/>
-    </x:i>
-    <x:i>
-      <x:x v="193"/>
-    </x:i>
-    <x:i>
-      <x:x v="194"/>
-    </x:i>
-    <x:i>
-      <x:x v="195"/>
-    </x:i>
-    <x:i>
-      <x:x v="196"/>
-    </x:i>
-    <x:i>
-      <x:x v="197"/>
-    </x:i>
-    <x:i>
-      <x:x v="198"/>
-    </x:i>
-    <x:i>
-      <x:x v="199"/>
-    </x:i>
-    <x:i>
-      <x:x v="200"/>
-    </x:i>
-    <x:i>
-      <x:x v="201"/>
-    </x:i>
-    <x:i>
-      <x:x v="202"/>
-    </x:i>
-    <x:i>
-      <x:x v="203"/>
-    </x:i>
-    <x:i>
-      <x:x v="204"/>
-    </x:i>
-    <x:i t="grand">
-      <x:x/>
-    </x:i>
-  </x:rowItems>
-  <x:colFields count="1">
-    <x:field x="1"/>
-  </x:colFields>
-  <x:colItems count="8">
-    <x:i>
-      <x:x v="0"/>
-    </x:i>
-    <x:i>
-      <x:x v="1"/>
-    </x:i>
-    <x:i>
-      <x:x v="2"/>
-    </x:i>
-    <x:i>
-      <x:x v="3"/>
-    </x:i>
-    <x:i>
-      <x:x v="4"/>
-    </x:i>
-    <x:i>
-      <x:x v="5"/>
-    </x:i>
-    <x:i>
-      <x:x v="6"/>
-    </x:i>
-    <x:i t="grand">
-      <x:x/>
-    </x:i>
-  </x:colItems>
-  <x:dataFields count="1">
-    <x:dataField name="Sum of Items total" fld="4" subtotal="sum" showDataAs="normal" baseField="0" baseItem="0" numFmtId="0"/>
-  </x:dataFields>
-  <x:formats count="1">
-    <x:format dxfId="1">
-      <x:pivotArea type="normal" dataOnly="0" labelOnly="1" fieldPosition="0">
-        <x:references count="1">
-          <x:reference field="1"/>
-        </x:references>
-      </x:pivotArea>
-    </x:format>
-  </x:formats>
-  <x:pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0"/>
-  <x:extLst>
-    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" enableEdit="0" hideValuesRow="1"/>
-    </x:ext>
-  </x:extLst>
-</x:pivotTableDefinition>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" mergeItem="1" createdVersion="3" indent="0" compact="0" compactData="0" gridDropZones="1">
+  <location ref="B4:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
+  <pivotFields count="7">
+    <pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="55">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Payment method" axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="OrderNo" axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="206">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="2"/>
+  </rowFields>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <dataFields count="1">
+    <dataField name="Sum of Items total" fld="4"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
